--- a/tables/Flexible CUE/Local_estpar_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_False_vo_False_CUE_False.xlsx
@@ -588,46 +588,46 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4756359890550635</v>
+        <v>0.4820009970627345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5495892650007902</v>
+        <v>0.5557748387239961</v>
       </c>
       <c r="M2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.465606698018054</v>
       </c>
       <c r="N2" t="n">
-        <v>4.392118121325788</v>
+        <v>4.439263099357669</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001411811968264017</v>
+        <v>0.001403324173184733</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003255034307260409</v>
+        <v>0.003314473593789447</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001084191392240015</v>
+        <v>0.001085901063395683</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001957151727093001</v>
+        <v>0.001988059006275667</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001713372259998414</v>
+        <v>0.001740976233937346</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002793798523456614</v>
+        <v>0.002669213027596314</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008104746108261616</v>
+        <v>0.00808550161638902</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002119649158318201</v>
+        <v>0.002109457767768127</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002868521366231377</v>
+        <v>0.003158695384935008</v>
       </c>
       <c r="X2" t="n">
-        <v>0.002396801792890515</v>
+        <v>0.002375230406224508</v>
       </c>
     </row>
     <row r="3">
@@ -668,46 +668,46 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3970292459420692</v>
+        <v>0.4085894186420144</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5237221972272476</v>
+        <v>0.5347107163444119</v>
       </c>
       <c r="M3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.378970833950168</v>
       </c>
       <c r="N3" t="n">
-        <v>4.321050359967424</v>
+        <v>4.397048503220401</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001001721141458953</v>
+        <v>0.0009986851631368897</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002173629693017153</v>
+        <v>0.00225192927431775</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008465153181801559</v>
+        <v>0.0008440649217406362</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001394393824537253</v>
+        <v>0.001426906904903323</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009224729064881722</v>
+        <v>0.0009465220259329515</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001261628910109229</v>
+        <v>0.001854818211479373</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003693316083615681</v>
+        <v>0.003908158180641577</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001267116457471463</v>
+        <v>0.001698875289465977</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002965805093144011</v>
+        <v>0.002147090031752763</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002200435484650641</v>
+        <v>0.001752792677320138</v>
       </c>
     </row>
     <row r="4">
@@ -748,46 +748,46 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5305184715213833</v>
+        <v>0.52327017402166</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5586178939924467</v>
+        <v>0.5632923374845957</v>
       </c>
       <c r="M4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.449533919724023</v>
       </c>
       <c r="N4" t="n">
-        <v>4.431594952995701</v>
+        <v>4.468590083632223</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002415282860284309</v>
+        <v>0.002104561765109033</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002661568220788083</v>
+        <v>0.002416459581371855</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005334544363852929</v>
+        <v>0.0005257164277545561</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00205313626149355</v>
+        <v>0.002100748064927779</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001240407029031069</v>
+        <v>0.001230053045317944</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006130829596330168</v>
+        <v>0.004879071473616233</v>
       </c>
       <c r="U4" t="n">
-        <v>9.409463560890647e-05</v>
+        <v>0.007151649058275476</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001549833604173108</v>
+        <v>0.001460633553275109</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003658873204429984</v>
+        <v>0.003527520023708981</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003242841009632323</v>
+        <v>0.00227229195208043</v>
       </c>
     </row>
     <row r="5">
@@ -828,46 +828,46 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4066877904640895</v>
+        <v>0.4069734038792395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5414329399232409</v>
+        <v>0.541421490791658</v>
       </c>
       <c r="M5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.328675728015952</v>
       </c>
       <c r="N5" t="n">
-        <v>4.406983813252559</v>
+        <v>4.405411329420687</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001299112279778735</v>
+        <v>0.001298742520986819</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002412228862300424</v>
+        <v>0.002413634136797562</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001047404465584038</v>
+        <v>0.001047245189878097</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001729075980092804</v>
+        <v>0.001728950585206608</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002256178022302035</v>
+        <v>0.002255947472997772</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002532835959561563</v>
+        <v>0.002457474712611301</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0046261637167981</v>
+        <v>0.004632729497721595</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00209372699563074</v>
+        <v>0.002088747330756964</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002441954280431034</v>
+        <v>0.002651575116943114</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004228461723553829</v>
+        <v>0.0041430025757515</v>
       </c>
     </row>
     <row r="6">
@@ -908,46 +908,46 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4654721783172479</v>
+        <v>0.4592879234335376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5556374824028737</v>
+        <v>0.5478670490145763</v>
       </c>
       <c r="M6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.385019187083561</v>
       </c>
       <c r="N6" t="n">
-        <v>4.478456501685485</v>
+        <v>4.422823879198369</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000918021924415632</v>
+        <v>0.0008975286452902113</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002052202011323266</v>
+        <v>0.00197973722332886</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0007449564708334967</v>
+        <v>0.0007343721415318114</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008950516156325404</v>
+        <v>0.000872609515650665</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001076988337713509</v>
+        <v>0.00104700916034469</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001667985080199109</v>
+        <v>0.001677744686486035</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003180329128476134</v>
+        <v>0.003350208408977679</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001455306358167611</v>
+        <v>0.001461941236259923</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001321138576297026</v>
+        <v>0.001556205208249434</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001514836556890999</v>
+        <v>0.001613811398169495</v>
       </c>
     </row>
     <row r="7">
@@ -988,46 +988,46 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3885161499124839</v>
+        <v>0.3951965360399166</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5256109942761992</v>
+        <v>0.5373242925554681</v>
       </c>
       <c r="M7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.421262405329895</v>
       </c>
       <c r="N7" t="n">
-        <v>4.307109887247182</v>
+        <v>4.403092963816217</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00135597236479785</v>
+        <v>0.001343117382976923</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002183389085189719</v>
+        <v>0.002235504906119629</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007504309099514768</v>
+        <v>0.0007539935253230279</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00199389629186568</v>
+        <v>0.002054580161391528</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001249153294987983</v>
+        <v>0.001265053356725014</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002713261854609794</v>
+        <v>0.002640388473431692</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004277295094808327</v>
+        <v>0.004321622735769258</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001471818235952123</v>
+        <v>0.001483845951389792</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002876399377056351</v>
+        <v>0.003236121690170925</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003015274244926424</v>
+        <v>0.002919361239637244</v>
       </c>
     </row>
     <row r="8">
@@ -1068,46 +1068,46 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2616922581078024</v>
+        <v>0.268136507449542</v>
       </c>
       <c r="L8" t="n">
-        <v>0.496615470769983</v>
+        <v>0.512087221972082</v>
       </c>
       <c r="M8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.51057323281028</v>
       </c>
       <c r="N8" t="n">
-        <v>4.301464438251406</v>
+        <v>4.425970018614482</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001919907198530632</v>
+        <v>0.001951356876075347</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002008796979883771</v>
+        <v>0.002105338646830639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00121522309582427</v>
+        <v>0.001229902412122511</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002507763700333836</v>
+        <v>0.002587694009365692</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001410490732759841</v>
+        <v>0.001461348118488464</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004187024036233994</v>
+        <v>0.004195592777139894</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003907754988793573</v>
+        <v>0.003980989251075713</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002552360500549433</v>
+        <v>0.002580439640805522</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004624210333591238</v>
+        <v>0.005067225189870457</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002506018176527174</v>
+        <v>0.002444557665928403</v>
       </c>
     </row>
     <row r="9">
@@ -1148,46 +1148,46 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3418105817087478</v>
+        <v>0.3433990727769943</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5290156789199036</v>
+        <v>0.5311637211698333</v>
       </c>
       <c r="M9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.328025721001465</v>
       </c>
       <c r="N9" t="n">
-        <v>4.389248600792218</v>
+        <v>4.403357051445087</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001902157631317458</v>
+        <v>0.001906604030232696</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002464458686026536</v>
+        <v>0.002483530823036278</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001005332375594415</v>
+        <v>0.001007348943064478</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001814014328350123</v>
+        <v>0.00182037810288859</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00149059573854278</v>
+        <v>0.001499467728638909</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003473427677972592</v>
+        <v>0.004066260606687803</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004070466418041959</v>
+        <v>0.005094961167173334</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001921700523586152</v>
+        <v>0.001973964429114461</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003293987102801381</v>
+        <v>0.002997609478698777</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002674957647020334</v>
+        <v>0.002614906820514569</v>
       </c>
     </row>
     <row r="10">
@@ -1228,46 +1228,46 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4075526360986579</v>
+        <v>0.4233368867748208</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5155120234803109</v>
+        <v>0.5377285023825336</v>
       </c>
       <c r="M10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.304645472857671</v>
       </c>
       <c r="N10" t="n">
-        <v>4.164092899021281</v>
+        <v>4.330826025340635</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001693147315627338</v>
+        <v>0.001730022522036795</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002187810184844546</v>
+        <v>0.002361588302747301</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0007572781584015338</v>
+        <v>0.0007766238730648337</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003160642056618472</v>
+        <v>0.003392152416526474</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001223648009864323</v>
+        <v>0.001286984888566293</v>
       </c>
       <c r="T10" t="n">
-        <v>0.003607481013416717</v>
+        <v>0.003640861161762531</v>
       </c>
       <c r="U10" t="n">
-        <v>0.004892617367354538</v>
+        <v>0.005383048416103412</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001470106296325752</v>
+        <v>0.001512808110715531</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00438443489636636</v>
+        <v>0.005069383831441475</v>
       </c>
       <c r="X10" t="n">
-        <v>0.002055494587555856</v>
+        <v>0.00206659563054242</v>
       </c>
     </row>
     <row r="11">
@@ -1308,46 +1308,46 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1963834722000099</v>
+        <v>0.2019906136872595</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4823820985987689</v>
+        <v>0.4906804358159074</v>
       </c>
       <c r="M11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.107405143193574</v>
       </c>
       <c r="N11" t="n">
-        <v>4.249963594351311</v>
+        <v>4.302765842510607</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002404424369842063</v>
+        <v>0.002392095840339019</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001687697762971891</v>
+        <v>0.001739468361475642</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001293704260371836</v>
+        <v>0.001310681980318146</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002586700036973709</v>
+        <v>0.002665750462055866</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002042656068351616</v>
+        <v>0.002075793884052734</v>
       </c>
       <c r="T11" t="n">
-        <v>0.006514584311248824</v>
+        <v>0.006375658856675861</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003563283447364248</v>
+        <v>0.003805064792629835</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002588278272043063</v>
+        <v>0.002635203690164511</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004899675803139974</v>
+        <v>0.005305818083680714</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004438214600578251</v>
+        <v>0.004431588574087487</v>
       </c>
     </row>
     <row r="12">
@@ -1388,46 +1388,46 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1717706053199348</v>
+        <v>0.1800254501765516</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4207054198532788</v>
+        <v>0.4456016176074714</v>
       </c>
       <c r="M12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.004770333347373</v>
       </c>
       <c r="N12" t="n">
-        <v>4.075693805336392</v>
+        <v>4.238743125060137</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004020999953140811</v>
+        <v>0.0004089097393641913</v>
       </c>
       <c r="P12" t="n">
-        <v>0.003226741083309772</v>
+        <v>0.003614286243177038</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0005079432901001495</v>
+        <v>0.0005128397362181788</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0049527311910969</v>
+        <v>0.00543986491245409</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0009005757861430416</v>
+        <v>0.0009604653684871111</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001063823978780014</v>
+        <v>0.001074674323083145</v>
       </c>
       <c r="U12" t="n">
-        <v>0.005061427934149413</v>
+        <v>0.005634469939059789</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001083897041699262</v>
+        <v>0.00109382852185618</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0089423609552671</v>
+        <v>0.009823647873238459</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00149819148935411</v>
+        <v>0.001555325397184552</v>
       </c>
     </row>
     <row r="13">
@@ -1468,46 +1468,46 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2664202682176131</v>
+        <v>0.2835460062602018</v>
       </c>
       <c r="L13" t="n">
-        <v>0.44892671240708</v>
+        <v>0.4780855870506601</v>
       </c>
       <c r="M13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.337432442552224</v>
       </c>
       <c r="N13" t="n">
-        <v>4.287058245957822</v>
+        <v>4.487672442533043</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001643803318838519</v>
+        <v>0.001753229293311984</v>
       </c>
       <c r="P13" t="n">
-        <v>0.002830537558789762</v>
+        <v>0.003185724771870839</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001361892460585225</v>
+        <v>0.001442563982057401</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01086528165405674</v>
+        <v>0.01128841474473307</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01696891430425618</v>
+        <v>0.01739662318465506</v>
       </c>
       <c r="T13" t="n">
-        <v>0.009642856626228</v>
+        <v>0.01063315898976523</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02773672133565627</v>
+        <v>0.0304457404121324</v>
       </c>
       <c r="V13" t="n">
-        <v>0.008083918402205828</v>
+        <v>0.008712285609849175</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03094112749840868</v>
+        <v>0.03433804052118489</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04663255395584775</v>
+        <v>0.05155769378607284</v>
       </c>
     </row>
     <row r="14">
@@ -1548,46 +1548,46 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3496678499507883</v>
+        <v>0.3546715346376434</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5052148281334342</v>
+        <v>0.5133953637543747</v>
       </c>
       <c r="M14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.399848195776872</v>
       </c>
       <c r="N14" t="n">
-        <v>4.327929319861911</v>
+        <v>4.399228757419802</v>
       </c>
       <c r="O14" t="n">
-        <v>0.007388876367138785</v>
+        <v>0.007427732388541494</v>
       </c>
       <c r="P14" t="n">
-        <v>0.007212785396248546</v>
+        <v>0.007413538375391182</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01070888646578344</v>
+        <v>0.01071438901634036</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01265264209305718</v>
+        <v>0.01285757004675775</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02213290108188845</v>
+        <v>0.02267604516406411</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01343485429141349</v>
+        <v>0.01408766459008326</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01873052008761066</v>
+        <v>0.02376792934684772</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02001043343520266</v>
+        <v>0.02035337642530559</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01874715372747956</v>
+        <v>0.02429903460229448</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0396970983236125</v>
+        <v>0.04834345345409055</v>
       </c>
     </row>
     <row r="15">
@@ -1628,46 +1628,46 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4100970253309362</v>
+        <v>0.4107507024762867</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5325380419366822</v>
+        <v>0.5352951084552128</v>
       </c>
       <c r="M15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.081381386375272</v>
       </c>
       <c r="N15" t="n">
-        <v>4.338064235351958</v>
+        <v>4.339169589930354</v>
       </c>
       <c r="O15" t="n">
-        <v>0.007934280484871221</v>
+        <v>0.007969960618389352</v>
       </c>
       <c r="P15" t="n">
-        <v>0.007829464083482599</v>
+        <v>0.007898270540086206</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.009543980150258502</v>
+        <v>0.009570617963066769</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01266018413841627</v>
+        <v>0.01276131220098181</v>
       </c>
       <c r="S15" t="n">
-        <v>0.04809053240089145</v>
+        <v>0.04861357676262122</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01494082124525295</v>
+        <v>0.01468075563442484</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01518462123198113</v>
+        <v>0.01539876186411284</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0180827061174778</v>
+        <v>0.01812021055044602</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01685212664213574</v>
+        <v>0.01782873845023634</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2136803800735428</v>
+        <v>0.2165882066593008</v>
       </c>
     </row>
     <row r="16">
@@ -1708,46 +1708,46 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5751444245764759</v>
+        <v>0.5547407510209781</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5874991383321818</v>
+        <v>0.5734821582779931</v>
       </c>
       <c r="M16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.399547914881411</v>
       </c>
       <c r="N16" t="n">
-        <v>4.643383743353472</v>
+        <v>4.539077565296358</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02892750265868274</v>
+        <v>0.02796949386226819</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02114754886087068</v>
+        <v>0.02003421251905571</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02297301594464203</v>
+        <v>0.02180540941540461</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01463328664401356</v>
+        <v>0.01388633991859524</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01412153133190294</v>
+        <v>0.006263433551753609</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1993752876481056</v>
+        <v>0.2916227790431715</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1648388222674023</v>
+        <v>0.262934803151423</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1836801468666151</v>
+        <v>0.2949069973461528</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1079234351673056</v>
+        <v>0.1716397859462628</v>
       </c>
       <c r="X16" t="n">
-        <v>2.313053389731011</v>
+        <v>26.51235180071523</v>
       </c>
     </row>
     <row r="17">
@@ -1788,46 +1788,46 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2566081945578824</v>
+        <v>0.2331461754905137</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4363746343617869</v>
+        <v>0.406589364121359</v>
       </c>
       <c r="M17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.94020970433473</v>
       </c>
       <c r="N17" t="n">
-        <v>4.201369302113632</v>
+        <v>4.112353878722189</v>
       </c>
       <c r="O17" t="n">
-        <v>0.007856708829439908</v>
+        <v>0.00750426518253162</v>
       </c>
       <c r="P17" t="n">
-        <v>0.00439244695718288</v>
+        <v>0.003433148094599903</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.007297043354753754</v>
+        <v>0.00707592562003308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.008517391233478772</v>
+        <v>0.007342364716052921</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01252726877965263</v>
+        <v>0.0118792985093066</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01411817878848988</v>
+        <v>0.01830638727051602</v>
       </c>
       <c r="U17" t="n">
-        <v>2.866704264320381e-05</v>
+        <v>0.0454312631705148</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01343441079209496</v>
+        <v>0.01597836488037385</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01110485910982707</v>
+        <v>0.04908081565810252</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02403350787685885</v>
+        <v>0.03080727381976259</v>
       </c>
     </row>
     <row r="18">
@@ -1868,46 +1868,46 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4170637401884277</v>
+        <v>0.4237696658272739</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5175566638754031</v>
+        <v>0.5310760399988518</v>
       </c>
       <c r="M18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.353516083339685</v>
       </c>
       <c r="N18" t="n">
-        <v>4.24963128998946</v>
+        <v>4.363451685761255</v>
       </c>
       <c r="O18" t="n">
-        <v>0.008310143899430338</v>
+        <v>0.008473421332769952</v>
       </c>
       <c r="P18" t="n">
-        <v>0.007860822726826996</v>
+        <v>0.008203538200273676</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.007465225165908592</v>
+        <v>0.007576683739947955</v>
       </c>
       <c r="R18" t="n">
-        <v>0.01633399668700194</v>
+        <v>0.01698566609386941</v>
       </c>
       <c r="S18" t="n">
-        <v>0.01478562471306004</v>
+        <v>0.0152744982461058</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01554257411534444</v>
+        <v>0.01553652280596278</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01629351614591764</v>
+        <v>0.01770063107284404</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01361709225752969</v>
+        <v>0.01380917670459922</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02363879161395742</v>
+        <v>0.02610768403474725</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02364402427600891</v>
+        <v>0.02431233473304231</v>
       </c>
     </row>
     <row r="19">
@@ -1948,46 +1948,46 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5813650193172442</v>
+        <v>0.4773272763108123</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5871285076440946</v>
+        <v>0.5579678990525505</v>
       </c>
       <c r="M19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.822055423832857</v>
       </c>
       <c r="N19" t="n">
-        <v>4.660973485752476</v>
+        <v>4.423535276551999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00360947368880803</v>
+        <v>0.003377614411842964</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01377131376106879</v>
+        <v>0.0123452368162881</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.004050223814973856</v>
+        <v>0.003958066090485471</v>
       </c>
       <c r="R19" t="n">
-        <v>0.003607110439425896</v>
+        <v>0.003276485620337937</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08490776835307436</v>
+        <v>0.07990161302197171</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0001114797870722531</v>
+        <v>0.009671759418108026</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02728735929367223</v>
+        <v>0.02573539372470116</v>
       </c>
       <c r="V19" t="n">
-        <v>0.009514390701118045</v>
+        <v>0.009842889091851513</v>
       </c>
       <c r="W19" t="n">
-        <v>0.009942387835779576</v>
+        <v>0.01091587937448386</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6197984411259235</v>
+        <v>0.6192280951586201</v>
       </c>
     </row>
     <row r="20">
@@ -2028,46 +2028,46 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4153745673784932</v>
+        <v>0.4199137651576323</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5434455208857594</v>
+        <v>0.5474936203784275</v>
       </c>
       <c r="M20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.56912263600572</v>
       </c>
       <c r="N20" t="n">
-        <v>4.513191280802014</v>
+        <v>4.539887473076988</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00543952324672648</v>
+        <v>0.00549481518068809</v>
       </c>
       <c r="P20" t="n">
-        <v>0.005662920114765049</v>
+        <v>0.005836481944462598</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.006335175254643104</v>
+        <v>0.006351785179579538</v>
       </c>
       <c r="R20" t="n">
-        <v>0.008238461903860638</v>
+        <v>0.00826320315471335</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03645597589308863</v>
+        <v>0.03705695498277304</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01007401957163782</v>
+        <v>0.01112562896190301</v>
       </c>
       <c r="U20" t="n">
-        <v>1.940317416243571e-05</v>
+        <v>0.01873979166028595</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01168705472859032</v>
+        <v>0.01212465097508708</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01357490379932782</v>
+        <v>0.01559584446911312</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06221750100399723</v>
+        <v>0.06060844297327843</v>
       </c>
     </row>
     <row r="21">
@@ -2108,46 +2108,46 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5351911822574889</v>
+        <v>0.5119505968393867</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5529805868839661</v>
+        <v>0.5213787263452643</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.080584583903153</v>
       </c>
       <c r="N21" t="n">
-        <v>4.386426514229272</v>
+        <v>4.150903815996617</v>
       </c>
       <c r="O21" t="n">
-        <v>0.005832137729673757</v>
+        <v>0.005639635455711436</v>
       </c>
       <c r="P21" t="n">
-        <v>0.02061937465829701</v>
+        <v>0.01978454819557003</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.001990827884337807</v>
+        <v>0.001936691368467081</v>
       </c>
       <c r="R21" t="n">
-        <v>0.003899819063973757</v>
+        <v>0.00314714169940986</v>
       </c>
       <c r="S21" t="n">
-        <v>0.02432251828926545</v>
+        <v>0.02137332562871849</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01231467678056997</v>
+        <v>0.01198871036824219</v>
       </c>
       <c r="U21" t="n">
-        <v>0.05097889634333815</v>
+        <v>0.0485109584786317</v>
       </c>
       <c r="V21" t="n">
-        <v>0.007627043694013456</v>
+        <v>0.007610641826160927</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01491131615829165</v>
+        <v>0.01544733776554973</v>
       </c>
       <c r="X21" t="n">
-        <v>0.04298008073173994</v>
+        <v>0.04307495191518745</v>
       </c>
     </row>
     <row r="22">
@@ -2188,46 +2188,46 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3707840411234965</v>
+        <v>0.3688714801677828</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4929829334718302</v>
+        <v>0.4920088310018856</v>
       </c>
       <c r="M22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.178478767273362</v>
       </c>
       <c r="N22" t="n">
-        <v>4.395534351996325</v>
+        <v>4.35056357786738</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004135340937874296</v>
+        <v>0.004117314356716533</v>
       </c>
       <c r="P22" t="n">
-        <v>0.00116821985563095</v>
+        <v>0.00114886756582807</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.003058157936809376</v>
+        <v>0.00305482716779904</v>
       </c>
       <c r="R22" t="n">
-        <v>0.00489886850597258</v>
+        <v>0.004910339209037033</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01591051158414338</v>
+        <v>0.0159113081786764</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01672794386958796</v>
+        <v>0.01626591487176414</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03446069469420119</v>
+        <v>0.03347402334414474</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0133395507589797</v>
+        <v>0.0130754115408137</v>
       </c>
       <c r="W22" t="n">
-        <v>0.03505059821410213</v>
+        <v>0.03419474270784342</v>
       </c>
       <c r="X22" t="n">
-        <v>0.08117722859950822</v>
+        <v>0.07925215511393971</v>
       </c>
     </row>
     <row r="23">
@@ -2268,46 +2268,46 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3404821858300435</v>
+        <v>0.3463056376458854</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4865803456486928</v>
+        <v>0.4955049680069133</v>
       </c>
       <c r="M23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.869820336646796</v>
       </c>
       <c r="N23" t="n">
-        <v>4.200834317766992</v>
+        <v>4.220654455048162</v>
       </c>
       <c r="O23" t="n">
-        <v>0.006836823950226738</v>
+        <v>0.006894049230856078</v>
       </c>
       <c r="P23" t="n">
-        <v>0.005961624207838277</v>
+        <v>0.006183078196142612</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.005029985956267802</v>
+        <v>0.005088717594890914</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01479646612886706</v>
+        <v>0.01530935327516402</v>
       </c>
       <c r="S23" t="n">
-        <v>0.04037345106417994</v>
+        <v>0.04151817707709853</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01373822070588126</v>
+        <v>0.01373854621123025</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01869300348572713</v>
+        <v>0.01927005828472981</v>
       </c>
       <c r="V23" t="n">
-        <v>0.01051341646594205</v>
+        <v>0.01064430192017393</v>
       </c>
       <c r="W23" t="n">
-        <v>0.03240530931595037</v>
+        <v>0.03312580761433149</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1737611542710998</v>
+        <v>0.1832004327571876</v>
       </c>
     </row>
     <row r="24">
@@ -2348,46 +2348,46 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5248228924400306</v>
+        <v>0.5381273422429782</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5346964253424216</v>
+        <v>0.5470027408408563</v>
       </c>
       <c r="M24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.275774819085798</v>
       </c>
       <c r="N24" t="n">
-        <v>4.250200988090688</v>
+        <v>4.34190649096697</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01191446139015323</v>
+        <v>0.01203545559721172</v>
       </c>
       <c r="P24" t="n">
-        <v>0.009843375670222953</v>
+        <v>0.01004529823354628</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01480522553972772</v>
+        <v>0.01499757294487271</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01810962373753187</v>
+        <v>0.01862265053993981</v>
       </c>
       <c r="S24" t="n">
-        <v>0.02290300202583332</v>
+        <v>0.00967468292000678</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03433548807395292</v>
+        <v>0.03507891200501202</v>
       </c>
       <c r="U24" t="n">
-        <v>0.05285209320903399</v>
+        <v>0.05415999265245638</v>
       </c>
       <c r="V24" t="n">
-        <v>0.05102574050886319</v>
+        <v>0.05259305234620553</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1211477477911129</v>
+        <v>0.1261211523055847</v>
       </c>
       <c r="X24" t="n">
-        <v>4.553326744797118</v>
+        <v>14.75414444609668</v>
       </c>
     </row>
     <row r="25">
@@ -2428,46 +2428,46 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.546176191779207</v>
+        <v>0.5494012369207484</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5474420448965328</v>
+        <v>0.553169863386759</v>
       </c>
       <c r="M25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.359776070804065</v>
       </c>
       <c r="N25" t="n">
-        <v>4.345180802258644</v>
+        <v>4.387847283084264</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001142236847386216</v>
+        <v>0.001157681547578076</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001125960288709156</v>
+        <v>0.001157589154790366</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0006278617346354387</v>
+        <v>0.0006302853211086022</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0007783675282419296</v>
+        <v>0.0007832485721281111</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003740896155903504</v>
+        <v>0.0003838724546397517</v>
       </c>
       <c r="T25" t="n">
-        <v>0.002278497080195158</v>
+        <v>0.002267958486245309</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002563132149518328</v>
+        <v>0.00270899601992159</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001613046222160079</v>
+        <v>0.00162140724802391</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001924345786680257</v>
+        <v>0.002106701845915807</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001594172714349105</v>
+        <v>0.001540730271712957</v>
       </c>
     </row>
     <row r="26">
@@ -2508,46 +2508,46 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5471977775578866</v>
+        <v>0.540731726273736</v>
       </c>
       <c r="L26" t="n">
-        <v>0.553243708882694</v>
+        <v>0.5490301157634917</v>
       </c>
       <c r="M26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.295183238249074</v>
       </c>
       <c r="N26" t="n">
-        <v>4.388396638380531</v>
+        <v>4.357008735272015</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001934712155372971</v>
+        <v>0.001938013741353031</v>
       </c>
       <c r="P26" t="n">
-        <v>0.002247508000181218</v>
+        <v>0.00221206757913711</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0009007415218890747</v>
+        <v>0.0008933418646792555</v>
       </c>
       <c r="R26" t="n">
-        <v>0.001115793874677582</v>
+        <v>0.00109962526127561</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0007023936735630908</v>
+        <v>0.0006904394360973052</v>
       </c>
       <c r="T26" t="n">
-        <v>0.003255327138696956</v>
+        <v>0.003211259008394061</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002616372654694592</v>
+        <v>0.002694103808050452</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001845537360012078</v>
+        <v>0.001847268570726132</v>
       </c>
       <c r="W26" t="n">
-        <v>0.002024537564001663</v>
+        <v>0.002219502083977518</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001572516164232235</v>
+        <v>0.001505072667080908</v>
       </c>
     </row>
     <row r="27">
@@ -2588,46 +2588,46 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5184276146984496</v>
+        <v>0.5300735357727636</v>
       </c>
       <c r="L27" t="n">
-        <v>0.522802990380229</v>
+        <v>0.535135312738271</v>
       </c>
       <c r="M27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.215743336119488</v>
       </c>
       <c r="N27" t="n">
-        <v>4.161532164486157</v>
+        <v>4.253474004984595</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0009977811094226037</v>
+        <v>0.001012555397734606</v>
       </c>
       <c r="P27" t="n">
-        <v>0.00140439241258761</v>
+        <v>0.001487015784377962</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001299767095309884</v>
+        <v>0.0013059701019892</v>
       </c>
       <c r="R27" t="n">
-        <v>0.001316891372834698</v>
+        <v>0.00136209974248716</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0009613934076053007</v>
+        <v>0.0009913447923430745</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001975091393319319</v>
+        <v>0.001988809417429517</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002347271507107148</v>
+        <v>0.002518024516275519</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002429274915114009</v>
+        <v>0.002455191652587889</v>
       </c>
       <c r="W27" t="n">
-        <v>0.002262981091139818</v>
+        <v>0.002537847236615794</v>
       </c>
       <c r="X27" t="n">
-        <v>0.002055689157811729</v>
+        <v>0.00200568844827443</v>
       </c>
     </row>
     <row r="28">
@@ -2668,46 +2668,46 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4418134987247647</v>
+        <v>0.4452115703335381</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5165380723694751</v>
+        <v>0.5401267358905437</v>
       </c>
       <c r="M28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.128552560111538</v>
       </c>
       <c r="N28" t="n">
-        <v>4.160435948102211</v>
+        <v>4.340322074606317</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001309947571271163</v>
+        <v>0.00126334998893581</v>
       </c>
       <c r="P28" t="n">
-        <v>1.000000000000025e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001444569409496707</v>
+        <v>0.001452102018642351</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005488927609893956</v>
+        <v>0.005614392106655404</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01147648556967765</v>
+        <v>0.01164061372255424</v>
       </c>
       <c r="T28" t="n">
-        <v>0.003050280472370881</v>
+        <v>0.002977483695452996</v>
       </c>
       <c r="U28" t="n">
-        <v>0.008309589076802073</v>
+        <v>0.008356130336639078</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003055555887744636</v>
+        <v>0.003065344613953413</v>
       </c>
       <c r="W28" t="n">
-        <v>0.01041339694030751</v>
+        <v>0.01074742264297821</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02723794056066892</v>
+        <v>0.02755580185847104</v>
       </c>
     </row>
     <row r="29">
@@ -2748,46 +2748,46 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5137115865110338</v>
+        <v>0.5450393411938402</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5153837872858579</v>
+        <v>0.5378439064658589</v>
       </c>
       <c r="M29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.327280143443206</v>
       </c>
       <c r="N29" t="n">
-        <v>4.106195300789897</v>
+        <v>4.273660911914124</v>
       </c>
       <c r="O29" t="n">
-        <v>0.003824203123864512</v>
+        <v>0.003929893345178515</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01898577390807267</v>
+        <v>0.01899259387671743</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0006860771199035154</v>
+        <v>0.0009447870484310175</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01901505209728481</v>
+        <v>0.02167819992120882</v>
       </c>
       <c r="S29" t="n">
-        <v>0.01019184225900133</v>
+        <v>0.0105071624805524</v>
       </c>
       <c r="T29" t="n">
-        <v>0.006369266018414415</v>
+        <v>0.006426931862669509</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0795738086483852</v>
+        <v>0.07519599170340231</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003495550622605898</v>
+        <v>0.003536722927407943</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03902895098122114</v>
+        <v>0.05000623514702596</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01852774714872968</v>
+        <v>0.01813806959402106</v>
       </c>
     </row>
     <row r="30">
@@ -2828,46 +2828,46 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.491714824136214</v>
+        <v>0.5180684702589733</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5157110676211089</v>
+        <v>0.5448577815063299</v>
       </c>
       <c r="M30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.577350772514278</v>
       </c>
       <c r="N30" t="n">
-        <v>4.113769683666699</v>
+        <v>4.339109306159301</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002198263300892629</v>
+        <v>0.002261034364808982</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004986673694323406</v>
+        <v>0.005629642527933598</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0004635534972475259</v>
+        <v>0.0006121217654199854</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01077971549114439</v>
+        <v>0.01178527129785273</v>
       </c>
       <c r="S30" t="n">
-        <v>0.005123274292086078</v>
+        <v>0.005617842513038024</v>
       </c>
       <c r="T30" t="n">
-        <v>0.003968089297065193</v>
+        <v>0.003996118371189472</v>
       </c>
       <c r="U30" t="n">
-        <v>0.009018699576119105</v>
+        <v>0.0101715710623463</v>
       </c>
       <c r="V30" t="n">
-        <v>0.003180133042586526</v>
+        <v>0.003288688272475206</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01847388087643579</v>
+        <v>0.02039742588598964</v>
       </c>
       <c r="X30" t="n">
-        <v>0.007319644624558094</v>
+        <v>0.007607950423399105</v>
       </c>
     </row>
     <row r="31">
@@ -2908,46 +2908,46 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5492159660579294</v>
+        <v>0.5411091241769229</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5549048310241131</v>
+        <v>0.5556978667155873</v>
       </c>
       <c r="M31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.297995521688784</v>
       </c>
       <c r="N31" t="n">
-        <v>4.400769419079285</v>
+        <v>4.406670651650804</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002493602409323193</v>
+        <v>0.002482585655425598</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007506319648128759</v>
+        <v>0.007465202381290556</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0006517560140672309</v>
+        <v>0.0006461726625112033</v>
       </c>
       <c r="R31" t="n">
-        <v>0.002413516613753379</v>
+        <v>0.002412704530710292</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001233507340494202</v>
+        <v>0.001226001704476962</v>
       </c>
       <c r="T31" t="n">
-        <v>0.004339783110714235</v>
+        <v>0.004252781974369944</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01882750645566571</v>
+        <v>0.01855833226933372</v>
       </c>
       <c r="V31" t="n">
-        <v>0.002773476924041719</v>
+        <v>0.002771415060403715</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003705191525455185</v>
+        <v>0.003967572597895572</v>
       </c>
       <c r="X31" t="n">
-        <v>0.003672114210861992</v>
+        <v>0.003509555661825215</v>
       </c>
     </row>
     <row r="32">
@@ -2988,46 +2988,46 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5246702789488129</v>
+        <v>0.5785259936431176</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5153732766279748</v>
+        <v>0.5569642496622</v>
       </c>
       <c r="M32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.576621334530718</v>
       </c>
       <c r="N32" t="n">
-        <v>4.106116203702602</v>
+        <v>4.41609064602723</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008102357520556184</v>
+        <v>0.0008324140239795527</v>
       </c>
       <c r="P32" t="n">
-        <v>0.004848617564499112</v>
+        <v>0.005225616144913479</v>
       </c>
       <c r="Q32" t="n">
-        <v>1e-05</v>
+        <v>1.000000000033531e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.005437605075745915</v>
+        <v>0.00592955115043159</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00178126677268422</v>
+        <v>0.001961800586290341</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002398586482394541</v>
+        <v>0.00242084692056028</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01070022966806358</v>
+        <v>0.01137717000891556</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002520404843956594</v>
+        <v>0.002535087797342961</v>
       </c>
       <c r="W32" t="n">
-        <v>0.01025888935666907</v>
+        <v>0.01157848904815869</v>
       </c>
       <c r="X32" t="n">
-        <v>0.004335413635141191</v>
+        <v>0.004406982058343866</v>
       </c>
     </row>
     <row r="33">
@@ -3066,46 +3066,46 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4068426477840261</v>
+        <v>0.3932497006496025</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5172729571962708</v>
+        <v>0.5378821124575858</v>
       </c>
       <c r="M33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.368367739242999</v>
       </c>
       <c r="N33" t="n">
-        <v>4.153925437863803</v>
+        <v>4.330314865607638</v>
       </c>
       <c r="O33" t="n">
-        <v>0.004806089910692628</v>
+        <v>0.004888663914502342</v>
       </c>
       <c r="P33" t="n">
-        <v>0.006698523892770663</v>
+        <v>0.007212428671348764</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00379831871740148</v>
+        <v>0.003912686249517354</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01446005909232549</v>
+        <v>0.01561764853255337</v>
       </c>
       <c r="S33" t="n">
-        <v>0.007551734189874931</v>
+        <v>0.007963689824454128</v>
       </c>
       <c r="T33" t="n">
-        <v>0.009414756713013665</v>
+        <v>0.009474880490404517</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01640988241328127</v>
+        <v>0.01675315289859948</v>
       </c>
       <c r="V33" t="n">
-        <v>0.006850385004793477</v>
+        <v>0.007049281676337073</v>
       </c>
       <c r="W33" t="n">
-        <v>0.02025610988278711</v>
+        <v>0.0231523686449879</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01140892947521701</v>
+        <v>0.01155482303228677</v>
       </c>
     </row>
     <row r="34">
@@ -3146,46 +3146,46 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5179999681685502</v>
+        <v>0.536901696262555</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5226960807051596</v>
+        <v>0.5432769441177873</v>
       </c>
       <c r="M34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.266640352725299</v>
       </c>
       <c r="N34" t="n">
-        <v>4.16073500377209</v>
+        <v>4.314148516785144</v>
       </c>
       <c r="O34" t="n">
-        <v>0.006396293635884806</v>
+        <v>0.006370157979814552</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01593558212972115</v>
+        <v>0.01702657890431597</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.003311364555461037</v>
+        <v>0.003641605001491819</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01676747950082454</v>
+        <v>0.0178614884672569</v>
       </c>
       <c r="S34" t="n">
-        <v>0.009904307118850443</v>
+        <v>0.0106640986111774</v>
       </c>
       <c r="T34" t="n">
-        <v>0.01031913871972387</v>
+        <v>0.01015912955820077</v>
       </c>
       <c r="U34" t="n">
-        <v>0.07415854436052925</v>
+        <v>0.08148469257749509</v>
       </c>
       <c r="V34" t="n">
-        <v>0.004802982096259873</v>
+        <v>0.004999184385137802</v>
       </c>
       <c r="W34" t="n">
-        <v>0.02041923634967668</v>
+        <v>0.02303028801158441</v>
       </c>
       <c r="X34" t="n">
-        <v>0.009061277402518027</v>
+        <v>0.009168973817179155</v>
       </c>
     </row>
     <row r="35">
@@ -3226,46 +3226,46 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5047782193068076</v>
+        <v>0.5172477546113869</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5047844883037719</v>
+        <v>0.5372052578390364</v>
       </c>
       <c r="M35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.120101088769337</v>
       </c>
       <c r="N35" t="n">
-        <v>4.027110841835609</v>
+        <v>4.268901056506724</v>
       </c>
       <c r="O35" t="n">
-        <v>0.00154006222019644</v>
+        <v>0.00160311689198589</v>
       </c>
       <c r="P35" t="n">
-        <v>0.07493306682902234</v>
+        <v>0.05305091754217937</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0009124259110673311</v>
+        <v>0.0009718893269561204</v>
       </c>
       <c r="R35" t="n">
-        <v>0.01203111620228813</v>
+        <v>0.01363881906275516</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001818954554079807</v>
+        <v>0.002001732789806226</v>
       </c>
       <c r="T35" t="n">
-        <v>0.003149503889992193</v>
+        <v>0.003294270805693139</v>
       </c>
       <c r="U35" t="n">
-        <v>11.45870262846453</v>
+        <v>13.76592079389676</v>
       </c>
       <c r="V35" t="n">
-        <v>0.001402909997364626</v>
+        <v>0.00263922640594925</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02350839033038936</v>
+        <v>0.02452224810155695</v>
       </c>
       <c r="X35" t="n">
-        <v>0.004113768905649615</v>
+        <v>0.003987109114662761</v>
       </c>
     </row>
     <row r="36">
@@ -3306,46 +3306,46 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5291426829145613</v>
+        <v>0.5508842687946176</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5286533001529031</v>
+        <v>0.5490937391614111</v>
       </c>
       <c r="M36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.370823363997192</v>
       </c>
       <c r="N36" t="n">
-        <v>4.205155128834506</v>
+        <v>4.357485294707015</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001117041646552059</v>
+        <v>0.001148490572273193</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002891208504392658</v>
+        <v>0.00307717957572216</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0006413463259769413</v>
+        <v>0.0006854268294459944</v>
       </c>
       <c r="R36" t="n">
-        <v>0.002745258714633022</v>
+        <v>0.002938435695939468</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001880469093095483</v>
+        <v>0.001999038289489383</v>
       </c>
       <c r="T36" t="n">
-        <v>0.00278728099009253</v>
+        <v>0.002811096147057301</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006138428184950777</v>
+        <v>0.006337624750983241</v>
       </c>
       <c r="V36" t="n">
-        <v>0.002754812920181533</v>
+        <v>0.0028171002403565</v>
       </c>
       <c r="W36" t="n">
-        <v>0.005006652958869997</v>
+        <v>0.005461112347909127</v>
       </c>
       <c r="X36" t="n">
-        <v>0.005724767737930852</v>
+        <v>0.005692943070074919</v>
       </c>
     </row>
     <row r="37">
@@ -3386,46 +3386,46 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5448562437145308</v>
+        <v>0.5416253914309452</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5499004292251642</v>
+        <v>0.5505769363543592</v>
       </c>
       <c r="M37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.301842560539425</v>
       </c>
       <c r="N37" t="n">
-        <v>4.363493875177069</v>
+        <v>4.368532165107248</v>
       </c>
       <c r="O37" t="n">
-        <v>0.001944411460133493</v>
+        <v>0.001951818525727223</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003764147968941724</v>
+        <v>0.003775338516418326</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001391995955655802</v>
+        <v>0.001390964160980643</v>
       </c>
       <c r="R37" t="n">
-        <v>0.003295915296602483</v>
+        <v>0.00329000288667543</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01088787103072513</v>
+        <v>0.01100114274129598</v>
       </c>
       <c r="T37" t="n">
-        <v>0.004457049396041493</v>
+        <v>0.004396328076821872</v>
       </c>
       <c r="U37" t="n">
-        <v>0.005297126046452208</v>
+        <v>0.005227424127431031</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003433483016010084</v>
+        <v>0.00344109741709066</v>
       </c>
       <c r="W37" t="n">
-        <v>0.00568987726091767</v>
+        <v>0.005951835509162308</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02334385496167965</v>
+        <v>0.02342914338681179</v>
       </c>
     </row>
     <row r="38">
@@ -3466,46 +3466,46 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.540912009343728</v>
+        <v>0.5410877791334675</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5469294033829774</v>
+        <v>0.5459458066566727</v>
       </c>
       <c r="M38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.297836464385832</v>
       </c>
       <c r="N38" t="n">
-        <v>4.341360212500053</v>
+        <v>4.334032058827635</v>
       </c>
       <c r="O38" t="n">
-        <v>0.002330715111194954</v>
+        <v>0.002338921322743589</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001670913674345598</v>
+        <v>0.001666349850650152</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.001018317353601977</v>
+        <v>0.001015483726897044</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002753073458856047</v>
+        <v>0.002741039073618736</v>
       </c>
       <c r="S38" t="n">
-        <v>0.007443781599034274</v>
+        <v>0.007427259195261015</v>
       </c>
       <c r="T38" t="n">
-        <v>0.005311953351493066</v>
+        <v>0.005274645397900988</v>
       </c>
       <c r="U38" t="n">
-        <v>0.002950310153599946</v>
+        <v>0.002918253790409358</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002897694732146856</v>
+        <v>0.002907041900607403</v>
       </c>
       <c r="W38" t="n">
-        <v>0.005044865253352634</v>
+        <v>0.00528189552377787</v>
       </c>
       <c r="X38" t="n">
-        <v>0.01041993151829597</v>
+        <v>0.01038654539914852</v>
       </c>
     </row>
     <row r="39">
@@ -3546,46 +3546,46 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5277031214589124</v>
+        <v>0.5532307663355256</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5262579938715614</v>
+        <v>0.5490907070150366</v>
       </c>
       <c r="M39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.388301465052076</v>
       </c>
       <c r="N39" t="n">
-        <v>4.187296076362964</v>
+        <v>4.357462340729385</v>
       </c>
       <c r="O39" t="n">
-        <v>0.002288722547957887</v>
+        <v>0.002359992589827809</v>
       </c>
       <c r="P39" t="n">
-        <v>0.003384472305631171</v>
+        <v>0.003702430483569739</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001417534797048852</v>
+        <v>0.001457906850969324</v>
       </c>
       <c r="R39" t="n">
-        <v>0.006477719040796281</v>
+        <v>0.00693351776837865</v>
       </c>
       <c r="S39" t="n">
-        <v>0.003213140002428405</v>
+        <v>0.003416305407835117</v>
       </c>
       <c r="T39" t="n">
-        <v>0.004232663474950402</v>
+        <v>0.004281865001445758</v>
       </c>
       <c r="U39" t="n">
-        <v>0.005288704966149901</v>
+        <v>0.005569409119699223</v>
       </c>
       <c r="V39" t="n">
-        <v>0.003173440524355455</v>
+        <v>0.003232027643082421</v>
       </c>
       <c r="W39" t="n">
-        <v>0.008800859635851966</v>
+        <v>0.009725194627759233</v>
       </c>
       <c r="X39" t="n">
-        <v>0.004614275015780799</v>
+        <v>0.004664106411195658</v>
       </c>
     </row>
     <row r="40">
@@ -3626,46 +3626,46 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2903270778508912</v>
+        <v>0.2863667851232301</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5403324737300715</v>
+        <v>0.5271207910217088</v>
       </c>
       <c r="M40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.296817286241648</v>
       </c>
       <c r="N40" t="n">
-        <v>4.620187126003644</v>
+        <v>4.506890140802735</v>
       </c>
       <c r="O40" t="n">
-        <v>0.003319051710264625</v>
+        <v>0.003278728445615086</v>
       </c>
       <c r="P40" t="n">
-        <v>0.003236739920961194</v>
+        <v>0.003089800473342979</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002924370103385985</v>
+        <v>0.002882570328982219</v>
       </c>
       <c r="R40" t="n">
-        <v>0.003097898386283741</v>
+        <v>0.003017740906169194</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08115213048463127</v>
+        <v>0.07807832236119872</v>
       </c>
       <c r="T40" t="n">
-        <v>0.005648526869261323</v>
+        <v>0.005476440935951244</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004954535060444793</v>
+        <v>0.004647382454243626</v>
       </c>
       <c r="V40" t="n">
-        <v>0.004879641105109724</v>
+        <v>0.004806524676509841</v>
       </c>
       <c r="W40" t="n">
-        <v>0.004245663747693837</v>
+        <v>0.004444480063743021</v>
       </c>
       <c r="X40" t="n">
-        <v>0.3992581461973712</v>
+        <v>0.380544158817807</v>
       </c>
     </row>
     <row r="41">
@@ -3706,46 +3706,46 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5262631340488253</v>
+        <v>0.5140482499878872</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5794186057778576</v>
+        <v>0.564414113880731</v>
       </c>
       <c r="M41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.40576475719459</v>
       </c>
       <c r="N41" t="n">
-        <v>4.614881185173552</v>
+        <v>4.493856779888718</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001421043565691609</v>
+        <v>0.001391656400926803</v>
       </c>
       <c r="P41" t="n">
-        <v>0.004666460301058674</v>
+        <v>0.004399313255137251</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.001372345630219622</v>
+        <v>0.001352162448147057</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001674336180520944</v>
+        <v>0.001596940527065349</v>
       </c>
       <c r="S41" t="n">
-        <v>0.007521377754649392</v>
+        <v>0.007221881731744752</v>
       </c>
       <c r="T41" t="n">
-        <v>0.002760299986407524</v>
+        <v>0.002651866114864359</v>
       </c>
       <c r="U41" t="n">
-        <v>0.006805787790750179</v>
+        <v>0.006451431272536002</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002588691178315544</v>
+        <v>0.002558933698549424</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002981284952420999</v>
+        <v>0.003099542075719755</v>
       </c>
       <c r="X41" t="n">
-        <v>0.01233594271569205</v>
+        <v>0.01186187215043931</v>
       </c>
     </row>
     <row r="42">
@@ -3786,46 +3786,46 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2810853425074218</v>
+        <v>0.3386526589655819</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5486911150403546</v>
+        <v>0.5342163589279788</v>
       </c>
       <c r="M42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.440464077287422</v>
       </c>
       <c r="N42" t="n">
-        <v>4.609690643626391</v>
+        <v>4.46843664188295</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004404776530890076</v>
+        <v>0.004281516471129437</v>
       </c>
       <c r="P42" t="n">
-        <v>0.00555477995241522</v>
+        <v>0.005214135917475113</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.004763908474776341</v>
+        <v>0.004670009338758509</v>
       </c>
       <c r="R42" t="n">
-        <v>0.004131570033817271</v>
+        <v>0.004021796853162577</v>
       </c>
       <c r="S42" t="n">
-        <v>0.09904374777527893</v>
+        <v>0.01132450225667985</v>
       </c>
       <c r="T42" t="n">
-        <v>0.0139483673403741</v>
+        <v>0.02774871723951278</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0401996951136813</v>
+        <v>0.1631452017061719</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01401374586530928</v>
+        <v>0.02913625638316486</v>
       </c>
       <c r="W42" t="n">
-        <v>0.01893402203832082</v>
+        <v>0.03825790635323686</v>
       </c>
       <c r="X42" t="n">
-        <v>41.43130655802128</v>
+        <v>3024.05788914925</v>
       </c>
     </row>
     <row r="43">
@@ -3866,46 +3866,46 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2594834876018521</v>
+        <v>0.2608254166930639</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4907148305868094</v>
+        <v>0.500792154886424</v>
       </c>
       <c r="M43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.977480086284531</v>
       </c>
       <c r="N43" t="n">
-        <v>4.235539055160632</v>
+        <v>4.303832950344297</v>
       </c>
       <c r="O43" t="n">
-        <v>0.01850666607496584</v>
+        <v>0.01874586278938806</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01344009307524385</v>
+        <v>0.01372248228968801</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.02002508928196374</v>
+        <v>0.0202453029478202</v>
       </c>
       <c r="R43" t="n">
-        <v>0.03408886976717256</v>
+        <v>0.03502886687088413</v>
       </c>
       <c r="S43" t="n">
-        <v>0.07175161304579468</v>
+        <v>0.07390886488689426</v>
       </c>
       <c r="T43" t="n">
-        <v>0.03361791729122338</v>
+        <v>0.03354842024453984</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02079666011529407</v>
+        <v>0.02232218124113033</v>
       </c>
       <c r="V43" t="n">
-        <v>0.03988752028582222</v>
+        <v>0.04036131334519136</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04208377096732457</v>
+        <v>0.04755366154509751</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1937319677701671</v>
+        <v>0.2016356741055982</v>
       </c>
     </row>
     <row r="44">
@@ -3946,46 +3946,46 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5457327389361865</v>
+        <v>0.5286870787682787</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5769789472562354</v>
+        <v>0.5601500753340829</v>
       </c>
       <c r="M44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.205406969984286</v>
       </c>
       <c r="N44" t="n">
-        <v>4.565090318592861</v>
+        <v>4.439811321784974</v>
       </c>
       <c r="O44" t="n">
-        <v>0.03352763048811068</v>
+        <v>0.03271704029141038</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02584628445381838</v>
+        <v>0.02441717894133158</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02265024210943484</v>
+        <v>0.02212281777374925</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02415279344858706</v>
+        <v>0.02308496603318283</v>
       </c>
       <c r="S44" t="n">
-        <v>0.05610706614681554</v>
+        <v>0.05343111858940566</v>
       </c>
       <c r="T44" t="n">
-        <v>0.06612278982813204</v>
+        <v>0.06370462302804071</v>
       </c>
       <c r="U44" t="n">
-        <v>0.03449176267519351</v>
+        <v>0.03180317974153177</v>
       </c>
       <c r="V44" t="n">
-        <v>0.04409701830178416</v>
+        <v>0.0430702891490072</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02779484718510984</v>
+        <v>0.02966094837093374</v>
       </c>
       <c r="X44" t="n">
-        <v>0.09409279849173041</v>
+        <v>0.08761204451491394</v>
       </c>
     </row>
     <row r="45">
@@ -4026,46 +4026,46 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.534591615256344</v>
+        <v>0.5400703130547023</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5478844266035466</v>
+        <v>0.5561626704094714</v>
       </c>
       <c r="M45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.290254436529441</v>
       </c>
       <c r="N45" t="n">
-        <v>4.348475448935595</v>
+        <v>4.410136618536906</v>
       </c>
       <c r="O45" t="n">
-        <v>0.09450347961146743</v>
+        <v>0.09555035461627759</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1226321488828774</v>
+        <v>0.1250915914571251</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.07248060991669485</v>
+        <v>0.07358513998912945</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1570763416174678</v>
+        <v>0.1603984936262677</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1936130798499568</v>
+        <v>0.1985422221337302</v>
       </c>
       <c r="T45" t="n">
-        <v>0.3341901326130188</v>
+        <v>0.3285839385364094</v>
       </c>
       <c r="U45" t="n">
-        <v>0.3679926259337881</v>
+        <v>0.368312342267658</v>
       </c>
       <c r="V45" t="n">
-        <v>0.172007863370118</v>
+        <v>0.1741461302697716</v>
       </c>
       <c r="W45" t="n">
-        <v>0.3704019940661787</v>
+        <v>0.4181644161022353</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7967336009019138</v>
+        <v>0.8008581742231349</v>
       </c>
     </row>
     <row r="46">
@@ -4106,46 +4106,46 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5306468072560714</v>
+        <v>0.4692195827002179</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5749965907415264</v>
+        <v>0.5639226084278881</v>
       </c>
       <c r="M46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.761450846446995</v>
       </c>
       <c r="N46" t="n">
-        <v>4.550344462455924</v>
+        <v>4.467884158084563</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06417524996116057</v>
+        <v>0.06328472078645837</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04677167949957709</v>
+        <v>0.04462164018410317</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03373787257444599</v>
+        <v>0.03204109986727702</v>
       </c>
       <c r="R46" t="n">
-        <v>0.05442019856002701</v>
+        <v>0.05109896705719571</v>
       </c>
       <c r="S46" t="n">
-        <v>0.2399778703200004</v>
+        <v>0.2440606428421472</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1635538696993637</v>
+        <v>0.1600066093206869</v>
       </c>
       <c r="U46" t="n">
-        <v>0.09166812924930819</v>
+        <v>0.08553689371680227</v>
       </c>
       <c r="V46" t="n">
-        <v>0.05016548654095149</v>
+        <v>0.04752251098581024</v>
       </c>
       <c r="W46" t="n">
-        <v>0.07693191528818039</v>
+        <v>0.07980915958113927</v>
       </c>
       <c r="X46" t="n">
-        <v>2.624839357983597</v>
+        <v>2.891900819193784</v>
       </c>
     </row>
     <row r="47">
@@ -4186,46 +4186,46 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5362846783319638</v>
+        <v>0.5376530400040005</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5493008162785327</v>
+        <v>0.5539463945344929</v>
       </c>
       <c r="M47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.272240003116125</v>
       </c>
       <c r="N47" t="n">
-        <v>4.359025029585109</v>
+        <v>4.393626783533189</v>
       </c>
       <c r="O47" t="n">
-        <v>0.02600544390372821</v>
+        <v>0.02629568054123893</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02027648752807924</v>
+        <v>0.02041470948493697</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02382098072699201</v>
+        <v>0.02389137395773333</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03253065815016812</v>
+        <v>0.03290551379086816</v>
       </c>
       <c r="S47" t="n">
-        <v>0.04860640436374226</v>
+        <v>0.04923244189691206</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04809089035665425</v>
+        <v>0.04780522201779444</v>
       </c>
       <c r="U47" t="n">
-        <v>0.0286043304491383</v>
+        <v>0.02798146392183112</v>
       </c>
       <c r="V47" t="n">
-        <v>0.0471868344320063</v>
+        <v>0.04733699667129609</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03549279168550291</v>
+        <v>0.03885331549029692</v>
       </c>
       <c r="X47" t="n">
-        <v>0.06162519097897144</v>
+        <v>0.06008300019995178</v>
       </c>
     </row>
     <row r="48">
@@ -4266,46 +4266,46 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5133086615075061</v>
+        <v>0.4047097120777118</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5306029283864057</v>
+        <v>0.5472509420816788</v>
       </c>
       <c r="M48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.278188650913639</v>
       </c>
       <c r="N48" t="n">
-        <v>4.219688687799472</v>
+        <v>4.343715651178799</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02646357961734834</v>
+        <v>0.02657723951613876</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05209989820319633</v>
+        <v>0.05274552791758433</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.04241082495231999</v>
+        <v>0.04243709189823286</v>
       </c>
       <c r="R48" t="n">
-        <v>0.08775440064513364</v>
+        <v>0.08900288061287753</v>
       </c>
       <c r="S48" t="n">
-        <v>0.3251100494438319</v>
+        <v>0.4372374145354189</v>
       </c>
       <c r="T48" t="n">
-        <v>0.0492095207243711</v>
+        <v>0.04810971543351892</v>
       </c>
       <c r="U48" t="n">
-        <v>0.08848120805739318</v>
+        <v>0.08841556091310868</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1014302703953202</v>
+        <v>0.1013494155246297</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08955088883736723</v>
+        <v>0.09393475410431229</v>
       </c>
       <c r="X48" t="n">
-        <v>5.996544397888185</v>
+        <v>10.59535791972128</v>
       </c>
     </row>
     <row r="49">
@@ -4346,46 +4346,46 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3582154952860752</v>
+        <v>0.3632462737432927</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5415053287432804</v>
+        <v>0.544970517889401</v>
       </c>
       <c r="M49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.068731139454012</v>
       </c>
       <c r="N49" t="n">
-        <v>4.405696155644946</v>
+        <v>4.413023442429037</v>
       </c>
       <c r="O49" t="n">
-        <v>0.02019428570755797</v>
+        <v>0.01994479468519353</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01184533456356174</v>
+        <v>0.01201849925632891</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01882195601746443</v>
+        <v>0.01883590216196246</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02419512783952734</v>
+        <v>0.0246997340023753</v>
       </c>
       <c r="S49" t="n">
-        <v>0.1119178300630544</v>
+        <v>0.1102549096656836</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03620778933419385</v>
+        <v>0.03501566541640557</v>
       </c>
       <c r="U49" t="n">
-        <v>0.0182409899047891</v>
+        <v>0.01799052030069824</v>
       </c>
       <c r="V49" t="n">
-        <v>0.03408345656064628</v>
+        <v>0.03399911443141951</v>
       </c>
       <c r="W49" t="n">
-        <v>0.03207280745129766</v>
+        <v>0.03523731116959425</v>
       </c>
       <c r="X49" t="n">
-        <v>0.414878835128362</v>
+        <v>0.4014669031282085</v>
       </c>
     </row>
     <row r="50">
@@ -4426,46 +4426,46 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5532153165827609</v>
+        <v>0.5409958952894117</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5853025666772579</v>
+        <v>0.5609105796056079</v>
       </c>
       <c r="M50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.297151770118207</v>
       </c>
       <c r="N50" t="n">
-        <v>4.627033791047181</v>
+        <v>4.445470385809243</v>
       </c>
       <c r="O50" t="n">
-        <v>0.06412561245614468</v>
+        <v>0.06486606026164178</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06734873133967131</v>
+        <v>0.06452410122925463</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06834154792754898</v>
+        <v>0.06516623177053395</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03812362395138322</v>
+        <v>0.03600624296411507</v>
       </c>
       <c r="S50" t="n">
-        <v>0.03794765455997967</v>
+        <v>0.01136839625712979</v>
       </c>
       <c r="T50" t="n">
-        <v>0.164035677268003</v>
+        <v>0.2270018663367448</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1164936324131352</v>
+        <v>0.2636069185885194</v>
       </c>
       <c r="V50" t="n">
-        <v>0.1199580347506689</v>
+        <v>0.2679372505169348</v>
       </c>
       <c r="W50" t="n">
-        <v>0.05448751524278343</v>
+        <v>0.1611465545386548</v>
       </c>
       <c r="X50" t="n">
-        <v>0.2051997841465424</v>
+        <v>14.3064493284135</v>
       </c>
     </row>
     <row r="51">
@@ -4506,46 +4506,46 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5293227205179547</v>
+        <v>0.4812086802605804</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5585943188815895</v>
+        <v>0.5588663612374861</v>
       </c>
       <c r="M51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.851059526098112</v>
       </c>
       <c r="N51" t="n">
-        <v>4.428243175548054</v>
+        <v>4.430252432167871</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05618015848064754</v>
+        <v>0.05474557304944666</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04342589532334352</v>
+        <v>0.04139987088441678</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1341382672215114</v>
+        <v>0.1289472612832484</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06672214395999347</v>
+        <v>0.06407570240233228</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1959101027517867</v>
+        <v>0.2179871846332974</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1396622376986278</v>
+        <v>0.1326478479834944</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08942006851060111</v>
+        <v>0.08255978716328416</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2416922220275962</v>
+        <v>0.2293256315720723</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1132155258783172</v>
+        <v>0.1199481010574502</v>
       </c>
       <c r="X51" t="n">
-        <v>1.793880449754884</v>
+        <v>2.408586938743106</v>
       </c>
     </row>
     <row r="52">
@@ -4586,46 +4586,46 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5458032169079876</v>
+        <v>0.5429836066241071</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5563059674706922</v>
+        <v>0.5519919379474244</v>
       </c>
       <c r="M52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.311963123218198</v>
       </c>
       <c r="N52" t="n">
-        <v>4.411201416360191</v>
+        <v>4.379070425761204</v>
       </c>
       <c r="O52" t="n">
-        <v>0.0106657879605282</v>
+        <v>0.01056980021685694</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0102691716327522</v>
+        <v>0.01011734337544687</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.01121306496217154</v>
+        <v>0.01115439287387856</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01285270707489839</v>
+        <v>0.01267777671203137</v>
       </c>
       <c r="S52" t="n">
-        <v>0.05317779636993288</v>
+        <v>0.05214676690899978</v>
       </c>
       <c r="T52" t="n">
-        <v>0.01831863295597363</v>
+        <v>0.01781992051110715</v>
       </c>
       <c r="U52" t="n">
-        <v>0.01435017847670419</v>
+        <v>0.01393050101495484</v>
       </c>
       <c r="V52" t="n">
-        <v>0.02017553612289931</v>
+        <v>0.02010213452782804</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01825564001090401</v>
+        <v>0.01949607486565501</v>
       </c>
       <c r="X52" t="n">
-        <v>0.08838550106424263</v>
+        <v>0.08528346792340756</v>
       </c>
     </row>
     <row r="53">
@@ -4666,46 +4666,46 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.492274680908048</v>
+        <v>0.4961096498617924</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5481530882022807</v>
+        <v>0.5569397584495432</v>
       </c>
       <c r="M53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.490422673838463</v>
       </c>
       <c r="N53" t="n">
-        <v>4.363437608643186</v>
+        <v>4.431904863413439</v>
       </c>
       <c r="O53" t="n">
-        <v>0.02261851632975782</v>
+        <v>0.02301682853957677</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02058262221795309</v>
+        <v>0.02115848481187217</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01434550357901415</v>
+        <v>0.01454550754735299</v>
       </c>
       <c r="R53" t="n">
-        <v>0.03908051719083647</v>
+        <v>0.03992718198825528</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1856614112853763</v>
+        <v>0.1920175385278811</v>
       </c>
       <c r="T53" t="n">
-        <v>0.04024414857063218</v>
+        <v>0.0400030918988551</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03000689310516569</v>
+        <v>0.02977304511028818</v>
       </c>
       <c r="V53" t="n">
-        <v>0.02279752416249341</v>
+        <v>0.02298465081135883</v>
       </c>
       <c r="W53" t="n">
-        <v>0.05509669075918949</v>
+        <v>0.05966659762148636</v>
       </c>
       <c r="X53" t="n">
-        <v>0.2266475535597333</v>
+        <v>0.2197006054314774</v>
       </c>
     </row>
     <row r="54">
@@ -4746,46 +4746,46 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.332316906027442</v>
+        <v>0.3258000977721076</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5425566809702975</v>
+        <v>0.5287898826449937</v>
       </c>
       <c r="M54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.139890418693176</v>
       </c>
       <c r="N54" t="n">
-        <v>4.473767057560834</v>
+        <v>4.361117336283419</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02403571760625988</v>
+        <v>0.02351676465159932</v>
       </c>
       <c r="P54" t="n">
-        <v>0.01069640953895437</v>
+        <v>0.01024406127602647</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02210626266966435</v>
+        <v>0.02179658485958028</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01468377606673288</v>
+        <v>0.01414296212851437</v>
       </c>
       <c r="S54" t="n">
-        <v>0.03333630098238007</v>
+        <v>0.03220731123326998</v>
       </c>
       <c r="T54" t="n">
-        <v>0.04497047281170433</v>
+        <v>0.04386528010369108</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01975885207454693</v>
+        <v>0.01796933988212004</v>
       </c>
       <c r="V54" t="n">
-        <v>0.04503433473419276</v>
+        <v>0.04456338969903082</v>
       </c>
       <c r="W54" t="n">
-        <v>0.02148564817917462</v>
+        <v>0.02145308495291094</v>
       </c>
       <c r="X54" t="n">
-        <v>0.0596618945113834</v>
+        <v>0.05650877433197121</v>
       </c>
     </row>
     <row r="55">
@@ -4826,46 +4826,46 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3199361685503805</v>
+        <v>0.3243733482653745</v>
       </c>
       <c r="L55" t="n">
-        <v>0.514956557862417</v>
+        <v>0.5207697334533022</v>
       </c>
       <c r="M55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.37343702145688</v>
       </c>
       <c r="N55" t="n">
-        <v>4.368348640241867</v>
+        <v>4.410295015553443</v>
       </c>
       <c r="O55" t="n">
-        <v>0.01697402724442464</v>
+        <v>0.01691980388186572</v>
       </c>
       <c r="P55" t="n">
-        <v>0.00964967147541641</v>
+        <v>0.009810806694572734</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.01826957600088539</v>
+        <v>0.01825446804135301</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01753998959925198</v>
+        <v>0.01786748179534087</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01930481788665805</v>
+        <v>0.01973821326632086</v>
       </c>
       <c r="T55" t="n">
-        <v>0.03014007654390603</v>
+        <v>0.02948921313147662</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01439070112678796</v>
+        <v>0.01461432315198538</v>
       </c>
       <c r="V55" t="n">
-        <v>0.03729702723620697</v>
+        <v>0.03712189866780809</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02170320625244218</v>
+        <v>0.02353727611921678</v>
       </c>
       <c r="X55" t="n">
-        <v>0.0286948143202994</v>
+        <v>0.0289465985119338</v>
       </c>
     </row>
     <row r="56">
@@ -4906,46 +4906,46 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5336789504017783</v>
+        <v>0.5097180810386136</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5484738829635747</v>
+        <v>0.5521349186700187</v>
       </c>
       <c r="M56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.063927352245716</v>
       </c>
       <c r="N56" t="n">
-        <v>4.352865751652848</v>
+        <v>4.380121791248679</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01783053422771821</v>
+        <v>0.01788283889818332</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01349403809284323</v>
+        <v>0.01340615818860914</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01475779474150362</v>
+        <v>0.01476816841035354</v>
       </c>
       <c r="R56" t="n">
-        <v>0.02568525103528024</v>
+        <v>0.02550269428741145</v>
       </c>
       <c r="S56" t="n">
-        <v>0.05728985021655331</v>
+        <v>0.05919001245145147</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0319921324385691</v>
+        <v>0.03154746106001149</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01905856187172331</v>
+        <v>0.01852511120146979</v>
       </c>
       <c r="V56" t="n">
-        <v>0.02740173242026793</v>
+        <v>0.02751403081654895</v>
       </c>
       <c r="W56" t="n">
-        <v>0.03263405250081356</v>
+        <v>0.03508856474236026</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1352503229545302</v>
+        <v>0.1402670044442715</v>
       </c>
     </row>
     <row r="57">
@@ -4986,46 +4986,46 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5416026416533484</v>
+        <v>0.5362984060044483</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5547665835679128</v>
+        <v>0.5545372151083801</v>
       </c>
       <c r="M57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.26214400069415</v>
       </c>
       <c r="N57" t="n">
-        <v>4.399737079731637</v>
+        <v>4.398024514826248</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02314460308555983</v>
+        <v>0.02335415796389578</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01066407993328903</v>
+        <v>0.01055041984585022</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01754600665077942</v>
+        <v>0.01749190118172447</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01875719173606427</v>
+        <v>0.01872592063907398</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02955662392871635</v>
+        <v>0.02947005120761005</v>
       </c>
       <c r="T57" t="n">
-        <v>0.04442974561755129</v>
+        <v>0.0443214406298665</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01621912638907154</v>
+        <v>0.01564946283566307</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03073887437887447</v>
+        <v>0.03067597931135057</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02281391489101722</v>
+        <v>0.02492786669493469</v>
       </c>
       <c r="X57" t="n">
-        <v>0.04230166827007783</v>
+        <v>0.04086461391742603</v>
       </c>
     </row>
     <row r="58">
@@ -5066,46 +5066,46 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2467965400229046</v>
+        <v>0.2359136518339272</v>
       </c>
       <c r="L58" t="n">
-        <v>0.552107838367995</v>
+        <v>0.5333513553544688</v>
       </c>
       <c r="M58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.091754229257946</v>
       </c>
       <c r="N58" t="n">
-        <v>4.742237275313982</v>
+        <v>4.428503233920229</v>
       </c>
       <c r="O58" t="n">
-        <v>0.04203478343571768</v>
+        <v>0.04113720345944752</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0129010015148132</v>
+        <v>0.01201190955085237</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.04090526414815391</v>
+        <v>0.04028031210337838</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01119594831231248</v>
+        <v>0.01041512724948527</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05492331076098093</v>
+        <v>0.0527906051136479</v>
       </c>
       <c r="T58" t="n">
-        <v>0.0335291006644494</v>
+        <v>0.09064664076817713</v>
       </c>
       <c r="U58" t="n">
-        <v>0.03385360691073735</v>
+        <v>0.02182126136206662</v>
       </c>
       <c r="V58" t="n">
-        <v>0.09998470566671014</v>
+        <v>0.09571734328003741</v>
       </c>
       <c r="W58" t="n">
-        <v>0.03349270599450786</v>
+        <v>0.02046337714861655</v>
       </c>
       <c r="X58" t="n">
-        <v>0.1353455006857162</v>
+        <v>0.1140005831565476</v>
       </c>
     </row>
     <row r="59">
@@ -5146,46 +5146,46 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5318362786808796</v>
+        <v>0.5293059348727757</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5523174300335125</v>
+        <v>0.5538338158486154</v>
       </c>
       <c r="M59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.210020762317669</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3814919243668</v>
+        <v>4.392782555440949</v>
       </c>
       <c r="O59" t="n">
-        <v>0.009994546307583814</v>
+        <v>0.01029833608232163</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004599870371277528</v>
+        <v>0.004539144323541964</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.008679565560645261</v>
+        <v>0.008650096836568687</v>
       </c>
       <c r="R59" t="n">
-        <v>0.007089957545603024</v>
+        <v>0.007098065092985744</v>
       </c>
       <c r="S59" t="n">
-        <v>0.008226302319105592</v>
+        <v>0.00822416294863002</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01622907177372473</v>
+        <v>0.01676074210330156</v>
       </c>
       <c r="U59" t="n">
-        <v>0.00574452079546865</v>
+        <v>0.005541944152225409</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01148373266078529</v>
+        <v>0.01143190424185291</v>
       </c>
       <c r="W59" t="n">
-        <v>0.006119439908754886</v>
+        <v>0.006676033978372371</v>
       </c>
       <c r="X59" t="n">
-        <v>0.00769649231244182</v>
+        <v>0.007331851313612147</v>
       </c>
     </row>
     <row r="60">
@@ -5226,46 +5226,46 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.525362947003733</v>
+        <v>0.520091897588902</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5397044654616852</v>
+        <v>0.5420607107055893</v>
       </c>
       <c r="M60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.141314459674549</v>
       </c>
       <c r="N60" t="n">
-        <v>4.287522373130157</v>
+        <v>4.30507491140169</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002672053249578549</v>
+        <v>0.002688510826234986</v>
       </c>
       <c r="P60" t="n">
-        <v>0.004429658019814849</v>
+        <v>0.004443635269329842</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001399321440583378</v>
+        <v>0.001399026473855564</v>
       </c>
       <c r="R60" t="n">
-        <v>0.004573453661146017</v>
+        <v>0.004570396915047842</v>
       </c>
       <c r="S60" t="n">
-        <v>0.008715767187239086</v>
+        <v>0.00879421067319191</v>
       </c>
       <c r="T60" t="n">
-        <v>0.003877522273468987</v>
+        <v>0.003856969144677906</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005347733255687183</v>
+        <v>0.005279303190128591</v>
       </c>
       <c r="V60" t="n">
-        <v>0.002230253580100608</v>
+        <v>0.002241673457764175</v>
       </c>
       <c r="W60" t="n">
-        <v>0.00490994929340449</v>
+        <v>0.005061016126528004</v>
       </c>
       <c r="X60" t="n">
-        <v>0.009848154690333708</v>
+        <v>0.009739714992418713</v>
       </c>
     </row>
     <row r="61">
@@ -5306,46 +5306,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4188133248307595</v>
+        <v>0.4276854726398666</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5246518864938392</v>
+        <v>0.5395379223645458</v>
       </c>
       <c r="M61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.964762310542818</v>
       </c>
       <c r="N61" t="n">
-        <v>4.200071136247483</v>
+        <v>4.304599680755931</v>
       </c>
       <c r="O61" t="n">
-        <v>0.005829135870519695</v>
+        <v>0.005887735743405191</v>
       </c>
       <c r="P61" t="n">
-        <v>0.008520144983286571</v>
+        <v>0.008942872273152736</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.003278529318087234</v>
+        <v>0.003397250813141699</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01839508971830805</v>
+        <v>0.01928900163698361</v>
       </c>
       <c r="S61" t="n">
-        <v>0.03810909286333825</v>
+        <v>0.03909610157582086</v>
       </c>
       <c r="T61" t="n">
-        <v>0.008059808072095501</v>
+        <v>0.00802721393766803</v>
       </c>
       <c r="U61" t="n">
-        <v>0.00984013687932698</v>
+        <v>0.01015982028744835</v>
       </c>
       <c r="V61" t="n">
-        <v>0.004050198345354438</v>
+        <v>0.004169802449378564</v>
       </c>
       <c r="W61" t="n">
-        <v>0.01556202868475484</v>
+        <v>0.01662024494803216</v>
       </c>
       <c r="X61" t="n">
-        <v>0.1530781740703197</v>
+        <v>0.1551983915692233</v>
       </c>
     </row>
     <row r="62">
@@ -5386,46 +5386,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1552434129439603</v>
+        <v>0.1560475317581405</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4431745598291147</v>
+        <v>0.4558713548482391</v>
       </c>
       <c r="M62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.22633178824696</v>
       </c>
       <c r="N62" t="n">
-        <v>4.144021638062128</v>
+        <v>4.265155680872917</v>
       </c>
       <c r="O62" t="n">
-        <v>0.006598627384834347</v>
+        <v>0.006638142889749127</v>
       </c>
       <c r="P62" t="n">
-        <v>0.003718164461488481</v>
+        <v>0.003780264533255319</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.00285855261817197</v>
+        <v>0.002891888951502434</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01664447615212956</v>
+        <v>0.01708510409172775</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01046991135716146</v>
+        <v>0.01055620094165153</v>
       </c>
       <c r="T62" t="n">
-        <v>0.01001854228320157</v>
+        <v>0.01001929893170729</v>
       </c>
       <c r="U62" t="n">
-        <v>0.007594806738111986</v>
+        <v>0.007964224673806039</v>
       </c>
       <c r="V62" t="n">
-        <v>0.004394200526819112</v>
+        <v>0.004498590127782346</v>
       </c>
       <c r="W62" t="n">
-        <v>0.03206343649467776</v>
+        <v>0.03397355668983816</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02217785956809635</v>
+        <v>0.02236573402603507</v>
       </c>
     </row>
     <row r="63">
@@ -5466,46 +5466,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3646171913311278</v>
+        <v>0.3712793451295304</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5157145868883104</v>
+        <v>0.5283584391795361</v>
       </c>
       <c r="M63" t="n">
-        <v>4.076109010387499</v>
+        <v>4.032785542367162</v>
       </c>
       <c r="N63" t="n">
-        <v>4.206136226674591</v>
+        <v>4.294852238078497</v>
       </c>
       <c r="O63" t="n">
-        <v>0.005481933009596805</v>
+        <v>0.005537805848895896</v>
       </c>
       <c r="P63" t="n">
-        <v>0.007180340805830223</v>
+        <v>0.0074515843057457</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002881240956826246</v>
+        <v>0.002958696488616361</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01422234309132572</v>
+        <v>0.01478289595286687</v>
       </c>
       <c r="S63" t="n">
-        <v>0.02197702721401216</v>
+        <v>0.02259216607375159</v>
       </c>
       <c r="T63" t="n">
-        <v>0.007754670666062028</v>
+        <v>0.007720608479823516</v>
       </c>
       <c r="U63" t="n">
-        <v>0.009099264787840971</v>
+        <v>0.00927061440870936</v>
       </c>
       <c r="V63" t="n">
-        <v>0.00367385904890648</v>
+        <v>0.003736957256765788</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01555184994719413</v>
+        <v>0.01597877252799531</v>
       </c>
       <c r="X63" t="n">
-        <v>0.04379166165561935</v>
+        <v>0.04657832162947657</v>
       </c>
     </row>
     <row r="64">
@@ -5546,46 +5546,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.261923789223986</v>
+        <v>0.2665008022242393</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5081096848617053</v>
+        <v>0.5274523951771934</v>
       </c>
       <c r="M64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.919470058378178</v>
       </c>
       <c r="N64" t="n">
-        <v>4.163063139756337</v>
+        <v>4.306337359755369</v>
       </c>
       <c r="O64" t="n">
-        <v>0.006285689177285431</v>
+        <v>0.006395490511863943</v>
       </c>
       <c r="P64" t="n">
-        <v>0.007050895856707503</v>
+        <v>0.007488293781800744</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.00433532796639125</v>
+        <v>0.004500634074302134</v>
       </c>
       <c r="R64" t="n">
-        <v>0.02751807644902432</v>
+        <v>0.02912685718544783</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05472469484490124</v>
+        <v>0.05592572937046784</v>
       </c>
       <c r="T64" t="n">
-        <v>0.009213789052074916</v>
+        <v>0.009248048119828248</v>
       </c>
       <c r="U64" t="n">
-        <v>0.008993049027153907</v>
+        <v>0.00963734871858862</v>
       </c>
       <c r="V64" t="n">
-        <v>0.005647707306717557</v>
+        <v>0.005837296435730784</v>
       </c>
       <c r="W64" t="n">
-        <v>0.04147535547906574</v>
+        <v>0.04527266360736645</v>
       </c>
       <c r="X64" t="n">
-        <v>0.5843043207350614</v>
+        <v>0.5741383341736978</v>
       </c>
     </row>
     <row r="65">
@@ -5626,46 +5626,46 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.363558395025915</v>
+        <v>0.3705977767793169</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5216302156996953</v>
+        <v>0.5347479820993566</v>
       </c>
       <c r="M65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.919437140445244</v>
       </c>
       <c r="N65" t="n">
-        <v>4.223984919061119</v>
+        <v>4.312903676909155</v>
       </c>
       <c r="O65" t="n">
-        <v>0.006501084962515054</v>
+        <v>0.006567038489902901</v>
       </c>
       <c r="P65" t="n">
-        <v>0.008923315420353468</v>
+        <v>0.009291301484505837</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.004932950012372037</v>
+        <v>0.005059207543341328</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01655215598645542</v>
+        <v>0.01725338998781449</v>
       </c>
       <c r="S65" t="n">
-        <v>0.04311832724133696</v>
+        <v>0.04457595703917552</v>
       </c>
       <c r="T65" t="n">
-        <v>0.009308811720398984</v>
+        <v>0.009263724505047598</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01132760704549922</v>
+        <v>0.01193624110781811</v>
       </c>
       <c r="V65" t="n">
-        <v>0.006390685986826241</v>
+        <v>0.006564081443977254</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01487889266726001</v>
+        <v>0.01627763747729805</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1826965804158812</v>
+        <v>0.1890572140702043</v>
       </c>
     </row>
     <row r="66">
@@ -5706,46 +5706,46 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3066348386477217</v>
+        <v>0.3123846531483918</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5124870335475997</v>
+        <v>0.5312811782261095</v>
       </c>
       <c r="M66" t="n">
-        <v>4.099154174190237</v>
+        <v>4.0372004394865</v>
       </c>
       <c r="N66" t="n">
-        <v>4.17111446203368</v>
+        <v>4.308918207759948</v>
       </c>
       <c r="O66" t="n">
-        <v>0.006303990624982558</v>
+        <v>0.006403456129815127</v>
       </c>
       <c r="P66" t="n">
-        <v>0.007779927625888958</v>
+        <v>0.008276722505966861</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.004368149620713038</v>
+        <v>0.004528767776314647</v>
       </c>
       <c r="R66" t="n">
-        <v>0.02464601923199248</v>
+        <v>0.02604835672299321</v>
       </c>
       <c r="S66" t="n">
-        <v>0.03728314223202914</v>
+        <v>0.038856132840531</v>
       </c>
       <c r="T66" t="n">
-        <v>0.009202982817749075</v>
+        <v>0.00921590487631741</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009617393126879186</v>
+        <v>0.01026551251932469</v>
       </c>
       <c r="V66" t="n">
-        <v>0.005706212216445685</v>
+        <v>0.005890271532821016</v>
       </c>
       <c r="W66" t="n">
-        <v>0.03214055800114358</v>
+        <v>0.034986680189511</v>
       </c>
       <c r="X66" t="n">
-        <v>0.2101327271299019</v>
+        <v>0.2216974876740873</v>
       </c>
     </row>
     <row r="67">
@@ -5786,46 +5786,46 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5363853847768683</v>
+        <v>0.5593936798993145</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5389197202579266</v>
+        <v>0.5511050848074464</v>
       </c>
       <c r="M67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.434199252443003</v>
       </c>
       <c r="N67" t="n">
-        <v>4.281679635280236</v>
+        <v>4.372467773239976</v>
       </c>
       <c r="O67" t="n">
-        <v>0.00553551468216682</v>
+        <v>0.005810294236388103</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01703462419127677</v>
+        <v>0.01807506346061479</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.004272325150137957</v>
+        <v>0.004460983961945137</v>
       </c>
       <c r="R67" t="n">
-        <v>0.01422493265702475</v>
+        <v>0.01478758572647783</v>
       </c>
       <c r="S67" t="n">
-        <v>0.1107302340135657</v>
+        <v>0.1218357413497161</v>
       </c>
       <c r="T67" t="n">
-        <v>0.008737650839662905</v>
+        <v>0.008988584861471633</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01626774690479342</v>
+        <v>0.01645928843055802</v>
       </c>
       <c r="V67" t="n">
-        <v>0.008153527477495467</v>
+        <v>0.0083946894445661</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0167777303451099</v>
+        <v>0.01808809256542971</v>
       </c>
       <c r="X67" t="n">
-        <v>0.1371617472250494</v>
+        <v>0.1492326560758366</v>
       </c>
     </row>
     <row r="68">
@@ -5866,46 +5866,46 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5363853847768683</v>
+        <v>0.5709446758847706</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5296987871847381</v>
+        <v>0.5512229937090362</v>
       </c>
       <c r="M68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.520196890876156</v>
       </c>
       <c r="N68" t="n">
-        <v>4.212949111802428</v>
+        <v>4.37334326431771</v>
       </c>
       <c r="O68" t="n">
-        <v>0.005286958560738319</v>
+        <v>0.00544297808667534</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01861523296903643</v>
+        <v>0.0201237168701102</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004677700543950635</v>
+        <v>0.004907960555246157</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01902800309128292</v>
+        <v>0.01926828959130466</v>
       </c>
       <c r="S68" t="n">
-        <v>0.03041556841056181</v>
+        <v>0.03435910924595399</v>
       </c>
       <c r="T68" t="n">
-        <v>0.00867944749801957</v>
+        <v>0.008974918624448453</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01811684738401906</v>
+        <v>0.01889077044834286</v>
       </c>
       <c r="V68" t="n">
-        <v>0.006941287584889235</v>
+        <v>0.007172022044769497</v>
       </c>
       <c r="W68" t="n">
-        <v>0.02495915945644413</v>
+        <v>0.02531331626586761</v>
       </c>
       <c r="X68" t="n">
-        <v>0.04327424699870755</v>
+        <v>0.04759366034142251</v>
       </c>
     </row>
     <row r="69">
@@ -5946,46 +5946,46 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4141431162653932</v>
+        <v>0.4227647615340945</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5237610409592882</v>
+        <v>0.5373287944473988</v>
       </c>
       <c r="M69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.368894955962674</v>
       </c>
       <c r="N69" t="n">
-        <v>4.265280254383081</v>
+        <v>4.372310551563071</v>
       </c>
       <c r="O69" t="n">
-        <v>0.004582942478869044</v>
+        <v>0.004670762396775427</v>
       </c>
       <c r="P69" t="n">
-        <v>0.006926455132948861</v>
+        <v>0.00727317018686316</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.004410046606588096</v>
+        <v>0.004458407973968088</v>
       </c>
       <c r="R69" t="n">
-        <v>0.008884938970891524</v>
+        <v>0.009195830713596094</v>
       </c>
       <c r="S69" t="n">
-        <v>0.007086014628969762</v>
+        <v>0.007272017115655488</v>
       </c>
       <c r="T69" t="n">
-        <v>0.006199751009259851</v>
+        <v>0.006158766567799165</v>
       </c>
       <c r="U69" t="n">
-        <v>0.008359525796018794</v>
+        <v>0.008909246267713366</v>
       </c>
       <c r="V69" t="n">
-        <v>0.006207354446740131</v>
+        <v>0.00625619934515729</v>
       </c>
       <c r="W69" t="n">
-        <v>0.00933906667507905</v>
+        <v>0.01013636437864746</v>
       </c>
       <c r="X69" t="n">
-        <v>0.009110321610122827</v>
+        <v>0.009042482915033973</v>
       </c>
     </row>
     <row r="70">
@@ -6026,46 +6026,46 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5481989593924306</v>
+        <v>0.5503708566416453</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5512121797110844</v>
+        <v>0.557175866779264</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.366998961487805</v>
       </c>
       <c r="N70" t="n">
-        <v>4.373265808810165</v>
+        <v>4.417682680857455</v>
       </c>
       <c r="O70" t="n">
-        <v>0.005147280777408622</v>
+        <v>0.005197892510978567</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009831345388224694</v>
+        <v>0.009986064107254541</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.006366063098463382</v>
+        <v>0.006403778328533694</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009287991801265976</v>
+        <v>0.009446083806372806</v>
       </c>
       <c r="S70" t="n">
-        <v>0.01208579594795775</v>
+        <v>0.01226053674075214</v>
       </c>
       <c r="T70" t="n">
-        <v>0.006744590946685748</v>
+        <v>0.006627898998414096</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01000647656139668</v>
+        <v>0.01000198339900437</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009210021607879672</v>
+        <v>0.009263447270604658</v>
       </c>
       <c r="W70" t="n">
-        <v>0.009997623536084094</v>
+        <v>0.01102278787193809</v>
       </c>
       <c r="X70" t="n">
-        <v>0.01620063572105224</v>
+        <v>0.01592689177776248</v>
       </c>
     </row>
     <row r="71">
@@ -6106,46 +6106,46 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5103518668467035</v>
+        <v>0.5091634325943012</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5602121933897544</v>
+        <v>0.5595167832296695</v>
       </c>
       <c r="M71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.443210889445625</v>
       </c>
       <c r="N71" t="n">
-        <v>4.455639353156864</v>
+        <v>4.451562041033815</v>
       </c>
       <c r="O71" t="n">
-        <v>0.006877694467616714</v>
+        <v>0.006876278507295617</v>
       </c>
       <c r="P71" t="n">
-        <v>0.01119769670853781</v>
+        <v>0.01116184222329778</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.00597695355416603</v>
+        <v>0.005974497088690771</v>
       </c>
       <c r="R71" t="n">
-        <v>0.008195573462547335</v>
+        <v>0.008187076760039035</v>
       </c>
       <c r="S71" t="n">
-        <v>0.009413805633295521</v>
+        <v>0.009397779318734149</v>
       </c>
       <c r="T71" t="n">
-        <v>0.009203090977226068</v>
+        <v>0.008990604501086238</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01208010749341931</v>
+        <v>0.01134582745677095</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007936639783470119</v>
+        <v>0.007934367505822342</v>
       </c>
       <c r="W71" t="n">
-        <v>0.008752937224132095</v>
+        <v>0.009655708446340495</v>
       </c>
       <c r="X71" t="n">
-        <v>0.009626905164442218</v>
+        <v>0.009190324929476178</v>
       </c>
     </row>
     <row r="72">
@@ -6186,46 +6186,46 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5584922532709602</v>
+        <v>0.5525686244778018</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5760014292602736</v>
+        <v>0.5680789099687878</v>
       </c>
       <c r="M72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.490464158932846</v>
       </c>
       <c r="N72" t="n">
-        <v>4.559763792922564</v>
+        <v>4.500431880349488</v>
       </c>
       <c r="O72" t="n">
-        <v>0.005981568071083244</v>
+        <v>0.005880365508362228</v>
       </c>
       <c r="P72" t="n">
-        <v>0.008564443735425661</v>
+        <v>0.00833042388929766</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.006837182052352841</v>
+        <v>0.006764412505359232</v>
       </c>
       <c r="R72" t="n">
-        <v>0.006399362488397387</v>
+        <v>0.006297990399647873</v>
       </c>
       <c r="S72" t="n">
-        <v>0.009136174139336317</v>
+        <v>0.008934965214403429</v>
       </c>
       <c r="T72" t="n">
-        <v>0.007664742405948189</v>
+        <v>0.007380016180022536</v>
       </c>
       <c r="U72" t="n">
-        <v>0.00866279840392023</v>
+        <v>0.00827478219519682</v>
       </c>
       <c r="V72" t="n">
-        <v>0.009459326005553296</v>
+        <v>0.009367818521080101</v>
       </c>
       <c r="W72" t="n">
-        <v>0.007618205731050499</v>
+        <v>0.008273389077911938</v>
       </c>
       <c r="X72" t="n">
-        <v>0.01024592485242726</v>
+        <v>0.009789025703110863</v>
       </c>
     </row>
     <row r="73">
@@ -6266,46 +6266,46 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5344803546979763</v>
+        <v>0.5594245360474558</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5300942224672476</v>
+        <v>0.5542417089438341</v>
       </c>
       <c r="M73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.434429024992574</v>
       </c>
       <c r="N73" t="n">
-        <v>4.21589678668229</v>
+        <v>4.395830258319456</v>
       </c>
       <c r="O73" t="n">
-        <v>0.002991820898381655</v>
+        <v>0.00311165531131248</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01069661426611113</v>
+        <v>0.01168548851110581</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002517048700918191</v>
+        <v>0.002575281000338605</v>
       </c>
       <c r="R73" t="n">
-        <v>0.009335871737348013</v>
+        <v>0.01010763561941757</v>
       </c>
       <c r="S73" t="n">
-        <v>0.00379131019449085</v>
+        <v>0.004155254204392331</v>
       </c>
       <c r="T73" t="n">
-        <v>0.004741098522568837</v>
+        <v>0.004794608039332855</v>
       </c>
       <c r="U73" t="n">
-        <v>0.01121135003245214</v>
+        <v>0.01195658560655915</v>
       </c>
       <c r="V73" t="n">
-        <v>0.004113614931709593</v>
+        <v>0.004188052880264031</v>
       </c>
       <c r="W73" t="n">
-        <v>0.01044455690846904</v>
+        <v>0.01157681866482518</v>
       </c>
       <c r="X73" t="n">
-        <v>0.00580425388859781</v>
+        <v>0.005866721198758036</v>
       </c>
     </row>
     <row r="74">
@@ -6346,46 +6346,46 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5564885816617008</v>
+        <v>0.5539023206624197</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5628812094550268</v>
+        <v>0.5600764583033748</v>
       </c>
       <c r="M74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.39330331686405</v>
       </c>
       <c r="N74" t="n">
-        <v>4.460283240759831</v>
+        <v>4.439282545417659</v>
       </c>
       <c r="O74" t="n">
-        <v>0.003570424915625856</v>
+        <v>0.003539485399138183</v>
       </c>
       <c r="P74" t="n">
-        <v>0.009560485086765821</v>
+        <v>0.009459346724213735</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003953676350101971</v>
+        <v>0.003942887401724333</v>
       </c>
       <c r="R74" t="n">
-        <v>0.005302128935595433</v>
+        <v>0.005261283744490171</v>
       </c>
       <c r="S74" t="n">
-        <v>0.00764928771372369</v>
+        <v>0.007590543917671987</v>
       </c>
       <c r="T74" t="n">
-        <v>0.005191802905106436</v>
+        <v>0.005069254413929998</v>
       </c>
       <c r="U74" t="n">
-        <v>0.00927134709897875</v>
+        <v>0.009201447473960093</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005828867272934125</v>
+        <v>0.005810979187408047</v>
       </c>
       <c r="W74" t="n">
-        <v>0.006384925990497153</v>
+        <v>0.006881547076612756</v>
       </c>
       <c r="X74" t="n">
-        <v>0.009444701165725249</v>
+        <v>0.009132946016990691</v>
       </c>
     </row>
     <row r="75">
@@ -6426,46 +6426,46 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5349426521273756</v>
+        <v>0.5371232694513625</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5414132738646801</v>
+        <v>0.5502940645259519</v>
       </c>
       <c r="M75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.268291721388134</v>
       </c>
       <c r="N75" t="n">
-        <v>4.300261186124661</v>
+        <v>4.366423447898454</v>
       </c>
       <c r="O75" t="n">
-        <v>0.004334969300107086</v>
+        <v>0.00439309765914696</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01002284179844473</v>
+        <v>0.01026514405593301</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004863265894900297</v>
+        <v>0.004907746701731233</v>
       </c>
       <c r="R75" t="n">
-        <v>0.00931973171907283</v>
+        <v>0.009513237997438131</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01050163067717712</v>
+        <v>0.01069227173459293</v>
       </c>
       <c r="T75" t="n">
-        <v>0.006041500642300778</v>
+        <v>0.005999087667311785</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01023343041722765</v>
+        <v>0.01037288258797529</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006787340551238159</v>
+        <v>0.006861234173145976</v>
       </c>
       <c r="W75" t="n">
-        <v>0.01025072226024404</v>
+        <v>0.01130364763349416</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01524947279348582</v>
+        <v>0.01507697132009915</v>
       </c>
     </row>
     <row r="76">
@@ -6506,46 +6506,46 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5259650027132445</v>
+        <v>0.543770931818184</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5299531701082921</v>
+        <v>0.5538113906052184</v>
       </c>
       <c r="M76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.439776253946184</v>
       </c>
       <c r="N76" t="n">
-        <v>4.215789973162262</v>
+        <v>4.395512032867538</v>
       </c>
       <c r="O76" t="n">
-        <v>0.003599402503095812</v>
+        <v>0.00376515086459863</v>
       </c>
       <c r="P76" t="n">
-        <v>0.008788712947667671</v>
+        <v>0.009554323552334621</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002404702271314053</v>
+        <v>0.002443056166938659</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01048424049968593</v>
+        <v>0.01133257225905577</v>
       </c>
       <c r="S76" t="n">
-        <v>0.003520744828808937</v>
+        <v>0.003795502052632326</v>
       </c>
       <c r="T76" t="n">
-        <v>0.005240764161328616</v>
+        <v>0.005318788553107376</v>
       </c>
       <c r="U76" t="n">
-        <v>0.009150312498470928</v>
+        <v>0.01000660700825819</v>
       </c>
       <c r="V76" t="n">
-        <v>0.004040672981550489</v>
+        <v>0.004101939093407743</v>
       </c>
       <c r="W76" t="n">
-        <v>0.01122203043468935</v>
+        <v>0.01244610098890504</v>
       </c>
       <c r="X76" t="n">
-        <v>0.004521100321287095</v>
+        <v>0.00456629799931043</v>
       </c>
     </row>
     <row r="77">
@@ -6586,46 +6586,46 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5107448989191544</v>
+        <v>0.4954473192373093</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5737343994656385</v>
+        <v>0.548596006887663</v>
       </c>
       <c r="M77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.299272883877356</v>
       </c>
       <c r="N77" t="n">
-        <v>4.564334046451275</v>
+        <v>4.371593978891362</v>
       </c>
       <c r="O77" t="n">
-        <v>0.003718853466600373</v>
+        <v>0.003514394027650367</v>
       </c>
       <c r="P77" t="n">
-        <v>0.007059945099086056</v>
+        <v>0.006422358746301867</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002461780828101518</v>
+        <v>0.002406775463466088</v>
       </c>
       <c r="R77" t="n">
-        <v>0.00228760131116767</v>
+        <v>0.002094916752757647</v>
       </c>
       <c r="S77" t="n">
-        <v>0.004796754913569742</v>
+        <v>0.004492136251616273</v>
       </c>
       <c r="T77" t="n">
-        <v>0.00455034047100411</v>
+        <v>0.004358661885619052</v>
       </c>
       <c r="U77" t="n">
-        <v>0.007259996581966238</v>
+        <v>0.007045527553508763</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003490678910223693</v>
+        <v>0.003433228032099846</v>
       </c>
       <c r="W77" t="n">
-        <v>0.003639558170356421</v>
+        <v>0.003824274931390079</v>
       </c>
       <c r="X77" t="n">
-        <v>0.005059814453745314</v>
+        <v>0.004812375491480065</v>
       </c>
     </row>
     <row r="78">
@@ -6666,46 +6666,46 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4915367798062171</v>
+        <v>0.4805966135072755</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5779851982610288</v>
+        <v>0.5552627887316869</v>
       </c>
       <c r="M78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.450858392300603</v>
       </c>
       <c r="N78" t="n">
-        <v>4.626570866390226</v>
+        <v>4.449226622035585</v>
       </c>
       <c r="O78" t="n">
-        <v>0.002067678207452573</v>
+        <v>0.001936822978948697</v>
       </c>
       <c r="P78" t="n">
-        <v>0.008358137063770948</v>
+        <v>0.007578632092538344</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.001730182155271701</v>
+        <v>0.00169054935656184</v>
       </c>
       <c r="R78" t="n">
-        <v>0.001287601818132588</v>
+        <v>0.001176642679695474</v>
       </c>
       <c r="S78" t="n">
-        <v>0.002423643236950788</v>
+        <v>0.002130181124430956</v>
       </c>
       <c r="T78" t="n">
-        <v>0.003345110724598941</v>
+        <v>0.003228607964990603</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01188180905641424</v>
+        <v>0.01152534273590268</v>
       </c>
       <c r="V78" t="n">
-        <v>0.002835604646444455</v>
+        <v>0.002781483306091168</v>
       </c>
       <c r="W78" t="n">
-        <v>0.0029307970674114</v>
+        <v>0.00304528819090173</v>
       </c>
       <c r="X78" t="n">
-        <v>0.005041158446732912</v>
+        <v>0.00490221643771764</v>
       </c>
     </row>
     <row r="79">
@@ -6746,46 +6746,46 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5515163866565659</v>
+        <v>0.5610550899029443</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5597631993720837</v>
+        <v>0.5629314367691181</v>
       </c>
       <c r="M79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.446570697558703</v>
       </c>
       <c r="N79" t="n">
-        <v>4.436949048940558</v>
+        <v>4.460541586380009</v>
       </c>
       <c r="O79" t="n">
-        <v>0.002346995187483055</v>
+        <v>0.002363085701296157</v>
       </c>
       <c r="P79" t="n">
-        <v>0.002512120847660788</v>
+        <v>0.002493468230435302</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001882607355503803</v>
+        <v>0.001893448215024157</v>
       </c>
       <c r="R79" t="n">
-        <v>0.003161333871784686</v>
+        <v>0.003174909657180953</v>
       </c>
       <c r="S79" t="n">
-        <v>0.4976924328963805</v>
+        <v>0.001052083578125455</v>
       </c>
       <c r="T79" t="n">
-        <v>0.003465363084410429</v>
+        <v>0.003513707948563072</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002159344593423184</v>
+        <v>0.001972333434337066</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002742070026928555</v>
+        <v>0.002786667368745591</v>
       </c>
       <c r="W79" t="n">
-        <v>0.003374068260695096</v>
+        <v>0.003641212570746621</v>
       </c>
       <c r="X79" t="n">
-        <v>306.4684865494842</v>
+        <v>0.07481062806337774</v>
       </c>
     </row>
     <row r="80">
@@ -6826,46 +6826,46 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5606867247544488</v>
+        <v>0.5606777633938708</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5629068163727795</v>
+        <v>0.5621761495646145</v>
       </c>
       <c r="M80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.540036555089061</v>
       </c>
       <c r="N80" t="n">
-        <v>4.460414387679079</v>
+        <v>4.455659895741714</v>
       </c>
       <c r="O80" t="n">
-        <v>0.002595993437593404</v>
+        <v>0.002599970185083688</v>
       </c>
       <c r="P80" t="n">
-        <v>0.003275690073416032</v>
+        <v>0.003273923925492484</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.002196708731227117</v>
+        <v>0.002203463077328192</v>
       </c>
       <c r="R80" t="n">
-        <v>0.003831624199725773</v>
+        <v>0.00384608703530474</v>
       </c>
       <c r="S80" t="n">
-        <v>0.1679063518858759</v>
+        <v>0.005904300473565313</v>
       </c>
       <c r="T80" t="n">
-        <v>0.003689860539297599</v>
+        <v>0.003812021045588731</v>
       </c>
       <c r="U80" t="n">
-        <v>0.002218795297381602</v>
+        <v>0.002224358336050397</v>
       </c>
       <c r="V80" t="n">
-        <v>0.003349544100288838</v>
+        <v>0.003489054886496084</v>
       </c>
       <c r="W80" t="n">
-        <v>0.004187888001211846</v>
+        <v>0.004626723061293953</v>
       </c>
       <c r="X80" t="n">
-        <v>135.3104755346407</v>
+        <v>0.5704342537206961</v>
       </c>
     </row>
     <row r="81">
@@ -6906,46 +6906,46 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.40758718491556</v>
+        <v>0.4048865563859553</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5555376511738532</v>
+        <v>0.5494547447668545</v>
       </c>
       <c r="M81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.610890896156159</v>
       </c>
       <c r="N81" t="n">
-        <v>4.552442218301301</v>
+        <v>4.50669197392645</v>
       </c>
       <c r="O81" t="n">
-        <v>0.002455977084466889</v>
+        <v>0.002428961705262596</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002848381669024926</v>
+        <v>0.002791026477254393</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001459711331802546</v>
+        <v>0.00144773530934036</v>
       </c>
       <c r="R81" t="n">
-        <v>0.002822611876905377</v>
+        <v>0.002790549440473973</v>
       </c>
       <c r="S81" t="n">
-        <v>0.3419412881419245</v>
+        <v>0.4970937479109305</v>
       </c>
       <c r="T81" t="n">
-        <v>0.003822342570045662</v>
+        <v>0.003414184336332713</v>
       </c>
       <c r="U81" t="n">
-        <v>0.004927031000691411</v>
+        <v>0.003793369303878517</v>
       </c>
       <c r="V81" t="n">
-        <v>0.002241855228355525</v>
+        <v>0.002088591239415925</v>
       </c>
       <c r="W81" t="n">
-        <v>0.004177303823774305</v>
+        <v>0.00350913951207799</v>
       </c>
       <c r="X81" t="n">
-        <v>144.1703708354243</v>
+        <v>3848.570378750543</v>
       </c>
     </row>
     <row r="82">
@@ -6986,46 +6986,46 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2997988150084465</v>
+        <v>0.2917254962962554</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5129576229304094</v>
+        <v>0.5178693238662242</v>
       </c>
       <c r="M82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.60546490597388</v>
       </c>
       <c r="N82" t="n">
-        <v>4.544480193625743</v>
+        <v>4.601086151681378</v>
       </c>
       <c r="O82" t="n">
-        <v>0.002698663339853888</v>
+        <v>0.002719871433499834</v>
       </c>
       <c r="P82" t="n">
-        <v>0.002598191739061718</v>
+        <v>0.002535876708074974</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.00137678227704196</v>
+        <v>0.001383850360950985</v>
       </c>
       <c r="R82" t="n">
-        <v>0.002921568655435401</v>
+        <v>0.00292486519799948</v>
       </c>
       <c r="S82" t="n">
-        <v>0.2302537402165207</v>
+        <v>1.000000000000024e-05</v>
       </c>
       <c r="T82" t="n">
-        <v>0.004222948913653427</v>
+        <v>0.004248012958814035</v>
       </c>
       <c r="U82" t="n">
-        <v>0.004712251555911406</v>
+        <v>0.004343343403376987</v>
       </c>
       <c r="V82" t="n">
-        <v>0.002146748265477811</v>
+        <v>0.002168905907955907</v>
       </c>
       <c r="W82" t="n">
-        <v>0.00388218197222274</v>
+        <v>0.004086730059497589</v>
       </c>
       <c r="X82" t="n">
-        <v>64.70975398866747</v>
+        <v>0.05111998818579167</v>
       </c>
     </row>
     <row r="83">
@@ -7064,46 +7064,46 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4674705519403926</v>
+        <v>0.5433397409012656</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5647928978252057</v>
+        <v>0.568047653279075</v>
       </c>
       <c r="M83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.643199327406445</v>
       </c>
       <c r="N83" t="n">
-        <v>4.484618423208232</v>
+        <v>4.506010167611416</v>
       </c>
       <c r="O83" t="n">
-        <v>0.002216179767475155</v>
+        <v>0.002227698822576718</v>
       </c>
       <c r="P83" t="n">
-        <v>0.002240342573698896</v>
+        <v>0.002262664115710382</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.001295855246095303</v>
+        <v>0.001305320341763647</v>
       </c>
       <c r="R83" t="n">
-        <v>0.003120076377653565</v>
+        <v>0.003179082081773116</v>
       </c>
       <c r="S83" t="n">
-        <v>0.1649296553593442</v>
+        <v>0.003402653009224385</v>
       </c>
       <c r="T83" t="n">
-        <v>0.003264536326886331</v>
+        <v>0.003216009133716249</v>
       </c>
       <c r="U83" t="n">
-        <v>0.003327657859587697</v>
+        <v>0.002817291396255174</v>
       </c>
       <c r="V83" t="n">
-        <v>0.001984189979251193</v>
+        <v>0.002031680929999283</v>
       </c>
       <c r="W83" t="n">
-        <v>0.004315621215233195</v>
+        <v>0.004408586241488692</v>
       </c>
       <c r="X83" t="n">
-        <v>119.8283480946596</v>
+        <v>0.2572767808716217</v>
       </c>
     </row>
     <row r="84">
@@ -7142,46 +7142,46 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3117458209363655</v>
+        <v>0.3162631075751626</v>
       </c>
       <c r="L84" t="n">
-        <v>0.531181230221128</v>
+        <v>0.5366847260638746</v>
       </c>
       <c r="M84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.586521951223069</v>
       </c>
       <c r="N84" t="n">
-        <v>4.408529981909352</v>
+        <v>4.463342169515876</v>
       </c>
       <c r="O84" t="n">
-        <v>0.002307328201738253</v>
+        <v>0.002313297494916917</v>
       </c>
       <c r="P84" t="n">
-        <v>0.002039831422271845</v>
+        <v>0.002082577737801762</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001739951747194378</v>
+        <v>0.001745268954148658</v>
       </c>
       <c r="R84" t="n">
-        <v>0.003812752785935672</v>
+        <v>0.003865178165058029</v>
       </c>
       <c r="S84" t="n">
-        <v>0.03343764744700815</v>
+        <v>0.008291942405082891</v>
       </c>
       <c r="T84" t="n">
-        <v>0.00341914235959427</v>
+        <v>0.003480762303234616</v>
       </c>
       <c r="U84" t="n">
-        <v>0.0009728527746580931</v>
+        <v>0.002490090000258875</v>
       </c>
       <c r="V84" t="n">
-        <v>0.002647397298335717</v>
+        <v>0.002703508748651533</v>
       </c>
       <c r="W84" t="n">
-        <v>0.005114408560467576</v>
+        <v>0.004977752067832083</v>
       </c>
       <c r="X84" t="n">
-        <v>13.46819809959546</v>
+        <v>1.305643617663522</v>
       </c>
     </row>
     <row r="85">
@@ -7220,46 +7220,46 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5023449079337079</v>
+        <v>0.4976135263187852</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5572700201547628</v>
+        <v>0.565054041765216</v>
       </c>
       <c r="M85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.548143428306743</v>
       </c>
       <c r="N85" t="n">
-        <v>4.429019718013674</v>
+        <v>4.489773371941594</v>
       </c>
       <c r="O85" t="n">
-        <v>0.002413812187012031</v>
+        <v>0.002408190510449579</v>
       </c>
       <c r="P85" t="n">
-        <v>0.001950229060857687</v>
+        <v>0.001980400080365809</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001294392393333573</v>
+        <v>0.001309120037836047</v>
       </c>
       <c r="R85" t="n">
-        <v>0.003466637127229636</v>
+        <v>0.003562330014203676</v>
       </c>
       <c r="S85" t="n">
-        <v>0.2072273675380267</v>
+        <v>0.00123190960995527</v>
       </c>
       <c r="T85" t="n">
-        <v>0.003542673890000585</v>
+        <v>0.00368994731817053</v>
       </c>
       <c r="U85" t="n">
-        <v>0.003119070562427769</v>
+        <v>0.00285676467699851</v>
       </c>
       <c r="V85" t="n">
-        <v>0.001901289759485224</v>
+        <v>0.001940873950962805</v>
       </c>
       <c r="W85" t="n">
-        <v>0.004103162307378847</v>
+        <v>0.00440105838592013</v>
       </c>
       <c r="X85" t="n">
-        <v>156.8417121762949</v>
+        <v>0.08426531387665179</v>
       </c>
     </row>
     <row r="86">
@@ -7298,46 +7298,46 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.4868109864264576</v>
+        <v>0.5001855836882525</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5548402214721208</v>
+        <v>0.5645914963074464</v>
       </c>
       <c r="M86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.655189285584574</v>
       </c>
       <c r="N86" t="n">
-        <v>4.411554185385604</v>
+        <v>4.489136163132573</v>
       </c>
       <c r="O86" t="n">
-        <v>0.002526502731325993</v>
+        <v>0.002558869330777236</v>
       </c>
       <c r="P86" t="n">
-        <v>0.002416214767713443</v>
+        <v>0.002498492652343923</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001771910666204131</v>
+        <v>0.001800170855414211</v>
       </c>
       <c r="R86" t="n">
-        <v>0.004471455961979826</v>
+        <v>0.004656547004153229</v>
       </c>
       <c r="S86" t="n">
-        <v>0.09798529976711341</v>
+        <v>0.001924593010585424</v>
       </c>
       <c r="T86" t="n">
-        <v>0.003798063795595208</v>
+        <v>0.003736981048562122</v>
       </c>
       <c r="U86" t="n">
-        <v>0.005378609540425613</v>
+        <v>0.003584250534883362</v>
       </c>
       <c r="V86" t="n">
-        <v>0.002652829120028037</v>
+        <v>0.002774650183428768</v>
       </c>
       <c r="W86" t="n">
-        <v>0.007046233613483999</v>
+        <v>0.006432464490078314</v>
       </c>
       <c r="X86" t="n">
-        <v>103.4515889808818</v>
+        <v>0.1095005539816664</v>
       </c>
     </row>
     <row r="87">
@@ -7376,46 +7376,46 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1824219159392768</v>
+        <v>0.1801165461460996</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4945038884000544</v>
+        <v>0.5054837591759742</v>
       </c>
       <c r="M87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.683999502138008</v>
       </c>
       <c r="N87" t="n">
-        <v>4.53177520219725</v>
+        <v>4.634427081471261</v>
       </c>
       <c r="O87" t="n">
-        <v>0.00272114900515137</v>
+        <v>0.0027420541333345</v>
       </c>
       <c r="P87" t="n">
-        <v>0.001661847581688478</v>
+        <v>0.001648542138880211</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.001394955195151356</v>
+        <v>0.001410820131783913</v>
       </c>
       <c r="R87" t="n">
-        <v>0.003154215234067909</v>
+        <v>0.003212262748333969</v>
       </c>
       <c r="S87" t="n">
-        <v>0.4999999996897916</v>
+        <v>1.000000000000122e-05</v>
       </c>
       <c r="T87" t="n">
-        <v>0.004870274711412501</v>
+        <v>0.004389203178119717</v>
       </c>
       <c r="U87" t="n">
-        <v>0.008259402607483177</v>
+        <v>0.003541782793342259</v>
       </c>
       <c r="V87" t="n">
-        <v>0.002437048306229612</v>
+        <v>0.002233922942977511</v>
       </c>
       <c r="W87" t="n">
-        <v>0.005304338646258398</v>
+        <v>0.004658863784332157</v>
       </c>
       <c r="X87" t="n">
-        <v>267.1345776119782</v>
+        <v>0.05913731895939856</v>
       </c>
     </row>
     <row r="88">
@@ -7454,46 +7454,46 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1719570752124408</v>
+        <v>0.1739893793974186</v>
       </c>
       <c r="L88" t="n">
-        <v>0.541042550812831</v>
+        <v>0.531456512631705</v>
       </c>
       <c r="M88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.663409450690607</v>
       </c>
       <c r="N88" t="n">
-        <v>4.606327035403109</v>
+        <v>4.538225610173969</v>
       </c>
       <c r="O88" t="n">
-        <v>0.002255666580925916</v>
+        <v>0.002238878514135571</v>
       </c>
       <c r="P88" t="n">
-        <v>0.008281548143212426</v>
+        <v>0.007913876977934463</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001222484317314992</v>
+        <v>0.001210169754577415</v>
       </c>
       <c r="R88" t="n">
-        <v>0.002496635390152388</v>
+        <v>0.002454898789865113</v>
       </c>
       <c r="S88" t="n">
-        <v>0.3758520663000774</v>
+        <v>0.003161005565094947</v>
       </c>
       <c r="T88" t="n">
-        <v>0.00336140810798419</v>
+        <v>0.003329725902673043</v>
       </c>
       <c r="U88" t="n">
-        <v>0.0184206847694719</v>
+        <v>0.01480037036079343</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001855215041522764</v>
+        <v>0.001856416415990756</v>
       </c>
       <c r="W88" t="n">
-        <v>0.003242315446217834</v>
+        <v>0.003297606894965767</v>
       </c>
       <c r="X88" t="n">
-        <v>103.6611786908913</v>
+        <v>0.2944849453992233</v>
       </c>
     </row>
     <row r="89">
@@ -7532,46 +7532,46 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.2700881523524867</v>
+        <v>0.2744023045987236</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5521358136220457</v>
+        <v>0.5414997110839789</v>
       </c>
       <c r="M89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.565818894645068</v>
       </c>
       <c r="N89" t="n">
-        <v>4.600021087846755</v>
+        <v>4.509249927115496</v>
       </c>
       <c r="O89" t="n">
-        <v>0.002915434746755069</v>
+        <v>0.002870152866398225</v>
       </c>
       <c r="P89" t="n">
-        <v>0.003116232582177875</v>
+        <v>0.002980408686188588</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001657568798413151</v>
+        <v>0.001635021145719489</v>
       </c>
       <c r="R89" t="n">
-        <v>0.002745908472256639</v>
+        <v>0.002699915099193609</v>
       </c>
       <c r="S89" t="n">
-        <v>0.03533330581033953</v>
+        <v>0.02207086978893256</v>
       </c>
       <c r="T89" t="n">
-        <v>0.004514961499207891</v>
+        <v>0.004720102390084328</v>
       </c>
       <c r="U89" t="n">
-        <v>0.004981087345915696</v>
+        <v>0.003210622145672739</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002408395199752218</v>
+        <v>0.002316230871430764</v>
       </c>
       <c r="W89" t="n">
-        <v>0.003573337020792281</v>
+        <v>0.003556408585269232</v>
       </c>
       <c r="X89" t="n">
-        <v>2.418273609192949</v>
+        <v>8.854709178984095</v>
       </c>
     </row>
     <row r="90">
@@ -7610,46 +7610,46 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2009697586071757</v>
+        <v>0.2308034783562465</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3949101135675893</v>
+        <v>0.4987691681967517</v>
       </c>
       <c r="M90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.504155908456531</v>
       </c>
       <c r="N90" t="n">
-        <v>3.531896932273188</v>
+        <v>4.286946619164399</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003637102604035654</v>
+        <v>0.003712133724656009</v>
       </c>
       <c r="P90" t="n">
-        <v>0.00283441711221466</v>
+        <v>0.003674065116094049</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.005410716596535368</v>
+        <v>0.006663209495693349</v>
       </c>
       <c r="R90" t="n">
-        <v>0.008322828118291615</v>
+        <v>0.01028761199310081</v>
       </c>
       <c r="S90" t="n">
-        <v>1.000000000228262e-05</v>
+        <v>0.002286678512656472</v>
       </c>
       <c r="T90" t="n">
-        <v>0.005407663427382321</v>
+        <v>0.006750567744379495</v>
       </c>
       <c r="U90" t="n">
-        <v>0.007831984389419382</v>
+        <v>0.006071709254221282</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01281778608814018</v>
+        <v>0.01214344360832982</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02331791682259975</v>
+        <v>0.02711329984200849</v>
       </c>
       <c r="X90" t="n">
-        <v>0.01734535278635061</v>
+        <v>0.08221776408323962</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Flexible CUE/Local_estpar_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_False_vo_False_CUE_False.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4820009970627345</v>
+        <v>0.4819862052836677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5557748387239961</v>
+        <v>0.5557732947795404</v>
       </c>
       <c r="M2" t="n">
-        <v>4.465606698018054</v>
+        <v>4.465607701141616</v>
       </c>
       <c r="N2" t="n">
-        <v>4.439263099357669</v>
+        <v>4.43926294832841</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001403324173184733</v>
+        <v>0.001403335582233443</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003314473593789447</v>
+        <v>0.003314376446541012</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001085901063395683</v>
+        <v>0.001085904973965971</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001988059006275667</v>
+        <v>0.001988062404111981</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001740976233937346</v>
+        <v>0.001740960669187959</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002669213027596314</v>
+        <v>0.002669239684484965</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00808550161638902</v>
+        <v>0.008084919785331936</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002109457767768127</v>
+        <v>0.002109467104822933</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003158695384935008</v>
+        <v>0.003158701517936889</v>
       </c>
       <c r="X2" t="n">
-        <v>0.002375230406224508</v>
+        <v>0.002375253000904934</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4085894186420144</v>
+        <v>0.4085894689594563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5347107163444119</v>
+        <v>0.5347107570693578</v>
       </c>
       <c r="M3" t="n">
-        <v>4.378970833950168</v>
+        <v>4.378970778573013</v>
       </c>
       <c r="N3" t="n">
-        <v>4.397048503220401</v>
+        <v>4.397048530441271</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0009986851631368897</v>
+        <v>0.0009986865112896065</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00225192927431775</v>
+        <v>0.002251932226455174</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008440649217406362</v>
+        <v>0.0008440660220287963</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001426906904903323</v>
+        <v>0.00142690806716877</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009465220259329515</v>
+        <v>0.0009465222394885416</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001854818211479373</v>
+        <v>0.001854822851037022</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003908158180641577</v>
+        <v>0.003908165667104682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001698875289465977</v>
+        <v>0.001698878475969215</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002147090031752763</v>
+        <v>0.002147091345203993</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001752792677320138</v>
+        <v>0.001752791925133239</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.52327017402166</v>
+        <v>0.5232640989042529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5632923374845957</v>
+        <v>0.5632921676615293</v>
       </c>
       <c r="M4" t="n">
-        <v>4.449533919724023</v>
+        <v>4.449531792817196</v>
       </c>
       <c r="N4" t="n">
-        <v>4.468590083632223</v>
+        <v>4.468590237503928</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002104561765109033</v>
+        <v>0.002104607176306674</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002416459581371855</v>
+        <v>0.002416470581426473</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005257164277545561</v>
+        <v>0.0005257198020493783</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002100748064927779</v>
+        <v>0.00210077216450664</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001230053045317944</v>
+        <v>0.00123005586485129</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004879071473616233</v>
+        <v>0.004879228866621919</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007151649058275476</v>
+        <v>0.0071517303918709</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001460633553275109</v>
+        <v>0.001460637082396226</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003527520023708981</v>
+        <v>0.003527560851520371</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00227229195208043</v>
+        <v>0.002272298254912744</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4069734038792395</v>
+        <v>0.4069735005006316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.541421490791658</v>
+        <v>0.5414215101218557</v>
       </c>
       <c r="M5" t="n">
-        <v>4.328675728015952</v>
+        <v>4.328675634134481</v>
       </c>
       <c r="N5" t="n">
-        <v>4.405411329420687</v>
+        <v>4.405411328083164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001298742520986819</v>
+        <v>0.001298742231510064</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002413634136797562</v>
+        <v>0.002413634505691426</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001047245189878097</v>
+        <v>0.001047245373517664</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001728950585206608</v>
+        <v>0.001728950175143055</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002255947472997772</v>
+        <v>0.002255948121524718</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002457474712611301</v>
+        <v>0.002457474934882375</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004632729497721595</v>
+        <v>0.004632736218648282</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002088747330756964</v>
+        <v>0.002088748191491861</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002651575116943114</v>
+        <v>0.002651580644099154</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0041430025757515</v>
+        <v>0.004143014631869577</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4592879234335376</v>
+        <v>0.4592879149818234</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5478670490145763</v>
+        <v>0.5478670662257827</v>
       </c>
       <c r="M6" t="n">
-        <v>4.385019187083561</v>
+        <v>4.385019195419657</v>
       </c>
       <c r="N6" t="n">
-        <v>4.422823879198369</v>
+        <v>4.422823928065834</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008975286452902113</v>
+        <v>0.0008975297826123751</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00197973722332886</v>
+        <v>0.001979739733869256</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0007343721415318114</v>
+        <v>0.0007343732669812053</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000872609515650665</v>
+        <v>0.0008726104972174032</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00104700916034469</v>
+        <v>0.001047009830238159</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001677744686486035</v>
+        <v>0.001677755493262214</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003350208408977679</v>
+        <v>0.003350241952124616</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001461941236259923</v>
+        <v>0.001461946681837973</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001556205208249434</v>
+        <v>0.001556226952272784</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001613811398169495</v>
+        <v>0.001613834421952307</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3951965360399166</v>
+        <v>0.3952111644541385</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5373242925554681</v>
+        <v>0.5373278029362806</v>
       </c>
       <c r="M7" t="n">
-        <v>4.421262405329895</v>
+        <v>4.421257329219673</v>
       </c>
       <c r="N7" t="n">
-        <v>4.403092963816217</v>
+        <v>4.403092028570548</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001343117382976923</v>
+        <v>0.001343137770803678</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002235504906119629</v>
+        <v>0.002235629852836817</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007539935253230279</v>
+        <v>0.0007540005727460266</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002054580161391528</v>
+        <v>0.002054612602297881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001265053356725014</v>
+        <v>0.001265160826241816</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002640388473431692</v>
+        <v>0.002640430012714204</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004321622735769258</v>
+        <v>0.004322105317827642</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001483845951389792</v>
+        <v>0.001483852791498152</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003236121690170925</v>
+        <v>0.003236126237252599</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002919361239637244</v>
+        <v>0.002919586142026606</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.268136507449542</v>
+        <v>0.2681364660808555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.512087221972082</v>
+        <v>0.5120871967915051</v>
       </c>
       <c r="M8" t="n">
-        <v>4.51057323281028</v>
+        <v>4.510573300984529</v>
       </c>
       <c r="N8" t="n">
-        <v>4.425970018614482</v>
+        <v>4.425970017796005</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001951356876075347</v>
+        <v>0.001951356202277138</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002105338646830639</v>
+        <v>0.002105337913644294</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001229902412122511</v>
+        <v>0.001229902438498839</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002587694009365692</v>
+        <v>0.002587693719101415</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001461348118488464</v>
+        <v>0.001461347594905527</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004195592777139894</v>
+        <v>0.004195614038645113</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003980989251075713</v>
+        <v>0.003980996521023147</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002580439640805522</v>
+        <v>0.00258044424010646</v>
       </c>
       <c r="W8" t="n">
-        <v>0.005067225189870457</v>
+        <v>0.005067338405873785</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002444557665928403</v>
+        <v>0.002444595375850951</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3433990727769943</v>
+        <v>0.3433996615356983</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5311637211698333</v>
+        <v>0.5311638720431645</v>
       </c>
       <c r="M9" t="n">
-        <v>4.328025721001465</v>
+        <v>4.328025823301873</v>
       </c>
       <c r="N9" t="n">
-        <v>4.403357051445087</v>
+        <v>4.403357084575182</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001906604030232696</v>
+        <v>0.001906603614151522</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002483530823036278</v>
+        <v>0.002483535759227612</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001007348943064478</v>
+        <v>0.001007349251825211</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00182037810288859</v>
+        <v>0.001820379310376713</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001499467728638909</v>
+        <v>0.001499468738935678</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004066260606687803</v>
+        <v>0.004066252817069568</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005094961167173334</v>
+        <v>0.005094981555923109</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001973964429114461</v>
+        <v>0.001973964273481157</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002997609478698777</v>
+        <v>0.00299760995303823</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002614906820514569</v>
+        <v>0.002614912292118673</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4233368867748208</v>
+        <v>0.4233319440240269</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5377285023825336</v>
+        <v>0.5377278824259737</v>
       </c>
       <c r="M10" t="n">
-        <v>4.304645472857671</v>
+        <v>4.304645875259563</v>
       </c>
       <c r="N10" t="n">
-        <v>4.330826025340635</v>
+        <v>4.330826014296707</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001730022522036795</v>
+        <v>0.001730030243531778</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002361588302747301</v>
+        <v>0.002361562074430464</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0007766238730648337</v>
+        <v>0.0007766231307726209</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003392152416526474</v>
+        <v>0.003392146521159673</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001286984888566293</v>
+        <v>0.001286965186219887</v>
       </c>
       <c r="T10" t="n">
-        <v>0.003640861161762531</v>
+        <v>0.003640851068979189</v>
       </c>
       <c r="U10" t="n">
-        <v>0.005383048416103412</v>
+        <v>0.005382916758795255</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001512808110715531</v>
+        <v>0.001512835928279318</v>
       </c>
       <c r="W10" t="n">
-        <v>0.005069383831441475</v>
+        <v>0.005069828906461868</v>
       </c>
       <c r="X10" t="n">
-        <v>0.00206659563054242</v>
+        <v>0.002067390483579575</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2019906136872595</v>
+        <v>0.2020093881041004</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4906804358159074</v>
+        <v>0.4906854818320289</v>
       </c>
       <c r="M11" t="n">
-        <v>4.107405143193574</v>
+        <v>4.107412849525095</v>
       </c>
       <c r="N11" t="n">
-        <v>4.302765842510607</v>
+        <v>4.302766080365228</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002392095840339019</v>
+        <v>0.002391961167079065</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001739468361475642</v>
+        <v>0.001739581659104056</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001310681980318146</v>
+        <v>0.001310734444242947</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002665750462055866</v>
+        <v>0.002665908473651712</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002075793884052734</v>
+        <v>0.00207594441140894</v>
       </c>
       <c r="T11" t="n">
-        <v>0.006375658856675861</v>
+        <v>0.006375069766837102</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003805064792629835</v>
+        <v>0.003805247919404558</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002635203690164511</v>
+        <v>0.002635191973655799</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005305818083680714</v>
+        <v>0.005304811042708402</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004431588574087487</v>
+        <v>0.00443168547105148</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1800254501765516</v>
+        <v>0.1800254450734588</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4456016176074714</v>
+        <v>0.4456015649967867</v>
       </c>
       <c r="M12" t="n">
-        <v>4.004770333347373</v>
+        <v>4.004770596798982</v>
       </c>
       <c r="N12" t="n">
-        <v>4.238743125060137</v>
+        <v>4.238743160893018</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004089097393641913</v>
+        <v>0.0004089090819971295</v>
       </c>
       <c r="P12" t="n">
-        <v>0.003614286243177038</v>
+        <v>0.003614281180866542</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0005128397362181788</v>
+        <v>0.0005128400664683097</v>
       </c>
       <c r="R12" t="n">
-        <v>0.00543986491245409</v>
+        <v>0.005439856706371286</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0009604653684871111</v>
+        <v>0.0009604640923235987</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001074674323083145</v>
+        <v>0.001074673605114627</v>
       </c>
       <c r="U12" t="n">
-        <v>0.005634469939059789</v>
+        <v>0.005634464047148352</v>
       </c>
       <c r="V12" t="n">
-        <v>0.00109382852185618</v>
+        <v>0.001093829230411012</v>
       </c>
       <c r="W12" t="n">
-        <v>0.009823647873238459</v>
+        <v>0.009823641744644132</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001555325397184552</v>
+        <v>0.001555324140314545</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2835460062602018</v>
+        <v>0.2835459920369254</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4780855870506601</v>
+        <v>0.47808557351448</v>
       </c>
       <c r="M13" t="n">
-        <v>4.337432442552224</v>
+        <v>4.337432423540404</v>
       </c>
       <c r="N13" t="n">
-        <v>4.487672442533043</v>
+        <v>4.487672437082733</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001753229293311984</v>
+        <v>0.001753229366189804</v>
       </c>
       <c r="P13" t="n">
-        <v>0.003185724771870839</v>
+        <v>0.003185724563871286</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001442563982057401</v>
+        <v>0.001442563966493311</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01128841474473307</v>
+        <v>0.01128841451609854</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01739662318465506</v>
+        <v>0.01739662333992922</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01063315898976523</v>
+        <v>0.01063326778789552</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0304457404121324</v>
+        <v>0.03044616579632715</v>
       </c>
       <c r="V13" t="n">
-        <v>0.008712285609849175</v>
+        <v>0.008712355316382247</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03433804052118489</v>
+        <v>0.03433844139913708</v>
       </c>
       <c r="X13" t="n">
-        <v>0.05155769378607284</v>
+        <v>0.05155797197471785</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3546715346376434</v>
+        <v>0.3546629830233172</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5133953637543747</v>
+        <v>0.5133909246142155</v>
       </c>
       <c r="M14" t="n">
-        <v>4.399848195776872</v>
+        <v>4.399847587477812</v>
       </c>
       <c r="N14" t="n">
-        <v>4.399228757419802</v>
+        <v>4.399228447789524</v>
       </c>
       <c r="O14" t="n">
-        <v>0.007427732388541494</v>
+        <v>0.007427579391166312</v>
       </c>
       <c r="P14" t="n">
-        <v>0.007413538375391182</v>
+        <v>0.007413121829289168</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01071438901634036</v>
+        <v>0.01071423814653151</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01285757004675775</v>
+        <v>0.01285725697300344</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02267604516406411</v>
+        <v>0.02267573696360298</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01408766459008326</v>
+        <v>0.01408779057481368</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02376792934684772</v>
+        <v>0.02376999968602327</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02035337642530559</v>
+        <v>0.02035327565629324</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02429903460229448</v>
+        <v>0.02430251045831406</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04834345345409055</v>
+        <v>0.04834903662519512</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4107507024762867</v>
+        <v>0.4107503650737579</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5352951084552128</v>
+        <v>0.5352950955533233</v>
       </c>
       <c r="M15" t="n">
-        <v>4.081381386375272</v>
+        <v>4.081379451844411</v>
       </c>
       <c r="N15" t="n">
-        <v>4.339169589930354</v>
+        <v>4.339169601632303</v>
       </c>
       <c r="O15" t="n">
-        <v>0.007969960618389352</v>
+        <v>0.007969965634459522</v>
       </c>
       <c r="P15" t="n">
-        <v>0.007898270540086206</v>
+        <v>0.007898273414974545</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.009570617963066769</v>
+        <v>0.009570622008554366</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01276131220098181</v>
+        <v>0.01276131752160502</v>
       </c>
       <c r="S15" t="n">
-        <v>0.04861357676262122</v>
+        <v>0.04861390440188909</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01468075563442484</v>
+        <v>0.01468025109079512</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01539876186411284</v>
+        <v>0.01539795744129051</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01812021055044602</v>
+        <v>0.01811971114915241</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01782873845023634</v>
+        <v>0.0178276926798683</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2165882066593008</v>
+        <v>0.2165744795447707</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5547407510209781</v>
+        <v>0.5547407800811401</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5734821582779931</v>
+        <v>0.5734822454886035</v>
       </c>
       <c r="M16" t="n">
-        <v>4.399547914881411</v>
+        <v>4.399548131317051</v>
       </c>
       <c r="N16" t="n">
-        <v>4.539077565296358</v>
+        <v>4.53907821435329</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02796949386226819</v>
+        <v>0.02796949295173958</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02003421251905571</v>
+        <v>0.02003421167117234</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02180540941540461</v>
+        <v>0.02180540853047539</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01388633991859524</v>
+        <v>0.01388633935989157</v>
       </c>
       <c r="S16" t="n">
-        <v>0.006263433551753609</v>
+        <v>0.006263349591880999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2916227790431715</v>
+        <v>0.2916137994978541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.262934803151423</v>
+        <v>0.2629257614800626</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2949069973461528</v>
+        <v>0.2948967926378642</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1716397859462628</v>
+        <v>0.1716339080856148</v>
       </c>
       <c r="X16" t="n">
-        <v>26.51235180071523</v>
+        <v>26.51115601394275</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2331461754905137</v>
+        <v>0.2331500314999871</v>
       </c>
       <c r="L17" t="n">
-        <v>0.406589364121359</v>
+        <v>0.4065941410254578</v>
       </c>
       <c r="M17" t="n">
-        <v>3.94020970433473</v>
+        <v>3.94021163738553</v>
       </c>
       <c r="N17" t="n">
-        <v>4.112353878722189</v>
+        <v>4.112357339925035</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00750426518253162</v>
+        <v>0.007504289394287735</v>
       </c>
       <c r="P17" t="n">
-        <v>0.003433148094599903</v>
+        <v>0.003433277120474064</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.00707592562003308</v>
+        <v>0.007075928225094934</v>
       </c>
       <c r="R17" t="n">
-        <v>0.007342364716052921</v>
+        <v>0.007342532964200555</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0118792985093066</v>
+        <v>0.01187939828382769</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01830638727051602</v>
+        <v>0.018308910671973</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0454312631705148</v>
+        <v>0.04544371249402258</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01597836488037385</v>
+        <v>0.01597992802191798</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04908081565810252</v>
+        <v>0.0490963985409373</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03080727381976259</v>
+        <v>0.03081222125605365</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4237696658272739</v>
+        <v>0.4237696014838366</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5310760399988518</v>
+        <v>0.5310760309121937</v>
       </c>
       <c r="M18" t="n">
-        <v>4.353516083339685</v>
+        <v>4.35351611582689</v>
       </c>
       <c r="N18" t="n">
-        <v>4.363451685761255</v>
+        <v>4.363451690511688</v>
       </c>
       <c r="O18" t="n">
-        <v>0.008473421332769952</v>
+        <v>0.008473426622743889</v>
       </c>
       <c r="P18" t="n">
-        <v>0.008203538200273676</v>
+        <v>0.008203541009976164</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.007576683739947955</v>
+        <v>0.007576684862861891</v>
       </c>
       <c r="R18" t="n">
-        <v>0.01698566609386941</v>
+        <v>0.01698567637826977</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0152744982461058</v>
+        <v>0.01527450470167842</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01553652280596278</v>
+        <v>0.01553665913308316</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01770063107284404</v>
+        <v>0.01770143389877288</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01380917670459922</v>
+        <v>0.01380923487298809</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02610768403474725</v>
+        <v>0.02610864523105859</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02431233473304231</v>
+        <v>0.0243128068190562</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4773272763108123</v>
+        <v>0.4773250445593811</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5579678990525505</v>
+        <v>0.5579679072016114</v>
       </c>
       <c r="M19" t="n">
-        <v>3.822055423832857</v>
+        <v>3.822038745202903</v>
       </c>
       <c r="N19" t="n">
-        <v>4.423535276551999</v>
+        <v>4.42353533571672</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003377614411842964</v>
+        <v>0.003377616978665548</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0123452368162881</v>
+        <v>0.01234524486262122</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003958066090485471</v>
+        <v>0.003958067840011987</v>
       </c>
       <c r="R19" t="n">
-        <v>0.003276485620337937</v>
+        <v>0.003276487699527221</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07990161302197171</v>
+        <v>0.07990394089655398</v>
       </c>
       <c r="T19" t="n">
-        <v>0.009671759418108026</v>
+        <v>0.009671766135552436</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02573539372470116</v>
+        <v>0.02573543517868565</v>
       </c>
       <c r="V19" t="n">
-        <v>0.009842889091851513</v>
+        <v>0.009842893346329979</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01091587937448386</v>
+        <v>0.01091588853810114</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6192280951586201</v>
+        <v>0.6190074153625479</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4199137651576323</v>
+        <v>0.4199058580112651</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5474936203784275</v>
+        <v>0.5474903714007548</v>
       </c>
       <c r="M20" t="n">
-        <v>4.56912263600572</v>
+        <v>4.569123216151214</v>
       </c>
       <c r="N20" t="n">
-        <v>4.539887473076988</v>
+        <v>4.539889475751193</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00549481518068809</v>
+        <v>0.005494647121636673</v>
       </c>
       <c r="P20" t="n">
-        <v>0.005836481944462598</v>
+        <v>0.005835996755416992</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.006351785179579538</v>
+        <v>0.006351716313733152</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00826320315471335</v>
+        <v>0.00826292578721181</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03705695498277304</v>
+        <v>0.03705549887794125</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01112562896190301</v>
+        <v>0.01112575169771915</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01873979166028595</v>
+        <v>0.01873971969283419</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01212465097508708</v>
+        <v>0.01212454421833092</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01559584446911312</v>
+        <v>0.015596280409951</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06060844297327843</v>
+        <v>0.06059760061083461</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5119505968393867</v>
+        <v>0.5119505969026676</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5213787263452643</v>
+        <v>0.5213787263607937</v>
       </c>
       <c r="M21" t="n">
-        <v>4.080584583903153</v>
+        <v>4.080584584375281</v>
       </c>
       <c r="N21" t="n">
-        <v>4.150903815996617</v>
+        <v>4.15090381611249</v>
       </c>
       <c r="O21" t="n">
-        <v>0.005639635455711436</v>
+        <v>0.005639635438614914</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01978454819557003</v>
+        <v>0.01978454810503249</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.001936691368467081</v>
+        <v>0.001936691374547758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.00314714169940986</v>
+        <v>0.003147141693485383</v>
       </c>
       <c r="S21" t="n">
-        <v>0.02137332562871849</v>
+        <v>0.0213733256318582</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01198871036824219</v>
+        <v>0.01198870811426322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0485109584786317</v>
+        <v>0.04851094207206648</v>
       </c>
       <c r="V21" t="n">
-        <v>0.007610641826160927</v>
+        <v>0.007610638755090889</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01544733776554973</v>
+        <v>0.01544733317408881</v>
       </c>
       <c r="X21" t="n">
-        <v>0.04307495191518745</v>
+        <v>0.04307497679517034</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3688714801677828</v>
+        <v>0.3688612018985629</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4920088310018856</v>
+        <v>0.4919989229145439</v>
       </c>
       <c r="M22" t="n">
-        <v>4.178478767273362</v>
+        <v>4.178475283245922</v>
       </c>
       <c r="N22" t="n">
-        <v>4.35056357786738</v>
+        <v>4.350560000706283</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004117314356716533</v>
+        <v>0.004117240709575115</v>
       </c>
       <c r="P22" t="n">
-        <v>0.00114886756582807</v>
+        <v>0.001148714828806296</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.00305482716779904</v>
+        <v>0.003054777623121086</v>
       </c>
       <c r="R22" t="n">
-        <v>0.004910339209037033</v>
+        <v>0.004910162744173794</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0159113081786764</v>
+        <v>0.01591089714076192</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01626591487176414</v>
+        <v>0.0162562948534215</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03347402334414474</v>
+        <v>0.03345145563136444</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0130754115408137</v>
+        <v>0.01306847633119048</v>
       </c>
       <c r="W22" t="n">
-        <v>0.03419474270784342</v>
+        <v>0.03416872444315955</v>
       </c>
       <c r="X22" t="n">
-        <v>0.07925215511393971</v>
+        <v>0.07920074942508994</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3463056376458854</v>
+        <v>0.3463059500009534</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4955049680069133</v>
+        <v>0.4955050599528029</v>
       </c>
       <c r="M23" t="n">
-        <v>3.869820336646796</v>
+        <v>3.869821613027207</v>
       </c>
       <c r="N23" t="n">
-        <v>4.220654455048162</v>
+        <v>4.22065451896456</v>
       </c>
       <c r="O23" t="n">
-        <v>0.006894049230856078</v>
+        <v>0.006894048931665894</v>
       </c>
       <c r="P23" t="n">
-        <v>0.006183078196142612</v>
+        <v>0.006183082126095065</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.005088717594890914</v>
+        <v>0.005088718360122062</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01530935327516402</v>
+        <v>0.01530935947442969</v>
       </c>
       <c r="S23" t="n">
-        <v>0.04151817707709853</v>
+        <v>0.04151804113153963</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01373854621123025</v>
+        <v>0.01373857182874083</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01927005828472981</v>
+        <v>0.01927011949006213</v>
       </c>
       <c r="V23" t="n">
-        <v>0.01064430192017393</v>
+        <v>0.01064432218201612</v>
       </c>
       <c r="W23" t="n">
-        <v>0.03312580761433149</v>
+        <v>0.03312618830989259</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1832004327571876</v>
+        <v>0.1831995532033085</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5381273422429782</v>
+        <v>0.5381273409542512</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5470027408408563</v>
+        <v>0.547002739713621</v>
       </c>
       <c r="M24" t="n">
-        <v>4.275774819085798</v>
+        <v>4.275774809481438</v>
       </c>
       <c r="N24" t="n">
-        <v>4.34190649096697</v>
+        <v>4.341906482568857</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01203545559721172</v>
+        <v>0.01203545562202727</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01004529823354628</v>
+        <v>0.01004529825579129</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01499757294487271</v>
+        <v>0.01499757305856862</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01862265053993981</v>
+        <v>0.01862265047482825</v>
       </c>
       <c r="S24" t="n">
-        <v>0.00967468292000678</v>
+        <v>0.009674684907949491</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03507891200501202</v>
+        <v>0.0350789073096866</v>
       </c>
       <c r="U24" t="n">
-        <v>0.05415999265245638</v>
+        <v>0.05415993384771214</v>
       </c>
       <c r="V24" t="n">
-        <v>0.05259305234620553</v>
+        <v>0.05259303522252935</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1261211523055847</v>
+        <v>0.1261210994671672</v>
       </c>
       <c r="X24" t="n">
-        <v>14.75414444609668</v>
+        <v>14.75414169250071</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5494012369207484</v>
+        <v>0.5494012367047949</v>
       </c>
       <c r="L25" t="n">
-        <v>0.553169863386759</v>
+        <v>0.5531698631861268</v>
       </c>
       <c r="M25" t="n">
-        <v>4.359776070804065</v>
+        <v>4.359776069195355</v>
       </c>
       <c r="N25" t="n">
-        <v>4.387847283084264</v>
+        <v>4.387847281589893</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001157681547578076</v>
+        <v>0.001157681545332393</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001157589154790366</v>
+        <v>0.001157589153162352</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0006302853211086022</v>
+        <v>0.000630285324941019</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0007832485721281111</v>
+        <v>0.000783248568483238</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003838724546397517</v>
+        <v>0.0003838724562848627</v>
       </c>
       <c r="T25" t="n">
-        <v>0.002267958486245309</v>
+        <v>0.002267958484017728</v>
       </c>
       <c r="U25" t="n">
-        <v>0.00270899601992159</v>
+        <v>0.002708996019472673</v>
       </c>
       <c r="V25" t="n">
-        <v>0.00162140724802391</v>
+        <v>0.001621407251698243</v>
       </c>
       <c r="W25" t="n">
-        <v>0.002106701845915807</v>
+        <v>0.002106701842403449</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001540730271712957</v>
+        <v>0.00154073027034562</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.540731726273736</v>
+        <v>0.5407317262128234</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5490301157634917</v>
+        <v>0.5490301157157812</v>
       </c>
       <c r="M26" t="n">
-        <v>4.295183238249074</v>
+        <v>4.295183237795165</v>
       </c>
       <c r="N26" t="n">
-        <v>4.357008735272015</v>
+        <v>4.357008734916589</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001938013741353031</v>
+        <v>0.001938013745720317</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00221206757913711</v>
+        <v>0.002212067581264251</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0008933418646792555</v>
+        <v>0.0008933418625129237</v>
       </c>
       <c r="R26" t="n">
-        <v>0.00109962526127561</v>
+        <v>0.001099625263218435</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0006904394360973052</v>
+        <v>0.0006904394410452116</v>
       </c>
       <c r="T26" t="n">
-        <v>0.003211259008394061</v>
+        <v>0.00321125902224697</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002694103808050452</v>
+        <v>0.002694103803596509</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001847268570726132</v>
+        <v>0.001847268567995235</v>
       </c>
       <c r="W26" t="n">
-        <v>0.002219502083977518</v>
+        <v>0.002219502084793593</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001505072667080908</v>
+        <v>0.001505072665028954</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5300735357727636</v>
+        <v>0.5300735357192439</v>
       </c>
       <c r="L27" t="n">
-        <v>0.535135312738271</v>
+        <v>0.5351353126940652</v>
       </c>
       <c r="M27" t="n">
-        <v>4.215743336119488</v>
+        <v>4.215743335720499</v>
       </c>
       <c r="N27" t="n">
-        <v>4.253474004984595</v>
+        <v>4.253474004655103</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001012555397734606</v>
+        <v>0.001012555396915253</v>
       </c>
       <c r="P27" t="n">
-        <v>0.001487015784377962</v>
+        <v>0.001487015783865734</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0013059701019892</v>
+        <v>0.001305970104220076</v>
       </c>
       <c r="R27" t="n">
-        <v>0.00136209974248716</v>
+        <v>0.001362099741218957</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0009913447923430745</v>
+        <v>0.0009913447922769662</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001988809417429517</v>
+        <v>0.001988809417001087</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002518024516275519</v>
+        <v>0.002518024513590993</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002455191652587889</v>
+        <v>0.002455191656608801</v>
       </c>
       <c r="W27" t="n">
-        <v>0.002537847236615794</v>
+        <v>0.002537847234674736</v>
       </c>
       <c r="X27" t="n">
-        <v>0.00200568844827443</v>
+        <v>0.002005688448929952</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4452115703335381</v>
+        <v>0.445211583392869</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5401267358905437</v>
+        <v>0.5401267310458568</v>
       </c>
       <c r="M28" t="n">
-        <v>4.128552560111538</v>
+        <v>4.128552781342059</v>
       </c>
       <c r="N28" t="n">
-        <v>4.340322074606317</v>
+        <v>4.340322062544591</v>
       </c>
       <c r="O28" t="n">
-        <v>0.00126334998893581</v>
+        <v>0.001263350155967723</v>
       </c>
       <c r="P28" t="n">
         <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001452102018642351</v>
+        <v>0.001452101771135116</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005614392106655404</v>
+        <v>0.005614392190411559</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01164061372255424</v>
+        <v>0.01164060687687198</v>
       </c>
       <c r="T28" t="n">
-        <v>0.002977483695452996</v>
+        <v>0.002977492642634639</v>
       </c>
       <c r="U28" t="n">
-        <v>0.008356130336639078</v>
+        <v>0.008356188901204183</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003065344613953413</v>
+        <v>0.003065350270035685</v>
       </c>
       <c r="W28" t="n">
-        <v>0.01074742264297821</v>
+        <v>0.01074746638025606</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02755580185847104</v>
+        <v>0.02755501810440017</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5450393411938402</v>
+        <v>0.5450393413035584</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5378439064658589</v>
+        <v>0.5378439064957135</v>
       </c>
       <c r="M29" t="n">
-        <v>4.327280143443206</v>
+        <v>4.327280144260669</v>
       </c>
       <c r="N29" t="n">
-        <v>4.273660911914124</v>
+        <v>4.273660912136644</v>
       </c>
       <c r="O29" t="n">
-        <v>0.003929893345178515</v>
+        <v>0.003929893332711217</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01899259387671743</v>
+        <v>0.0189925936786421</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0009447870484310175</v>
+        <v>0.000944787063132475</v>
       </c>
       <c r="R29" t="n">
-        <v>0.02167819992120882</v>
+        <v>0.02167819989327526</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0105071624805524</v>
+        <v>0.01050716249094746</v>
       </c>
       <c r="T29" t="n">
-        <v>0.006426931862669509</v>
+        <v>0.006426931815995308</v>
       </c>
       <c r="U29" t="n">
-        <v>0.07519599170340231</v>
+        <v>0.07519598957619354</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003536722927407943</v>
+        <v>0.003536722907099762</v>
       </c>
       <c r="W29" t="n">
-        <v>0.05000623514702596</v>
+        <v>0.05000623489004311</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01813806959402106</v>
+        <v>0.01813806960565919</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5180684702589733</v>
+        <v>0.5180692828056708</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5448577815063299</v>
+        <v>0.5448578321850709</v>
       </c>
       <c r="M30" t="n">
-        <v>4.577350772514278</v>
+        <v>4.577351645319422</v>
       </c>
       <c r="N30" t="n">
-        <v>4.339109306159301</v>
+        <v>4.339109372852636</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002261034364808982</v>
+        <v>0.002261029606328758</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005629642527933598</v>
+        <v>0.005629650033192894</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0006121217654199854</v>
+        <v>0.0006121214175922358</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01178527129785273</v>
+        <v>0.01178528432929125</v>
       </c>
       <c r="S30" t="n">
-        <v>0.005617842513038024</v>
+        <v>0.005617841702753589</v>
       </c>
       <c r="T30" t="n">
-        <v>0.003996118371189472</v>
+        <v>0.003996054665493262</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0101715710623463</v>
+        <v>0.0101706605924921</v>
       </c>
       <c r="V30" t="n">
-        <v>0.003288688272475206</v>
+        <v>0.003288547435417809</v>
       </c>
       <c r="W30" t="n">
-        <v>0.02039742588598964</v>
+        <v>0.02039719518248434</v>
       </c>
       <c r="X30" t="n">
-        <v>0.007607950423399105</v>
+        <v>0.007607510580302882</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5411091241769229</v>
+        <v>0.5411091243856065</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5556978667155873</v>
+        <v>0.5556978668907762</v>
       </c>
       <c r="M31" t="n">
-        <v>4.297995521688784</v>
+        <v>4.297995523243836</v>
       </c>
       <c r="N31" t="n">
-        <v>4.406670651650804</v>
+        <v>4.406670652955556</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002482585655425598</v>
+        <v>0.002482585714528534</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007465202381290556</v>
+        <v>0.00746520238740976</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0006461726625112033</v>
+        <v>0.0006461727029412601</v>
       </c>
       <c r="R31" t="n">
-        <v>0.002412704530710292</v>
+        <v>0.002412704574836931</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001226001704476962</v>
+        <v>0.001226001711208524</v>
       </c>
       <c r="T31" t="n">
-        <v>0.004252781974369944</v>
+        <v>0.004252782063407671</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01855833226933372</v>
+        <v>0.01855833198751329</v>
       </c>
       <c r="V31" t="n">
-        <v>0.002771415060403715</v>
+        <v>0.002771415086046717</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003967572597895572</v>
+        <v>0.003967572620662782</v>
       </c>
       <c r="X31" t="n">
-        <v>0.003509555661825215</v>
+        <v>0.003509555647454621</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5785259936431176</v>
+        <v>0.5785259286975886</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5569642496622</v>
+        <v>0.5569642658630317</v>
       </c>
       <c r="M32" t="n">
-        <v>4.576621334530718</v>
+        <v>4.576620851231514</v>
       </c>
       <c r="N32" t="n">
-        <v>4.41609064602723</v>
+        <v>4.416090766784087</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008324140239795527</v>
+        <v>0.000832412594005572</v>
       </c>
       <c r="P32" t="n">
-        <v>0.005225616144913479</v>
+        <v>0.005225607555272127</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.000000000033531e-05</v>
+        <v>1.000000000033804e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.00592955115043159</v>
+        <v>0.005929534895807368</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001961800586290341</v>
+        <v>0.001961798335946971</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00242084692056028</v>
+        <v>0.002420845610897785</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01137717000891556</v>
+        <v>0.0113771491744154</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002535087797342961</v>
+        <v>0.002535088239485972</v>
       </c>
       <c r="W32" t="n">
-        <v>0.01157848904815869</v>
+        <v>0.01157844954904428</v>
       </c>
       <c r="X32" t="n">
-        <v>0.004406982058343866</v>
+        <v>0.004406980607236974</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3932497006496025</v>
+        <v>0.3932499985155354</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5378821124575858</v>
+        <v>0.5378821214916114</v>
       </c>
       <c r="M33" t="n">
-        <v>4.368367739242999</v>
+        <v>4.368367793710408</v>
       </c>
       <c r="N33" t="n">
-        <v>4.330314865607638</v>
+        <v>4.330314908187959</v>
       </c>
       <c r="O33" t="n">
-        <v>0.004888663914502342</v>
+        <v>0.004888658209405932</v>
       </c>
       <c r="P33" t="n">
-        <v>0.007212428671348764</v>
+        <v>0.007212384788177682</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003912686249517354</v>
+        <v>0.003912683755184647</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01561764853255337</v>
+        <v>0.0156176352002752</v>
       </c>
       <c r="S33" t="n">
-        <v>0.007963689824454128</v>
+        <v>0.007963683982461348</v>
       </c>
       <c r="T33" t="n">
-        <v>0.009474880490404517</v>
+        <v>0.009474857227960421</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01675315289859948</v>
+        <v>0.01675305992259682</v>
       </c>
       <c r="V33" t="n">
-        <v>0.007049281676337073</v>
+        <v>0.007049276941316167</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0231523686449879</v>
+        <v>0.02315232538351211</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01155482303228677</v>
+        <v>0.01155480352082398</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.536901696262555</v>
+        <v>0.5369016959858964</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5432769441177873</v>
+        <v>0.5432769441207026</v>
       </c>
       <c r="M34" t="n">
-        <v>4.266640352725299</v>
+        <v>4.266640350663374</v>
       </c>
       <c r="N34" t="n">
-        <v>4.314148516785144</v>
+        <v>4.314148516806856</v>
       </c>
       <c r="O34" t="n">
-        <v>0.006370157979814552</v>
+        <v>0.006370157948108135</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01702657890431597</v>
+        <v>0.0170265795975241</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.003641605001491819</v>
+        <v>0.00364160498733877</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0178614884672569</v>
+        <v>0.01786148844866371</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0106640986111774</v>
+        <v>0.01066409856641214</v>
       </c>
       <c r="T34" t="n">
-        <v>0.01015912955820077</v>
+        <v>0.01015912948283414</v>
       </c>
       <c r="U34" t="n">
-        <v>0.08148469257749509</v>
+        <v>0.08148470136963391</v>
       </c>
       <c r="V34" t="n">
-        <v>0.004999184385137802</v>
+        <v>0.004999184378125962</v>
       </c>
       <c r="W34" t="n">
-        <v>0.02303028801158441</v>
+        <v>0.02303028803684702</v>
       </c>
       <c r="X34" t="n">
-        <v>0.009168973817179155</v>
+        <v>0.009168973752999167</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5172477546113869</v>
+        <v>0.5002346258691004</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5372052578390364</v>
+        <v>0.5379442884696014</v>
       </c>
       <c r="M35" t="n">
-        <v>4.120101088769337</v>
+        <v>3.993150554641779</v>
       </c>
       <c r="N35" t="n">
-        <v>4.268901056506724</v>
+        <v>4.274407835124276</v>
       </c>
       <c r="O35" t="n">
-        <v>0.00160311689198589</v>
+        <v>0.001611442063359442</v>
       </c>
       <c r="P35" t="n">
-        <v>0.05305091754217937</v>
+        <v>0.4999999348815848</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0009718893269561204</v>
+        <v>0.0009762447285230196</v>
       </c>
       <c r="R35" t="n">
-        <v>0.01363881906275516</v>
+        <v>0.01360903222067151</v>
       </c>
       <c r="S35" t="n">
-        <v>0.002001732789806226</v>
+        <v>0.002009112271392676</v>
       </c>
       <c r="T35" t="n">
-        <v>0.003294270805693139</v>
+        <v>0.003300065094914236</v>
       </c>
       <c r="U35" t="n">
-        <v>13.76592079389676</v>
+        <v>1510.983170175587</v>
       </c>
       <c r="V35" t="n">
-        <v>0.00263922640594925</v>
+        <v>0.002666300952959859</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02452224810155695</v>
+        <v>0.02505873926785777</v>
       </c>
       <c r="X35" t="n">
-        <v>0.003987109114662761</v>
+        <v>0.003975027491810793</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5508842687946176</v>
+        <v>0.5508842674969333</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5490937391614111</v>
+        <v>0.549093738428441</v>
       </c>
       <c r="M36" t="n">
-        <v>4.370823363997192</v>
+        <v>4.370823354330846</v>
       </c>
       <c r="N36" t="n">
-        <v>4.357485294707015</v>
+        <v>4.357485289246882</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001148490572273193</v>
+        <v>0.001148490657381395</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00307717957572216</v>
+        <v>0.003077179821902338</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0006854268294459944</v>
+        <v>0.0006854268940854434</v>
       </c>
       <c r="R36" t="n">
-        <v>0.002938435695939468</v>
+        <v>0.002938435850241455</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001999038289489383</v>
+        <v>0.001999038475037432</v>
       </c>
       <c r="T36" t="n">
-        <v>0.002811096147057301</v>
+        <v>0.002811096197717063</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006337624750983241</v>
+        <v>0.006337625242553987</v>
       </c>
       <c r="V36" t="n">
-        <v>0.0028171002403565</v>
+        <v>0.002817100325132901</v>
       </c>
       <c r="W36" t="n">
-        <v>0.005461112347909127</v>
+        <v>0.005461112328953203</v>
       </c>
       <c r="X36" t="n">
-        <v>0.005692943070074919</v>
+        <v>0.005692942924321855</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5416253914309452</v>
+        <v>0.5416253932533359</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5505769363543592</v>
+        <v>0.5505769366825227</v>
       </c>
       <c r="M37" t="n">
-        <v>4.301842560539425</v>
+        <v>4.301842574119091</v>
       </c>
       <c r="N37" t="n">
-        <v>4.368532165107248</v>
+        <v>4.36853216755206</v>
       </c>
       <c r="O37" t="n">
-        <v>0.001951818525727223</v>
+        <v>0.001951818657936519</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003775338516418326</v>
+        <v>0.003775338815150046</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001390964160980643</v>
+        <v>0.001390964252173642</v>
       </c>
       <c r="R37" t="n">
-        <v>0.00329000288667543</v>
+        <v>0.00329000308150584</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01100114274129598</v>
+        <v>0.01100114207365007</v>
       </c>
       <c r="T37" t="n">
-        <v>0.004396328076821872</v>
+        <v>0.004396328455118859</v>
       </c>
       <c r="U37" t="n">
-        <v>0.005227424127431031</v>
+        <v>0.005227424341747817</v>
       </c>
       <c r="V37" t="n">
-        <v>0.00344109741709066</v>
+        <v>0.00344109759215231</v>
       </c>
       <c r="W37" t="n">
-        <v>0.005951835509162308</v>
+        <v>0.005951835554850922</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02342914338681179</v>
+        <v>0.02342913974811657</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5410877791334675</v>
+        <v>0.5410877784062029</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5459458066566727</v>
+        <v>0.5459458049843995</v>
       </c>
       <c r="M38" t="n">
-        <v>4.297836464385832</v>
+        <v>4.297836458966457</v>
       </c>
       <c r="N38" t="n">
-        <v>4.334032058827635</v>
+        <v>4.334032046369179</v>
       </c>
       <c r="O38" t="n">
-        <v>0.002338921322743589</v>
+        <v>0.00233892084882577</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001666349850650152</v>
+        <v>0.001666349601542721</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.001015483726897044</v>
+        <v>0.001015483449105355</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002741039073618736</v>
+        <v>0.002741038489811496</v>
       </c>
       <c r="S38" t="n">
-        <v>0.007427259195261015</v>
+        <v>0.00742725776241806</v>
       </c>
       <c r="T38" t="n">
-        <v>0.005274645397900988</v>
+        <v>0.005274644632839331</v>
       </c>
       <c r="U38" t="n">
-        <v>0.002918253790409358</v>
+        <v>0.002918253733868105</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002907041900607403</v>
+        <v>0.002907041609621463</v>
       </c>
       <c r="W38" t="n">
-        <v>0.00528189552377787</v>
+        <v>0.005281895229720768</v>
       </c>
       <c r="X38" t="n">
-        <v>0.01038654539914852</v>
+        <v>0.01038654664022216</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5532307663355256</v>
+        <v>0.5532307752309462</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5490907070150366</v>
+        <v>0.5490907096364179</v>
       </c>
       <c r="M39" t="n">
-        <v>4.388301465052076</v>
+        <v>4.388301531307524</v>
       </c>
       <c r="N39" t="n">
-        <v>4.357462340729385</v>
+        <v>4.357462360255743</v>
       </c>
       <c r="O39" t="n">
-        <v>0.002359992589827809</v>
+        <v>0.002359992861863835</v>
       </c>
       <c r="P39" t="n">
-        <v>0.003702430483569739</v>
+        <v>0.003702430575148988</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001457906850969324</v>
+        <v>0.001457906954338344</v>
       </c>
       <c r="R39" t="n">
-        <v>0.00693351776837865</v>
+        <v>0.006933519811974364</v>
       </c>
       <c r="S39" t="n">
-        <v>0.003416305407835117</v>
+        <v>0.003416305715974498</v>
       </c>
       <c r="T39" t="n">
-        <v>0.004281865001445758</v>
+        <v>0.004281864773907172</v>
       </c>
       <c r="U39" t="n">
-        <v>0.005569409119699223</v>
+        <v>0.005569407861429469</v>
       </c>
       <c r="V39" t="n">
-        <v>0.003232027643082421</v>
+        <v>0.003232027481218742</v>
       </c>
       <c r="W39" t="n">
-        <v>0.009725194627759233</v>
+        <v>0.009725194048488013</v>
       </c>
       <c r="X39" t="n">
-        <v>0.004664106411195658</v>
+        <v>0.004664106324570991</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2863667851232301</v>
+        <v>0.2863664886197732</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5271207910217088</v>
+        <v>0.5271204502379122</v>
       </c>
       <c r="M40" t="n">
-        <v>4.296817286241648</v>
+        <v>4.296820969432684</v>
       </c>
       <c r="N40" t="n">
-        <v>4.506890140802735</v>
+        <v>4.506889998369746</v>
       </c>
       <c r="O40" t="n">
-        <v>0.003278728445615086</v>
+        <v>0.003278726070929605</v>
       </c>
       <c r="P40" t="n">
-        <v>0.003089800473342979</v>
+        <v>0.003089779720339843</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002882570328982219</v>
+        <v>0.002882568103542677</v>
       </c>
       <c r="R40" t="n">
-        <v>0.003017740906169194</v>
+        <v>0.003017726054565006</v>
       </c>
       <c r="S40" t="n">
-        <v>0.07807832236119872</v>
+        <v>0.07807661241129382</v>
       </c>
       <c r="T40" t="n">
-        <v>0.005476440935951244</v>
+        <v>0.005476256086230317</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004647382454243626</v>
+        <v>0.004646521166477284</v>
       </c>
       <c r="V40" t="n">
-        <v>0.004806524676509841</v>
+        <v>0.004806334527187849</v>
       </c>
       <c r="W40" t="n">
-        <v>0.004444480063743021</v>
+        <v>0.00444411654279376</v>
       </c>
       <c r="X40" t="n">
-        <v>0.380544158817807</v>
+        <v>0.3805575829259759</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5140482499878872</v>
+        <v>0.5140475197579126</v>
       </c>
       <c r="L41" t="n">
-        <v>0.564414113880731</v>
+        <v>0.5644141345471967</v>
       </c>
       <c r="M41" t="n">
-        <v>4.40576475719459</v>
+        <v>4.405764247326678</v>
       </c>
       <c r="N41" t="n">
-        <v>4.493856779888718</v>
+        <v>4.493857408736279</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001391656400926803</v>
+        <v>0.001391669066400706</v>
       </c>
       <c r="P41" t="n">
-        <v>0.004399313255137251</v>
+        <v>0.004399357850331868</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.001352162448147057</v>
+        <v>0.001352178462662594</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001596940527065349</v>
+        <v>0.001596960000336592</v>
       </c>
       <c r="S41" t="n">
-        <v>0.007221881731744752</v>
+        <v>0.007222002458092432</v>
       </c>
       <c r="T41" t="n">
-        <v>0.002651866114864359</v>
+        <v>0.002651875999703658</v>
       </c>
       <c r="U41" t="n">
-        <v>0.006451431272536002</v>
+        <v>0.006451453545156444</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002558933698549424</v>
+        <v>0.002558947464053217</v>
       </c>
       <c r="W41" t="n">
-        <v>0.003099542075719755</v>
+        <v>0.003099554242942193</v>
       </c>
       <c r="X41" t="n">
-        <v>0.01186187215043931</v>
+        <v>0.01186201134781627</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3386526589655819</v>
+        <v>0.338826929622885</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5342163589279788</v>
+        <v>0.5342474547176886</v>
       </c>
       <c r="M42" t="n">
-        <v>4.440464077287422</v>
+        <v>4.442217945015177</v>
       </c>
       <c r="N42" t="n">
-        <v>4.46843664188295</v>
+        <v>4.468687475338037</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004281516471129437</v>
+        <v>0.004281508704868541</v>
       </c>
       <c r="P42" t="n">
-        <v>0.005214135917475113</v>
+        <v>0.00521412980827872</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.004670009338758509</v>
+        <v>0.004669928374372534</v>
       </c>
       <c r="R42" t="n">
-        <v>0.004021796853162577</v>
+        <v>0.004021788907481127</v>
       </c>
       <c r="S42" t="n">
-        <v>0.01132450225667985</v>
+        <v>0.0111153975937515</v>
       </c>
       <c r="T42" t="n">
-        <v>0.02774871723951278</v>
+        <v>0.0113223849537367</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1631452017061719</v>
+        <v>0.0772923643234</v>
       </c>
       <c r="V42" t="n">
-        <v>0.02913625638316486</v>
+        <v>0.01472954098585295</v>
       </c>
       <c r="W42" t="n">
-        <v>0.03825790635323686</v>
+        <v>0.009081784077814343</v>
       </c>
       <c r="X42" t="n">
-        <v>3024.05788914925</v>
+        <v>2676.777685335336</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2608254166930639</v>
+        <v>0.260825778069708</v>
       </c>
       <c r="L43" t="n">
-        <v>0.500792154886424</v>
+        <v>0.5007923199843168</v>
       </c>
       <c r="M43" t="n">
-        <v>3.977480086284531</v>
+        <v>3.977476633209355</v>
       </c>
       <c r="N43" t="n">
-        <v>4.303832950344297</v>
+        <v>4.303832975848606</v>
       </c>
       <c r="O43" t="n">
-        <v>0.01874586278938806</v>
+        <v>0.01874580092876143</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01372248228968801</v>
+        <v>0.01372248987722231</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0202453029478202</v>
+        <v>0.02024529018634331</v>
       </c>
       <c r="R43" t="n">
-        <v>0.03502886687088413</v>
+        <v>0.03502884891852464</v>
       </c>
       <c r="S43" t="n">
-        <v>0.07390886488689426</v>
+        <v>0.0739098280115701</v>
       </c>
       <c r="T43" t="n">
-        <v>0.03354842024453984</v>
+        <v>0.03354828348051372</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02232218124113033</v>
+        <v>0.02232203907674345</v>
       </c>
       <c r="V43" t="n">
-        <v>0.04036131334519136</v>
+        <v>0.04036128172782141</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04755366154509751</v>
+        <v>0.04755306184605636</v>
       </c>
       <c r="X43" t="n">
-        <v>0.2016356741055982</v>
+        <v>0.2016407495007457</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5286870787682787</v>
+        <v>0.5286870788523486</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5601500753340829</v>
+        <v>0.5601500753244641</v>
       </c>
       <c r="M44" t="n">
-        <v>4.205406969984286</v>
+        <v>4.205406970611064</v>
       </c>
       <c r="N44" t="n">
-        <v>4.439811321784974</v>
+        <v>4.439811321713447</v>
       </c>
       <c r="O44" t="n">
-        <v>0.03271704029141038</v>
+        <v>0.03271704027618151</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02441717894133158</v>
+        <v>0.02441717890143893</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02212281777374925</v>
+        <v>0.0221228176652262</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02308496603318283</v>
+        <v>0.02308496601756155</v>
       </c>
       <c r="S44" t="n">
-        <v>0.05343111858940566</v>
+        <v>0.05343111854570366</v>
       </c>
       <c r="T44" t="n">
-        <v>0.06370462302804071</v>
+        <v>0.06370462282802503</v>
       </c>
       <c r="U44" t="n">
-        <v>0.03180317974153177</v>
+        <v>0.03180317964852051</v>
       </c>
       <c r="V44" t="n">
-        <v>0.0430702891490072</v>
+        <v>0.04307028894329093</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02966094837093374</v>
+        <v>0.02966094833997664</v>
       </c>
       <c r="X44" t="n">
-        <v>0.08761204451491394</v>
+        <v>0.08761204435006276</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5400703130547023</v>
+        <v>0.5400682057539532</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5561626704094714</v>
+        <v>0.5561630602657146</v>
       </c>
       <c r="M45" t="n">
-        <v>4.290254436529441</v>
+        <v>4.290238732877079</v>
       </c>
       <c r="N45" t="n">
-        <v>4.410136618536906</v>
+        <v>4.410139521744966</v>
       </c>
       <c r="O45" t="n">
-        <v>0.09555035461627759</v>
+        <v>0.09554874875990049</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1250915914571251</v>
+        <v>0.1250931591510586</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.07358513998912945</v>
+        <v>0.0735850187080641</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1603984936262677</v>
+        <v>0.1603991817974873</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1985422221337302</v>
+        <v>0.1985671732430643</v>
       </c>
       <c r="T45" t="n">
-        <v>0.3285839385364094</v>
+        <v>0.3285720122474886</v>
       </c>
       <c r="U45" t="n">
-        <v>0.368312342267658</v>
+        <v>0.3683267143406719</v>
       </c>
       <c r="V45" t="n">
-        <v>0.1741461302697716</v>
+        <v>0.1741458253283941</v>
       </c>
       <c r="W45" t="n">
-        <v>0.4181644161022353</v>
+        <v>0.418170153888601</v>
       </c>
       <c r="X45" t="n">
-        <v>0.8008581742231349</v>
+        <v>0.8011280844810089</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4692195827002179</v>
+        <v>0.4692227989288898</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5639226084278881</v>
+        <v>0.5639225381280216</v>
       </c>
       <c r="M46" t="n">
-        <v>3.761450846446995</v>
+        <v>3.761474892830758</v>
       </c>
       <c r="N46" t="n">
-        <v>4.467884158084563</v>
+        <v>4.467883635561851</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06328472078645837</v>
+        <v>0.06328466881218602</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04462164018410317</v>
+        <v>0.04462163011382053</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03204109986727702</v>
+        <v>0.03204109565159344</v>
       </c>
       <c r="R46" t="n">
-        <v>0.05109896705719571</v>
+        <v>0.0510989448345948</v>
       </c>
       <c r="S46" t="n">
-        <v>0.2440606428421472</v>
+        <v>0.2440482826360077</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1600066093206869</v>
+        <v>0.1600064158750759</v>
       </c>
       <c r="U46" t="n">
-        <v>0.08553689371680227</v>
+        <v>0.08553687401930028</v>
       </c>
       <c r="V46" t="n">
-        <v>0.04752251098581024</v>
+        <v>0.04752250777496061</v>
       </c>
       <c r="W46" t="n">
-        <v>0.07980915958113927</v>
+        <v>0.07980912133676514</v>
       </c>
       <c r="X46" t="n">
-        <v>2.891900819193784</v>
+        <v>2.891545098106384</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5376530400040005</v>
+        <v>0.5376530401280268</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5539463945344929</v>
+        <v>0.5539463945369345</v>
       </c>
       <c r="M47" t="n">
-        <v>4.272240003116125</v>
+        <v>4.272240004040461</v>
       </c>
       <c r="N47" t="n">
-        <v>4.393626783533189</v>
+        <v>4.393626783551436</v>
       </c>
       <c r="O47" t="n">
-        <v>0.02629568054123893</v>
+        <v>0.02629568054744607</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02041470948493697</v>
+        <v>0.02041470949021812</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02389137395773333</v>
+        <v>0.02389137405215568</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03290551379086816</v>
+        <v>0.03290551379655882</v>
       </c>
       <c r="S47" t="n">
-        <v>0.04923244189691206</v>
+        <v>0.0492324416134196</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04780522201779444</v>
+        <v>0.04780522204310972</v>
       </c>
       <c r="U47" t="n">
-        <v>0.02798146392183112</v>
+        <v>0.02798146392272971</v>
       </c>
       <c r="V47" t="n">
-        <v>0.04733699667129609</v>
+        <v>0.04733699679048463</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03885331549029692</v>
+        <v>0.038853315601297</v>
       </c>
       <c r="X47" t="n">
-        <v>0.06008300019995178</v>
+        <v>0.06008299907425721</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4047097120777118</v>
+        <v>0.4047095718033272</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5472509420816788</v>
+        <v>0.5472509429512606</v>
       </c>
       <c r="M48" t="n">
-        <v>3.278188650913639</v>
+        <v>3.27818759776892</v>
       </c>
       <c r="N48" t="n">
-        <v>4.343715651178799</v>
+        <v>4.343715657605308</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02657723951613876</v>
+        <v>0.0265772395201899</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05274552791758433</v>
+        <v>0.05274552807042486</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.04243709189823286</v>
+        <v>0.04243709195863585</v>
       </c>
       <c r="R48" t="n">
-        <v>0.08900288061287753</v>
+        <v>0.08900288065764353</v>
       </c>
       <c r="S48" t="n">
-        <v>0.4372374145354189</v>
+        <v>0.4372380472155886</v>
       </c>
       <c r="T48" t="n">
-        <v>0.04810971543351892</v>
+        <v>0.04810971492986994</v>
       </c>
       <c r="U48" t="n">
-        <v>0.08841556091310868</v>
+        <v>0.08841556159837076</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1013494155246297</v>
+        <v>0.101349414954587</v>
       </c>
       <c r="W48" t="n">
-        <v>0.09393475410431229</v>
+        <v>0.09393475367658047</v>
       </c>
       <c r="X48" t="n">
-        <v>10.59535791972128</v>
+        <v>10.59538949925502</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3632462737432927</v>
+        <v>0.3632548584744411</v>
       </c>
       <c r="L49" t="n">
-        <v>0.544970517889401</v>
+        <v>0.5449726727035527</v>
       </c>
       <c r="M49" t="n">
-        <v>4.068731139454012</v>
+        <v>4.068683261012442</v>
       </c>
       <c r="N49" t="n">
-        <v>4.413023442429037</v>
+        <v>4.413023214906262</v>
       </c>
       <c r="O49" t="n">
-        <v>0.01994479468519353</v>
+        <v>0.01994440329165346</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01201849925632891</v>
+        <v>0.01201880221183307</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01883590216196246</v>
+        <v>0.0188345736682798</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0246997340023753</v>
+        <v>0.02469977958777791</v>
       </c>
       <c r="S49" t="n">
-        <v>0.1102549096656836</v>
+        <v>0.1102692020714981</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03501566541640557</v>
+        <v>0.0350149612060867</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01799052030069824</v>
+        <v>0.0179908422082301</v>
       </c>
       <c r="V49" t="n">
-        <v>0.03399911443141951</v>
+        <v>0.03399726768779774</v>
       </c>
       <c r="W49" t="n">
-        <v>0.03523731116959425</v>
+        <v>0.03523746785807305</v>
       </c>
       <c r="X49" t="n">
-        <v>0.4014669031282085</v>
+        <v>0.401606975651256</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5409958952894117</v>
+        <v>0.540998905599272</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5609105796056079</v>
+        <v>0.5609127617027081</v>
       </c>
       <c r="M50" t="n">
-        <v>4.297151770118207</v>
+        <v>4.297174202195596</v>
       </c>
       <c r="N50" t="n">
-        <v>4.445470385809243</v>
+        <v>4.445486584110231</v>
       </c>
       <c r="O50" t="n">
-        <v>0.06486606026164178</v>
+        <v>0.06486632291762735</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06452410122925463</v>
+        <v>0.06452418018592221</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06516623177053395</v>
+        <v>0.06516618478440823</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03600624296411507</v>
+        <v>0.03600617295366941</v>
       </c>
       <c r="S50" t="n">
-        <v>0.01136839625712979</v>
+        <v>0.01135174676225052</v>
       </c>
       <c r="T50" t="n">
-        <v>0.2270018663367448</v>
+        <v>0.2270669384296271</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2636069185885194</v>
+        <v>0.2640638292175684</v>
       </c>
       <c r="V50" t="n">
-        <v>0.2679372505169348</v>
+        <v>0.268413893924108</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1611465545386548</v>
+        <v>0.1615666609368926</v>
       </c>
       <c r="X50" t="n">
-        <v>14.3064493284135</v>
+        <v>14.32484121568235</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4812086802605804</v>
+        <v>0.4812090458799397</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5588663612374861</v>
+        <v>0.5588663725590283</v>
       </c>
       <c r="M51" t="n">
-        <v>3.851059526098112</v>
+        <v>3.851062257943341</v>
       </c>
       <c r="N51" t="n">
-        <v>4.430252432167871</v>
+        <v>4.430252516575232</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05474557304944666</v>
+        <v>0.05474574679854656</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04139987088441678</v>
+        <v>0.0413999229465196</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1289472612832484</v>
+        <v>0.1289473194543958</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06407570240233228</v>
+        <v>0.06407579312780651</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2179871846332974</v>
+        <v>0.217986333288868</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1326478479834944</v>
+        <v>0.1326488291261534</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08255978716328416</v>
+        <v>0.08255991642362341</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2293256315720723</v>
+        <v>0.229325703389019</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1199481010574502</v>
+        <v>0.1199482802202736</v>
       </c>
       <c r="X51" t="n">
-        <v>2.408586938743106</v>
+        <v>2.408617015401786</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5429836066241071</v>
+        <v>0.5429836102873031</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5519919379474244</v>
+        <v>0.5519919380643462</v>
       </c>
       <c r="M52" t="n">
-        <v>4.311963123218198</v>
+        <v>4.3119631505133</v>
       </c>
       <c r="N52" t="n">
-        <v>4.379070425761204</v>
+        <v>4.379070426633709</v>
       </c>
       <c r="O52" t="n">
-        <v>0.01056980021685694</v>
+        <v>0.01056979969781632</v>
       </c>
       <c r="P52" t="n">
-        <v>0.01011734337544687</v>
+        <v>0.01011734309230839</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.01115439287387856</v>
+        <v>0.01115439212154074</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01267777671203137</v>
+        <v>0.01267777655208299</v>
       </c>
       <c r="S52" t="n">
-        <v>0.05214676690899978</v>
+        <v>0.05214674920908486</v>
       </c>
       <c r="T52" t="n">
-        <v>0.01781992051110715</v>
+        <v>0.01781991963489088</v>
       </c>
       <c r="U52" t="n">
-        <v>0.01393050101495484</v>
+        <v>0.01393050081159345</v>
       </c>
       <c r="V52" t="n">
-        <v>0.02010213452782804</v>
+        <v>0.02010213291821791</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01949607486565501</v>
+        <v>0.01949607489855787</v>
       </c>
       <c r="X52" t="n">
-        <v>0.08528346792340756</v>
+        <v>0.08528342039959375</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4961096498617924</v>
+        <v>0.4961113824202694</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5569397584495432</v>
+        <v>0.5569398536644009</v>
       </c>
       <c r="M53" t="n">
-        <v>4.490422673838463</v>
+        <v>4.49042296350168</v>
       </c>
       <c r="N53" t="n">
-        <v>4.431904863413439</v>
+        <v>4.431904841609771</v>
       </c>
       <c r="O53" t="n">
-        <v>0.02301682853957677</v>
+        <v>0.02301676682047736</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02115848481187217</v>
+        <v>0.02115853940174127</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01454550754735299</v>
+        <v>0.01454550952274899</v>
       </c>
       <c r="R53" t="n">
-        <v>0.03992718198825528</v>
+        <v>0.0399271713960245</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1920175385278811</v>
+        <v>0.1920175817164271</v>
       </c>
       <c r="T53" t="n">
-        <v>0.0400030918988551</v>
+        <v>0.04000296776645997</v>
       </c>
       <c r="U53" t="n">
-        <v>0.02977304511028818</v>
+        <v>0.02977314796502658</v>
       </c>
       <c r="V53" t="n">
-        <v>0.02298465081135883</v>
+        <v>0.02298465561804789</v>
       </c>
       <c r="W53" t="n">
-        <v>0.05966659762148636</v>
+        <v>0.05966662807054187</v>
       </c>
       <c r="X53" t="n">
-        <v>0.2197006054314774</v>
+        <v>0.2197008157492841</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3258000977721076</v>
+        <v>0.3258004340263557</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5287898826449937</v>
+        <v>0.5287899333415547</v>
       </c>
       <c r="M54" t="n">
-        <v>4.139890418693176</v>
+        <v>4.139890457854863</v>
       </c>
       <c r="N54" t="n">
-        <v>4.361117336283419</v>
+        <v>4.361117324160594</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02351676465159932</v>
+        <v>0.02351676759459878</v>
       </c>
       <c r="P54" t="n">
-        <v>0.01024406127602647</v>
+        <v>0.01024406425672435</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02179658485958028</v>
+        <v>0.02179651967391544</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01414296212851437</v>
+        <v>0.01414297027944847</v>
       </c>
       <c r="S54" t="n">
-        <v>0.03220731123326998</v>
+        <v>0.03220727173169589</v>
       </c>
       <c r="T54" t="n">
-        <v>0.04386528010369108</v>
+        <v>0.04386536033874317</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01796933988212004</v>
+        <v>0.01796926924345473</v>
       </c>
       <c r="V54" t="n">
-        <v>0.04456338969903082</v>
+        <v>0.04456293628972086</v>
       </c>
       <c r="W54" t="n">
-        <v>0.02145308495291094</v>
+        <v>0.02145300743512026</v>
       </c>
       <c r="X54" t="n">
-        <v>0.05650877433197121</v>
+        <v>0.05650822549500029</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3243733482653745</v>
+        <v>0.3243715757543829</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5207697334533022</v>
+        <v>0.5207691742897034</v>
       </c>
       <c r="M55" t="n">
-        <v>4.37343702145688</v>
+        <v>4.373436424558091</v>
       </c>
       <c r="N55" t="n">
-        <v>4.410295015553443</v>
+        <v>4.410295051077955</v>
       </c>
       <c r="O55" t="n">
-        <v>0.01691980388186572</v>
+        <v>0.01691985191371047</v>
       </c>
       <c r="P55" t="n">
-        <v>0.009810806694572734</v>
+        <v>0.009810752562902696</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.01825446804135301</v>
+        <v>0.01825443090386275</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01786748179534087</v>
+        <v>0.01786745226323148</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01973821326632086</v>
+        <v>0.01973810320767517</v>
       </c>
       <c r="T55" t="n">
-        <v>0.02948921313147662</v>
+        <v>0.02948928928017197</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01461432315198538</v>
+        <v>0.01461269726751561</v>
       </c>
       <c r="V55" t="n">
-        <v>0.03712189866780809</v>
+        <v>0.0371221582573948</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02353727611921678</v>
+        <v>0.02353475317792963</v>
       </c>
       <c r="X55" t="n">
-        <v>0.0289465985119338</v>
+        <v>0.02894101932925007</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5097180810386136</v>
+        <v>0.5097180812285835</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5521349186700187</v>
+        <v>0.5521349186664659</v>
       </c>
       <c r="M56" t="n">
-        <v>4.063927352245716</v>
+        <v>4.063927353663189</v>
       </c>
       <c r="N56" t="n">
-        <v>4.380121791248679</v>
+        <v>4.380121791222325</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01788283889818332</v>
+        <v>0.01788283889402423</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01340615818860914</v>
+        <v>0.01340615820661926</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01476816841035354</v>
+        <v>0.01476816845092419</v>
       </c>
       <c r="R56" t="n">
-        <v>0.02550269428741145</v>
+        <v>0.0255026943091674</v>
       </c>
       <c r="S56" t="n">
-        <v>0.05919001245145147</v>
+        <v>0.05919001225645634</v>
       </c>
       <c r="T56" t="n">
-        <v>0.03154746106001149</v>
+        <v>0.03154746099517089</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01852511120146979</v>
+        <v>0.0185251112666143</v>
       </c>
       <c r="V56" t="n">
-        <v>0.02751403081654895</v>
+        <v>0.02751403087410189</v>
       </c>
       <c r="W56" t="n">
-        <v>0.03508856474236026</v>
+        <v>0.03508856479366628</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1402670044442715</v>
+        <v>0.1402670047527875</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5362984060044483</v>
+        <v>0.5362984060841561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5545372151083801</v>
+        <v>0.5545372150903707</v>
       </c>
       <c r="M57" t="n">
-        <v>4.26214400069415</v>
+        <v>4.262144001288224</v>
       </c>
       <c r="N57" t="n">
-        <v>4.398024514826248</v>
+        <v>4.398024514692201</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02335415796389578</v>
+        <v>0.02335415789816163</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01055041984585022</v>
+        <v>0.01055041984106579</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01749190118172447</v>
+        <v>0.01749190112285755</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01872592063907398</v>
+        <v>0.01872592065414534</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02947005120761005</v>
+        <v>0.0294700511204646</v>
       </c>
       <c r="T57" t="n">
-        <v>0.0443214406298665</v>
+        <v>0.04432144036737171</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01564946283566307</v>
+        <v>0.01564946282173266</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03067597931135057</v>
+        <v>0.03067597917244633</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02492786669493469</v>
+        <v>0.02492786675848525</v>
       </c>
       <c r="X57" t="n">
-        <v>0.04086461391742603</v>
+        <v>0.04086461377210767</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2359136518339272</v>
+        <v>0.2359135900857199</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5333513553544688</v>
+        <v>0.5333513402283213</v>
       </c>
       <c r="M58" t="n">
-        <v>4.091754229257946</v>
+        <v>4.091754218681647</v>
       </c>
       <c r="N58" t="n">
-        <v>4.428503233920229</v>
+        <v>4.428503206011263</v>
       </c>
       <c r="O58" t="n">
-        <v>0.04113720345944752</v>
+        <v>0.04113719548891011</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01201190955085237</v>
+        <v>0.01201190629912731</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.04028031210337838</v>
+        <v>0.04028032695475253</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01041512724948527</v>
+        <v>0.01041512339304197</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0527906051136479</v>
+        <v>0.05279061316809013</v>
       </c>
       <c r="T58" t="n">
-        <v>0.09064664076817713</v>
+        <v>0.09064567183766213</v>
       </c>
       <c r="U58" t="n">
-        <v>0.02182126136206662</v>
+        <v>0.02182131693413635</v>
       </c>
       <c r="V58" t="n">
-        <v>0.09571734328003741</v>
+        <v>0.09571746933346392</v>
       </c>
       <c r="W58" t="n">
-        <v>0.02046337714861655</v>
+        <v>0.02046350801083293</v>
       </c>
       <c r="X58" t="n">
-        <v>0.1140005831565476</v>
+        <v>0.1140006909300416</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5293059348727757</v>
+        <v>0.529305935645196</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5538338158486154</v>
+        <v>0.5538338154450453</v>
       </c>
       <c r="M59" t="n">
-        <v>4.210020762317669</v>
+        <v>4.210020768076263</v>
       </c>
       <c r="N59" t="n">
-        <v>4.392782555440949</v>
+        <v>4.392782552435599</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01029833608232163</v>
+        <v>0.01029833533417803</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004539144323541964</v>
+        <v>0.00453914424498581</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.008650096836568687</v>
+        <v>0.008650096759533005</v>
       </c>
       <c r="R59" t="n">
-        <v>0.007098065092985744</v>
+        <v>0.007098064930533415</v>
       </c>
       <c r="S59" t="n">
-        <v>0.00822416294863002</v>
+        <v>0.008224162736488839</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01676074210330156</v>
+        <v>0.01676074233610583</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005541944152225409</v>
+        <v>0.005541944080237548</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01143190424185291</v>
+        <v>0.01143190326471464</v>
       </c>
       <c r="W59" t="n">
-        <v>0.006676033978372371</v>
+        <v>0.00667603427183447</v>
       </c>
       <c r="X59" t="n">
-        <v>0.007331851313612147</v>
+        <v>0.007331851557140006</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.520091897588902</v>
+        <v>0.5200918946229371</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5420607107055893</v>
+        <v>0.5420607064299383</v>
       </c>
       <c r="M60" t="n">
-        <v>4.141314459674549</v>
+        <v>4.141314437553916</v>
       </c>
       <c r="N60" t="n">
-        <v>4.30507491140169</v>
+        <v>4.305074879542543</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002688510826234986</v>
+        <v>0.002688509876704253</v>
       </c>
       <c r="P60" t="n">
-        <v>0.004443635269329842</v>
+        <v>0.004443631870204095</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001399026473855564</v>
+        <v>0.001399025702763169</v>
       </c>
       <c r="R60" t="n">
-        <v>0.004570396915047842</v>
+        <v>0.004570395180094162</v>
       </c>
       <c r="S60" t="n">
-        <v>0.00879421067319191</v>
+        <v>0.008794208760202702</v>
       </c>
       <c r="T60" t="n">
-        <v>0.003856969144677906</v>
+        <v>0.003856968448603529</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005279303190128591</v>
+        <v>0.005279299429339826</v>
       </c>
       <c r="V60" t="n">
-        <v>0.002241673457764175</v>
+        <v>0.002241672900072007</v>
       </c>
       <c r="W60" t="n">
-        <v>0.005061016126528004</v>
+        <v>0.005061013846246434</v>
       </c>
       <c r="X60" t="n">
-        <v>0.009739714992418713</v>
+        <v>0.009739738059253156</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4276854726398666</v>
+        <v>0.4276857654472169</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5395379223645458</v>
+        <v>0.5395379467983648</v>
       </c>
       <c r="M61" t="n">
-        <v>3.964762310542818</v>
+        <v>3.964763507400216</v>
       </c>
       <c r="N61" t="n">
-        <v>4.304599680755931</v>
+        <v>4.304599776773225</v>
       </c>
       <c r="O61" t="n">
-        <v>0.005887735743405191</v>
+        <v>0.005887748594677501</v>
       </c>
       <c r="P61" t="n">
-        <v>0.008942872273152736</v>
+        <v>0.008942894013426236</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.003397250813141699</v>
+        <v>0.003397253624711337</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01928900163698361</v>
+        <v>0.01928902200586704</v>
       </c>
       <c r="S61" t="n">
-        <v>0.03909610157582086</v>
+        <v>0.03909597819541948</v>
       </c>
       <c r="T61" t="n">
-        <v>0.00802721393766803</v>
+        <v>0.008027200949565518</v>
       </c>
       <c r="U61" t="n">
-        <v>0.01015982028744835</v>
+        <v>0.01015983944577239</v>
       </c>
       <c r="V61" t="n">
-        <v>0.004169802449378564</v>
+        <v>0.004169809534080407</v>
       </c>
       <c r="W61" t="n">
-        <v>0.01662024494803216</v>
+        <v>0.01662043657157579</v>
       </c>
       <c r="X61" t="n">
-        <v>0.1551983915692233</v>
+        <v>0.1551824124241999</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1560475317581405</v>
+        <v>0.1558892941267478</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4558713548482391</v>
+        <v>0.4557413373554173</v>
       </c>
       <c r="M62" t="n">
-        <v>4.22633178824696</v>
+        <v>4.226186446895603</v>
       </c>
       <c r="N62" t="n">
-        <v>4.265155680872917</v>
+        <v>4.265102198995067</v>
       </c>
       <c r="O62" t="n">
-        <v>0.006638142889749127</v>
+        <v>0.006637690913906368</v>
       </c>
       <c r="P62" t="n">
-        <v>0.003780264533255319</v>
+        <v>0.00377524106450906</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.002891888951502434</v>
+        <v>0.002890784434391435</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01708510409172775</v>
+        <v>0.01707141329884695</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01055620094165153</v>
+        <v>0.01055113661344337</v>
       </c>
       <c r="T62" t="n">
-        <v>0.01001929893170729</v>
+        <v>0.01001794179487657</v>
       </c>
       <c r="U62" t="n">
-        <v>0.007964224673806039</v>
+        <v>0.007977162953683808</v>
       </c>
       <c r="V62" t="n">
-        <v>0.004498590127782346</v>
+        <v>0.004500605763905186</v>
       </c>
       <c r="W62" t="n">
-        <v>0.03397355668983816</v>
+        <v>0.03399598931009478</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02236573402603507</v>
+        <v>0.02236665683064162</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3712793451295304</v>
+        <v>0.371279416122849</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5283584391795361</v>
+        <v>0.5283584213346767</v>
       </c>
       <c r="M63" t="n">
-        <v>4.032785542367162</v>
+        <v>4.032786438210414</v>
       </c>
       <c r="N63" t="n">
-        <v>4.294852238078497</v>
+        <v>4.294852177236955</v>
       </c>
       <c r="O63" t="n">
-        <v>0.005537805848895896</v>
+        <v>0.005537803586461179</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0074515843057457</v>
+        <v>0.007451581095653909</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002958696488616361</v>
+        <v>0.002958694854106709</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01478289595286687</v>
+        <v>0.01478289714484534</v>
       </c>
       <c r="S63" t="n">
-        <v>0.02259216607375159</v>
+        <v>0.02259206175753467</v>
       </c>
       <c r="T63" t="n">
-        <v>0.007720608479823516</v>
+        <v>0.007720584622724408</v>
       </c>
       <c r="U63" t="n">
-        <v>0.00927061440870936</v>
+        <v>0.009270521153485096</v>
       </c>
       <c r="V63" t="n">
-        <v>0.003736957256765788</v>
+        <v>0.003736941348585259</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01597877252799531</v>
+        <v>0.01597861029406603</v>
       </c>
       <c r="X63" t="n">
-        <v>0.04657832162947657</v>
+        <v>0.04657788354691615</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2665008022242393</v>
+        <v>0.2664992806655571</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5274523951771934</v>
+        <v>0.5274525176711109</v>
       </c>
       <c r="M64" t="n">
-        <v>3.919470058378178</v>
+        <v>3.919452017702655</v>
       </c>
       <c r="N64" t="n">
-        <v>4.306337359755369</v>
+        <v>4.306337562250604</v>
       </c>
       <c r="O64" t="n">
-        <v>0.006395490511863943</v>
+        <v>0.006395494750800205</v>
       </c>
       <c r="P64" t="n">
-        <v>0.007488293781800744</v>
+        <v>0.007488322507297828</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.004500634074302134</v>
+        <v>0.004500641607003707</v>
       </c>
       <c r="R64" t="n">
-        <v>0.02912685718544783</v>
+        <v>0.02912699888805108</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05592572937046784</v>
+        <v>0.05592796255944005</v>
       </c>
       <c r="T64" t="n">
-        <v>0.009248048119828248</v>
+        <v>0.009248058500763386</v>
       </c>
       <c r="U64" t="n">
-        <v>0.00963734871858862</v>
+        <v>0.009637479285853536</v>
       </c>
       <c r="V64" t="n">
-        <v>0.005837296435730784</v>
+        <v>0.005837315186295127</v>
       </c>
       <c r="W64" t="n">
-        <v>0.04527266360736645</v>
+        <v>0.04527318186301673</v>
       </c>
       <c r="X64" t="n">
-        <v>0.5741383341736978</v>
+        <v>0.5743065616455471</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3705977767793169</v>
+        <v>0.3705978997527218</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5347479820993566</v>
+        <v>0.5347479032228878</v>
       </c>
       <c r="M65" t="n">
-        <v>3.919437140445244</v>
+        <v>3.919438743173946</v>
       </c>
       <c r="N65" t="n">
-        <v>4.312903676909155</v>
+        <v>4.312903371490091</v>
       </c>
       <c r="O65" t="n">
-        <v>0.006567038489902901</v>
+        <v>0.006567011026608553</v>
       </c>
       <c r="P65" t="n">
-        <v>0.009291301484505837</v>
+        <v>0.009291265044294216</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.005059207543341328</v>
+        <v>0.005059195473896327</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01725338998781449</v>
+        <v>0.017253358530122</v>
       </c>
       <c r="S65" t="n">
-        <v>0.04457595703917552</v>
+        <v>0.04457560285531074</v>
       </c>
       <c r="T65" t="n">
-        <v>0.009263724505047598</v>
+        <v>0.009263674805511489</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01193624110781811</v>
+        <v>0.01193613605773242</v>
       </c>
       <c r="V65" t="n">
-        <v>0.006564081443977254</v>
+        <v>0.006564064060707944</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01627763747729805</v>
+        <v>0.0162775581513375</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1890572140702043</v>
+        <v>0.1890477182386672</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3123846531483918</v>
+        <v>0.3123839006204402</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5312811782261095</v>
+        <v>0.5312812108289982</v>
       </c>
       <c r="M66" t="n">
-        <v>4.0372004394865</v>
+        <v>4.037191967623349</v>
       </c>
       <c r="N66" t="n">
-        <v>4.308918207759948</v>
+        <v>4.30891837078826</v>
       </c>
       <c r="O66" t="n">
-        <v>0.006403456129815127</v>
+        <v>0.006403452165609063</v>
       </c>
       <c r="P66" t="n">
-        <v>0.008276722505966861</v>
+        <v>0.008276718812968206</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.004528767776314647</v>
+        <v>0.00452876663778323</v>
       </c>
       <c r="R66" t="n">
-        <v>0.02604835672299321</v>
+        <v>0.02604832947593625</v>
       </c>
       <c r="S66" t="n">
-        <v>0.038856132840531</v>
+        <v>0.03885692033457903</v>
       </c>
       <c r="T66" t="n">
-        <v>0.00921590487631741</v>
+        <v>0.009215903504681662</v>
       </c>
       <c r="U66" t="n">
-        <v>0.01026551251932469</v>
+        <v>0.01026547110010424</v>
       </c>
       <c r="V66" t="n">
-        <v>0.005890271532821016</v>
+        <v>0.00589026698028011</v>
       </c>
       <c r="W66" t="n">
-        <v>0.034986680189511</v>
+        <v>0.03498649909610336</v>
       </c>
       <c r="X66" t="n">
-        <v>0.2216974876740873</v>
+        <v>0.2217083379267043</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5593936798993145</v>
+        <v>0.5593924454499485</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5511050848074464</v>
+        <v>0.5511050906248832</v>
       </c>
       <c r="M67" t="n">
-        <v>4.434199252443003</v>
+        <v>4.434190060020733</v>
       </c>
       <c r="N67" t="n">
-        <v>4.372467773239976</v>
+        <v>4.372467816418642</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005810294236388103</v>
+        <v>0.005810723124134572</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01807506346061479</v>
+        <v>0.0180756172306622</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.004460983961945137</v>
+        <v>0.00446100269598462</v>
       </c>
       <c r="R67" t="n">
-        <v>0.01478758572647783</v>
+        <v>0.01478804084616026</v>
       </c>
       <c r="S67" t="n">
-        <v>0.1218357413497161</v>
+        <v>0.1218443679464897</v>
       </c>
       <c r="T67" t="n">
-        <v>0.008988584861471633</v>
+        <v>0.008989068092398956</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01645928843055802</v>
+        <v>0.0164595423774586</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0083946894445661</v>
+        <v>0.008394677859924055</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01808809256542971</v>
+        <v>0.0180886280399006</v>
       </c>
       <c r="X67" t="n">
-        <v>0.1492326560758366</v>
+        <v>0.1492429687118153</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5709446758847706</v>
+        <v>0.5709446760465906</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5512229937090362</v>
+        <v>0.5512229938039233</v>
       </c>
       <c r="M68" t="n">
-        <v>4.520196890876156</v>
+        <v>4.520196892080668</v>
       </c>
       <c r="N68" t="n">
-        <v>4.37334326431771</v>
+        <v>4.373343265024216</v>
       </c>
       <c r="O68" t="n">
-        <v>0.00544297808667534</v>
+        <v>0.005442977854864222</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0201237168701102</v>
+        <v>0.02012371607624067</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004907960555246157</v>
+        <v>0.004907960436824325</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01926828959130466</v>
+        <v>0.0192682889255027</v>
       </c>
       <c r="S68" t="n">
-        <v>0.03435910924595399</v>
+        <v>0.03435910574545667</v>
       </c>
       <c r="T68" t="n">
-        <v>0.008974918624448453</v>
+        <v>0.008974918208018951</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01889077044834286</v>
+        <v>0.01889076964371699</v>
       </c>
       <c r="V68" t="n">
-        <v>0.007172022044769497</v>
+        <v>0.007172021920671532</v>
       </c>
       <c r="W68" t="n">
-        <v>0.02531331626586761</v>
+        <v>0.02531331525884701</v>
       </c>
       <c r="X68" t="n">
-        <v>0.04759366034142251</v>
+        <v>0.04759365419645756</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4227647615340945</v>
+        <v>0.4227645132326193</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5373287944473988</v>
+        <v>0.5373287634944319</v>
       </c>
       <c r="M69" t="n">
-        <v>4.368894955962674</v>
+        <v>4.368895569985296</v>
       </c>
       <c r="N69" t="n">
-        <v>4.372310551563071</v>
+        <v>4.372310639385343</v>
       </c>
       <c r="O69" t="n">
-        <v>0.004670762396775427</v>
+        <v>0.00467077101572015</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00727317018686316</v>
+        <v>0.007273179613454459</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.004458407973968088</v>
+        <v>0.004458413590520472</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009195830713596094</v>
+        <v>0.009195854450362121</v>
       </c>
       <c r="S69" t="n">
-        <v>0.007272017115655488</v>
+        <v>0.007272017611276992</v>
       </c>
       <c r="T69" t="n">
-        <v>0.006158766567799165</v>
+        <v>0.006158815343903133</v>
       </c>
       <c r="U69" t="n">
-        <v>0.008909246267713366</v>
+        <v>0.008909441120746544</v>
       </c>
       <c r="V69" t="n">
-        <v>0.00625619934515729</v>
+        <v>0.006256341416213982</v>
       </c>
       <c r="W69" t="n">
-        <v>0.01013636437864746</v>
+        <v>0.01013656006851842</v>
       </c>
       <c r="X69" t="n">
-        <v>0.009042482915033973</v>
+        <v>0.009042561635130907</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5503708566416453</v>
+        <v>0.5503708593126074</v>
       </c>
       <c r="L70" t="n">
-        <v>0.557175866779264</v>
+        <v>0.5571758683644447</v>
       </c>
       <c r="M70" t="n">
-        <v>4.366998961487805</v>
+        <v>4.36699898138397</v>
       </c>
       <c r="N70" t="n">
-        <v>4.417682680857455</v>
+        <v>4.417682692663453</v>
       </c>
       <c r="O70" t="n">
-        <v>0.005197892510978567</v>
+        <v>0.005197894341232977</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009986064107254541</v>
+        <v>0.009986069237390255</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.006403778328533694</v>
+        <v>0.006403779732745967</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009446083806372806</v>
+        <v>0.009446089063799358</v>
       </c>
       <c r="S70" t="n">
-        <v>0.01226053674075214</v>
+        <v>0.01226054344169278</v>
       </c>
       <c r="T70" t="n">
-        <v>0.006627898998414096</v>
+        <v>0.006627900707491545</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01000198339900437</v>
+        <v>0.01000198877797201</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009263447270604658</v>
+        <v>0.009263449258998484</v>
       </c>
       <c r="W70" t="n">
-        <v>0.01102278787193809</v>
+        <v>0.01102279435530214</v>
       </c>
       <c r="X70" t="n">
-        <v>0.01592689177776248</v>
+        <v>0.01592689196276542</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5091634325943012</v>
+        <v>0.5091633868659499</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5595167832296695</v>
+        <v>0.5595167785676533</v>
       </c>
       <c r="M71" t="n">
-        <v>4.443210889445625</v>
+        <v>4.443210832107212</v>
       </c>
       <c r="N71" t="n">
-        <v>4.451562041033815</v>
+        <v>4.451562032231279</v>
       </c>
       <c r="O71" t="n">
-        <v>0.006876278507295617</v>
+        <v>0.006876278584488734</v>
       </c>
       <c r="P71" t="n">
-        <v>0.01116184222329778</v>
+        <v>0.01116184002308088</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.005974497088690771</v>
+        <v>0.005974496559981057</v>
       </c>
       <c r="R71" t="n">
-        <v>0.008187076760039035</v>
+        <v>0.008187074949367764</v>
       </c>
       <c r="S71" t="n">
-        <v>0.009397779318734149</v>
+        <v>0.009397778572936827</v>
       </c>
       <c r="T71" t="n">
-        <v>0.008990604501086238</v>
+        <v>0.008990627207162968</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01134582745677095</v>
+        <v>0.01134582927213883</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007934367505822342</v>
+        <v>0.007934375252081498</v>
       </c>
       <c r="W71" t="n">
-        <v>0.009655708446340495</v>
+        <v>0.009655729602417553</v>
       </c>
       <c r="X71" t="n">
-        <v>0.009190324929476178</v>
+        <v>0.009190343741585835</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5525686244778018</v>
+        <v>0.5525676405558657</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5680789099687878</v>
+        <v>0.568078879891796</v>
       </c>
       <c r="M72" t="n">
-        <v>4.490464158932846</v>
+        <v>4.490463887273571</v>
       </c>
       <c r="N72" t="n">
-        <v>4.500431880349488</v>
+        <v>4.500431834869093</v>
       </c>
       <c r="O72" t="n">
-        <v>0.005880365508362228</v>
+        <v>0.005880356041585741</v>
       </c>
       <c r="P72" t="n">
-        <v>0.00833042388929766</v>
+        <v>0.008330389566801181</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.006764412505359232</v>
+        <v>0.006764396574722088</v>
       </c>
       <c r="R72" t="n">
-        <v>0.006297990399647873</v>
+        <v>0.006297975494368146</v>
       </c>
       <c r="S72" t="n">
-        <v>0.008934965214403429</v>
+        <v>0.008934959151146142</v>
       </c>
       <c r="T72" t="n">
-        <v>0.007380016180022536</v>
+        <v>0.00738001383587514</v>
       </c>
       <c r="U72" t="n">
-        <v>0.00827478219519682</v>
+        <v>0.008274752344368724</v>
       </c>
       <c r="V72" t="n">
-        <v>0.009367818521080101</v>
+        <v>0.009367787854908679</v>
       </c>
       <c r="W72" t="n">
-        <v>0.008273389077911938</v>
+        <v>0.008273370833510011</v>
       </c>
       <c r="X72" t="n">
-        <v>0.009789025703110863</v>
+        <v>0.009789008837257649</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5594245360474558</v>
+        <v>0.5594245356377606</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5542417089438341</v>
+        <v>0.5542417087873213</v>
       </c>
       <c r="M73" t="n">
-        <v>4.434429024992574</v>
+        <v>4.43442902194175</v>
       </c>
       <c r="N73" t="n">
-        <v>4.395830258319456</v>
+        <v>4.395830257153843</v>
       </c>
       <c r="O73" t="n">
-        <v>0.00311165531131248</v>
+        <v>0.003111655234723161</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01168548851110581</v>
+        <v>0.01168548808111125</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002575281000338605</v>
+        <v>0.002575280609140498</v>
       </c>
       <c r="R73" t="n">
-        <v>0.01010763561941757</v>
+        <v>0.01010763507961342</v>
       </c>
       <c r="S73" t="n">
-        <v>0.004155254204392331</v>
+        <v>0.004155253945700331</v>
       </c>
       <c r="T73" t="n">
-        <v>0.004794608039332855</v>
+        <v>0.004794606663299697</v>
       </c>
       <c r="U73" t="n">
-        <v>0.01195658560655915</v>
+        <v>0.01195659331495061</v>
       </c>
       <c r="V73" t="n">
-        <v>0.004188052880264031</v>
+        <v>0.004188051797655148</v>
       </c>
       <c r="W73" t="n">
-        <v>0.01157681866482518</v>
+        <v>0.0115768137261033</v>
       </c>
       <c r="X73" t="n">
-        <v>0.005866721198758036</v>
+        <v>0.005866719274250102</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5539023206624197</v>
+        <v>0.5539023225854812</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5600764583033748</v>
+        <v>0.5600764589046899</v>
       </c>
       <c r="M74" t="n">
-        <v>4.39330331686405</v>
+        <v>4.393303331187163</v>
       </c>
       <c r="N74" t="n">
-        <v>4.439282545417659</v>
+        <v>4.439282549895685</v>
       </c>
       <c r="O74" t="n">
-        <v>0.003539485399138183</v>
+        <v>0.003539485668819712</v>
       </c>
       <c r="P74" t="n">
-        <v>0.009459346724213735</v>
+        <v>0.009459348347293849</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003942887401724333</v>
+        <v>0.003942887819154635</v>
       </c>
       <c r="R74" t="n">
-        <v>0.005261283744490171</v>
+        <v>0.005261284209655393</v>
       </c>
       <c r="S74" t="n">
-        <v>0.007590543917671987</v>
+        <v>0.007590543920279602</v>
       </c>
       <c r="T74" t="n">
-        <v>0.005069254413929998</v>
+        <v>0.005069255950003198</v>
       </c>
       <c r="U74" t="n">
-        <v>0.009201447473960093</v>
+        <v>0.009201439006543988</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005810979187408047</v>
+        <v>0.005810984256595005</v>
       </c>
       <c r="W74" t="n">
-        <v>0.006881547076612756</v>
+        <v>0.006881550152034082</v>
       </c>
       <c r="X74" t="n">
-        <v>0.009132946016990691</v>
+        <v>0.00913296714761927</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5371232694513625</v>
+        <v>0.5371232677635055</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5502940645259519</v>
+        <v>0.5502940657481453</v>
       </c>
       <c r="M75" t="n">
-        <v>4.268291721388134</v>
+        <v>4.268291708808715</v>
       </c>
       <c r="N75" t="n">
-        <v>4.366423447898454</v>
+        <v>4.366423457001999</v>
       </c>
       <c r="O75" t="n">
-        <v>0.00439309765914696</v>
+        <v>0.004393098330925994</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01026514405593301</v>
+        <v>0.01026514613395234</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004907746701731233</v>
+        <v>0.004907747620813534</v>
       </c>
       <c r="R75" t="n">
-        <v>0.009513237997438131</v>
+        <v>0.009513240072563793</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01069227173459293</v>
+        <v>0.0106922747083258</v>
       </c>
       <c r="T75" t="n">
-        <v>0.005999087667311785</v>
+        <v>0.005999088194199288</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01037288258797529</v>
+        <v>0.01037287955940899</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006861234173145976</v>
+        <v>0.006861236984615546</v>
       </c>
       <c r="W75" t="n">
-        <v>0.01130364763349416</v>
+        <v>0.01130365262903175</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01507697132009915</v>
+        <v>0.01507702801412776</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.543770931818184</v>
+        <v>0.5437709213996799</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5538113906052184</v>
+        <v>0.5538113897340888</v>
       </c>
       <c r="M76" t="n">
-        <v>4.439776253946184</v>
+        <v>4.439776240423371</v>
       </c>
       <c r="N76" t="n">
-        <v>4.395512032867538</v>
+        <v>4.395512028912898</v>
       </c>
       <c r="O76" t="n">
-        <v>0.00376515086459863</v>
+        <v>0.003765151763956153</v>
       </c>
       <c r="P76" t="n">
-        <v>0.009554323552334621</v>
+        <v>0.009554325494936693</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002443056166938659</v>
+        <v>0.002443056855633676</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01133257225905577</v>
+        <v>0.01133257404339707</v>
       </c>
       <c r="S76" t="n">
-        <v>0.003795502052632326</v>
+        <v>0.003795502621115864</v>
       </c>
       <c r="T76" t="n">
-        <v>0.005318788553107376</v>
+        <v>0.005318738638685904</v>
       </c>
       <c r="U76" t="n">
-        <v>0.01000660700825819</v>
+        <v>0.01000634855198076</v>
       </c>
       <c r="V76" t="n">
-        <v>0.004101939093407743</v>
+        <v>0.004101932385757781</v>
       </c>
       <c r="W76" t="n">
-        <v>0.01244610098890504</v>
+        <v>0.01244554401553114</v>
       </c>
       <c r="X76" t="n">
-        <v>0.00456629799931043</v>
+        <v>0.004566164961942887</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.4954473192373093</v>
+        <v>0.4954568924422989</v>
       </c>
       <c r="L77" t="n">
-        <v>0.548596006887663</v>
+        <v>0.5485968610346551</v>
       </c>
       <c r="M77" t="n">
-        <v>4.299272883877356</v>
+        <v>4.299271167020737</v>
       </c>
       <c r="N77" t="n">
-        <v>4.371593978891362</v>
+        <v>4.371593020958598</v>
       </c>
       <c r="O77" t="n">
-        <v>0.003514394027650367</v>
+        <v>0.003514378386156498</v>
       </c>
       <c r="P77" t="n">
-        <v>0.006422358746301867</v>
+        <v>0.006422458169288816</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002406775463466088</v>
+        <v>0.00240674670774936</v>
       </c>
       <c r="R77" t="n">
-        <v>0.002094916752757647</v>
+        <v>0.002094905227484751</v>
       </c>
       <c r="S77" t="n">
-        <v>0.004492136251616273</v>
+        <v>0.004492136047748646</v>
       </c>
       <c r="T77" t="n">
-        <v>0.004358661885619052</v>
+        <v>0.00439450699667728</v>
       </c>
       <c r="U77" t="n">
-        <v>0.007045527553508763</v>
+        <v>0.007193675143823135</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003433228032099846</v>
+        <v>0.00343370804250593</v>
       </c>
       <c r="W77" t="n">
-        <v>0.003824274931390079</v>
+        <v>0.003868426717809448</v>
       </c>
       <c r="X77" t="n">
-        <v>0.004812375491480065</v>
+        <v>0.004876295924066332</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4805966135072755</v>
+        <v>0.480595184661407</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5552627887316869</v>
+        <v>0.5552628847924577</v>
       </c>
       <c r="M78" t="n">
-        <v>4.450858392300603</v>
+        <v>4.450860975036541</v>
       </c>
       <c r="N78" t="n">
-        <v>4.449226622035585</v>
+        <v>4.449229004314714</v>
       </c>
       <c r="O78" t="n">
-        <v>0.001936822978948697</v>
+        <v>0.001936858604100439</v>
       </c>
       <c r="P78" t="n">
-        <v>0.007578632092538344</v>
+        <v>0.007578806295593824</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.00169054935656184</v>
+        <v>0.001690576618859039</v>
       </c>
       <c r="R78" t="n">
-        <v>0.001176642679695474</v>
+        <v>0.001176680891077756</v>
       </c>
       <c r="S78" t="n">
-        <v>0.002130181124430956</v>
+        <v>0.002130235683015278</v>
       </c>
       <c r="T78" t="n">
-        <v>0.003228607964990603</v>
+        <v>0.003228608226449816</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01152534273590268</v>
+        <v>0.01152545037303081</v>
       </c>
       <c r="V78" t="n">
-        <v>0.002781483306091168</v>
+        <v>0.002781506794120777</v>
       </c>
       <c r="W78" t="n">
-        <v>0.00304528819090173</v>
+        <v>0.003045320310414962</v>
       </c>
       <c r="X78" t="n">
-        <v>0.00490221643771764</v>
+        <v>0.004902318566328075</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5610550899029443</v>
+        <v>0.5610551126721089</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5629314367691181</v>
+        <v>0.5629307178031868</v>
       </c>
       <c r="M79" t="n">
-        <v>4.446570697558703</v>
+        <v>4.446570867100848</v>
       </c>
       <c r="N79" t="n">
-        <v>4.460541586380009</v>
+        <v>4.46053623321937</v>
       </c>
       <c r="O79" t="n">
-        <v>0.002363085701296157</v>
+        <v>0.00236308343499959</v>
       </c>
       <c r="P79" t="n">
-        <v>0.002493468230435302</v>
+        <v>0.002493468373352354</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001893448215024157</v>
+        <v>0.001893447483266265</v>
       </c>
       <c r="R79" t="n">
-        <v>0.003174909657180953</v>
+        <v>0.003174909123613709</v>
       </c>
       <c r="S79" t="n">
-        <v>0.001052083578125455</v>
+        <v>0.001052246697884329</v>
       </c>
       <c r="T79" t="n">
-        <v>0.003513707948563072</v>
+        <v>0.003513707945610168</v>
       </c>
       <c r="U79" t="n">
-        <v>0.001972333434337066</v>
+        <v>0.001972332749004523</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002786667368745591</v>
+        <v>0.002786666825571839</v>
       </c>
       <c r="W79" t="n">
-        <v>0.003641212570746621</v>
+        <v>0.003641212240208892</v>
       </c>
       <c r="X79" t="n">
-        <v>0.07481062806337774</v>
+        <v>0.07481857707704458</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5606777633938708</v>
+        <v>0.560678124195241</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5621761495646145</v>
+        <v>0.5621761154932691</v>
       </c>
       <c r="M80" t="n">
-        <v>4.540036555089061</v>
+        <v>4.540036489764575</v>
       </c>
       <c r="N80" t="n">
-        <v>4.455659895741714</v>
+        <v>4.455659602309535</v>
       </c>
       <c r="O80" t="n">
-        <v>0.002599970185083688</v>
+        <v>0.002599967079706541</v>
       </c>
       <c r="P80" t="n">
-        <v>0.003273923925492484</v>
+        <v>0.003273923233343639</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.002203463077328192</v>
+        <v>0.002203462988424281</v>
       </c>
       <c r="R80" t="n">
-        <v>0.00384608703530474</v>
+        <v>0.003846082800576127</v>
       </c>
       <c r="S80" t="n">
-        <v>0.005904300473565313</v>
+        <v>0.00590489450922545</v>
       </c>
       <c r="T80" t="n">
-        <v>0.003812021045588731</v>
+        <v>0.003812020139449461</v>
       </c>
       <c r="U80" t="n">
-        <v>0.002224358336050397</v>
+        <v>0.00222437410316246</v>
       </c>
       <c r="V80" t="n">
-        <v>0.003489054886496084</v>
+        <v>0.003489057371578768</v>
       </c>
       <c r="W80" t="n">
-        <v>0.004626723061293953</v>
+        <v>0.004626726888160479</v>
       </c>
       <c r="X80" t="n">
-        <v>0.5704342537206961</v>
+        <v>0.5705363877163621</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4048865563859553</v>
+        <v>0.4048866820430508</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5494547447668545</v>
+        <v>0.5494548342855183</v>
       </c>
       <c r="M81" t="n">
-        <v>4.610890896156159</v>
+        <v>4.610890901594733</v>
       </c>
       <c r="N81" t="n">
-        <v>4.50669197392645</v>
+        <v>4.506692430450761</v>
       </c>
       <c r="O81" t="n">
-        <v>0.002428961705262596</v>
+        <v>0.002428960214813898</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002791026477254393</v>
+        <v>0.002791025939544275</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.00144773530934036</v>
+        <v>0.001447734988776757</v>
       </c>
       <c r="R81" t="n">
-        <v>0.002790549440473973</v>
+        <v>0.002790548055071088</v>
       </c>
       <c r="S81" t="n">
-        <v>0.4970937479109305</v>
+        <v>0.4999999999880164</v>
       </c>
       <c r="T81" t="n">
-        <v>0.003414184336332713</v>
+        <v>0.003498515546543223</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003793369303878517</v>
+        <v>0.003489957258036443</v>
       </c>
       <c r="V81" t="n">
-        <v>0.002088591239415925</v>
+        <v>0.002103168930339552</v>
       </c>
       <c r="W81" t="n">
-        <v>0.00350913951207799</v>
+        <v>0.003523783595147308</v>
       </c>
       <c r="X81" t="n">
-        <v>3848.570378750543</v>
+        <v>4805.882907992461</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2917254962962554</v>
+        <v>0.291725558480019</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5178693238662242</v>
+        <v>0.5178693575299822</v>
       </c>
       <c r="M82" t="n">
-        <v>4.60546490597388</v>
+        <v>4.60546498201934</v>
       </c>
       <c r="N82" t="n">
-        <v>4.601086151681378</v>
+        <v>4.601086160636482</v>
       </c>
       <c r="O82" t="n">
-        <v>0.002719871433499834</v>
+        <v>0.002719871301947985</v>
       </c>
       <c r="P82" t="n">
-        <v>0.002535876708074974</v>
+        <v>0.00253587728230467</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001383850360950985</v>
+        <v>0.00138384989641135</v>
       </c>
       <c r="R82" t="n">
-        <v>0.00292486519799948</v>
+        <v>0.002924865747517776</v>
       </c>
       <c r="S82" t="n">
-        <v>1.000000000000024e-05</v>
+        <v>1.000000000000054e-05</v>
       </c>
       <c r="T82" t="n">
-        <v>0.004248012958814035</v>
+        <v>0.004248081381766614</v>
       </c>
       <c r="U82" t="n">
-        <v>0.004343343403376987</v>
+        <v>0.004342906727920833</v>
       </c>
       <c r="V82" t="n">
-        <v>0.002168905907955907</v>
+        <v>0.002168929719543218</v>
       </c>
       <c r="W82" t="n">
-        <v>0.004086730059497589</v>
+        <v>0.004086683566095062</v>
       </c>
       <c r="X82" t="n">
-        <v>0.05111998818579167</v>
+        <v>0.05111790229359389</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5433397409012656</v>
+        <v>0.5433397459150068</v>
       </c>
       <c r="L83" t="n">
-        <v>0.568047653279075</v>
+        <v>0.5680487479049672</v>
       </c>
       <c r="M83" t="n">
-        <v>4.643199327406445</v>
+        <v>4.643205446022499</v>
       </c>
       <c r="N83" t="n">
-        <v>4.506010167611416</v>
+        <v>4.506018547893986</v>
       </c>
       <c r="O83" t="n">
-        <v>0.002227698822576718</v>
+        <v>0.00222770337106413</v>
       </c>
       <c r="P83" t="n">
-        <v>0.002262664115710382</v>
+        <v>0.002262664769353419</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.001305320341763647</v>
+        <v>0.001305322877718494</v>
       </c>
       <c r="R83" t="n">
-        <v>0.003179082081773116</v>
+        <v>0.003179088321280501</v>
       </c>
       <c r="S83" t="n">
-        <v>0.003402653009224385</v>
+        <v>0.003401039099769599</v>
       </c>
       <c r="T83" t="n">
-        <v>0.003216009133716249</v>
+        <v>0.003216066046411047</v>
       </c>
       <c r="U83" t="n">
-        <v>0.002817291396255174</v>
+        <v>0.00281731206177527</v>
       </c>
       <c r="V83" t="n">
-        <v>0.002031680929999283</v>
+        <v>0.002031703742984063</v>
       </c>
       <c r="W83" t="n">
-        <v>0.004408586241488692</v>
+        <v>0.00440866763399387</v>
       </c>
       <c r="X83" t="n">
-        <v>0.2572767808716217</v>
+        <v>0.2570912188601854</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3162631075751626</v>
+        <v>0.3162642480996137</v>
       </c>
       <c r="L84" t="n">
-        <v>0.5366847260638746</v>
+        <v>0.5366847839923332</v>
       </c>
       <c r="M84" t="n">
-        <v>4.586521951223069</v>
+        <v>4.586544988422995</v>
       </c>
       <c r="N84" t="n">
-        <v>4.463342169515876</v>
+        <v>4.463344260178164</v>
       </c>
       <c r="O84" t="n">
-        <v>0.002313297494916917</v>
+        <v>0.002313305976743061</v>
       </c>
       <c r="P84" t="n">
-        <v>0.002082577737801762</v>
+        <v>0.002082578597031732</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001745268954148658</v>
+        <v>0.001745275360421834</v>
       </c>
       <c r="R84" t="n">
-        <v>0.003865178165058029</v>
+        <v>0.003865186376802885</v>
       </c>
       <c r="S84" t="n">
-        <v>0.008291942405082891</v>
+        <v>0.008281615069399019</v>
       </c>
       <c r="T84" t="n">
-        <v>0.003480762303234616</v>
+        <v>0.003480527514033219</v>
       </c>
       <c r="U84" t="n">
-        <v>0.002490090000258875</v>
+        <v>0.002489851181749412</v>
       </c>
       <c r="V84" t="n">
-        <v>0.002703508748651533</v>
+        <v>0.002703440278360256</v>
       </c>
       <c r="W84" t="n">
-        <v>0.004977752067832083</v>
+        <v>0.004977033146368077</v>
       </c>
       <c r="X84" t="n">
-        <v>1.305643617663522</v>
+        <v>1.302690081687144</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4976135263187852</v>
+        <v>0.4915819063210994</v>
       </c>
       <c r="L85" t="n">
-        <v>0.565054041765216</v>
+        <v>0.5548813474585903</v>
       </c>
       <c r="M85" t="n">
-        <v>4.548143428306743</v>
+        <v>4.449872865454893</v>
       </c>
       <c r="N85" t="n">
-        <v>4.489773371941594</v>
+        <v>4.42057021953541</v>
       </c>
       <c r="O85" t="n">
-        <v>0.002408190510449579</v>
+        <v>0.002357558792331891</v>
       </c>
       <c r="P85" t="n">
-        <v>0.001980400080365809</v>
+        <v>0.002485564840947573</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001309120037836047</v>
+        <v>0.001484534252581396</v>
       </c>
       <c r="R85" t="n">
-        <v>0.003562330014203676</v>
+        <v>0.00316902437228997</v>
       </c>
       <c r="S85" t="n">
-        <v>0.00123190960995527</v>
+        <v>0.005833756056695323</v>
       </c>
       <c r="T85" t="n">
-        <v>0.00368994731817053</v>
+        <v>0.003681185996465295</v>
       </c>
       <c r="U85" t="n">
-        <v>0.00285676467699851</v>
+        <v>0.002894931380161413</v>
       </c>
       <c r="V85" t="n">
-        <v>0.001940873950962805</v>
+        <v>0.002160197724446098</v>
       </c>
       <c r="W85" t="n">
-        <v>0.00440105838592013</v>
+        <v>0.003581966974431122</v>
       </c>
       <c r="X85" t="n">
-        <v>0.08426531387665179</v>
+        <v>0.6613223569176252</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5001855836882525</v>
+        <v>0.4578443045975884</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5645914963074464</v>
+        <v>0.5544587055430522</v>
       </c>
       <c r="M86" t="n">
-        <v>4.655189285584574</v>
+        <v>4.558363897467068</v>
       </c>
       <c r="N86" t="n">
-        <v>4.489136163132573</v>
+        <v>4.456949992647446</v>
       </c>
       <c r="O86" t="n">
-        <v>0.002558869330777236</v>
+        <v>0.00246660163874325</v>
       </c>
       <c r="P86" t="n">
-        <v>0.002498492652343923</v>
+        <v>0.003071255053762073</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001800170855414211</v>
+        <v>0.001923655609098718</v>
       </c>
       <c r="R86" t="n">
-        <v>0.004656547004153229</v>
+        <v>0.003812025262396995</v>
       </c>
       <c r="S86" t="n">
-        <v>0.001924593010585424</v>
+        <v>0.006203447779970939</v>
       </c>
       <c r="T86" t="n">
-        <v>0.003736981048562122</v>
+        <v>0.003595678802248549</v>
       </c>
       <c r="U86" t="n">
-        <v>0.003584250534883362</v>
+        <v>0.003588213010299361</v>
       </c>
       <c r="V86" t="n">
-        <v>0.002774650183428768</v>
+        <v>0.002997924946737783</v>
       </c>
       <c r="W86" t="n">
-        <v>0.006432464490078314</v>
+        <v>0.004613676667451388</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1095005539816664</v>
+        <v>0.6788687177561488</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1801165461460996</v>
+        <v>0.2964562122809248</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5054837591759742</v>
+        <v>0.5270097738427626</v>
       </c>
       <c r="M87" t="n">
-        <v>4.683999502138008</v>
+        <v>4.607564071222449</v>
       </c>
       <c r="N87" t="n">
-        <v>4.634427081471261</v>
+        <v>4.600542944439558</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0027420541333345</v>
+        <v>0.003052611825797706</v>
       </c>
       <c r="P87" t="n">
-        <v>0.001648542138880211</v>
+        <v>0.00292172564219639</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.001410820131783913</v>
+        <v>0.001613908686034291</v>
       </c>
       <c r="R87" t="n">
-        <v>0.003212262748333969</v>
+        <v>0.003336844883070103</v>
       </c>
       <c r="S87" t="n">
-        <v>1.000000000000122e-05</v>
+        <v>1.00000000002813e-05</v>
       </c>
       <c r="T87" t="n">
-        <v>0.004389203178119717</v>
+        <v>0.004879021979478724</v>
       </c>
       <c r="U87" t="n">
-        <v>0.003541782793342259</v>
+        <v>0.004490123228233441</v>
       </c>
       <c r="V87" t="n">
-        <v>0.002233922942977511</v>
+        <v>0.002514755191673077</v>
       </c>
       <c r="W87" t="n">
-        <v>0.004658863784332157</v>
+        <v>0.004651985430625421</v>
       </c>
       <c r="X87" t="n">
-        <v>0.05913731895939856</v>
+        <v>0.04537730438535553</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1739893793974186</v>
+        <v>0.3754603734848493</v>
       </c>
       <c r="L88" t="n">
-        <v>0.531456512631705</v>
+        <v>0.5440395807100645</v>
       </c>
       <c r="M88" t="n">
-        <v>4.663409450690607</v>
+        <v>4.61250856617769</v>
       </c>
       <c r="N88" t="n">
-        <v>4.538225610173969</v>
+        <v>4.527211662328532</v>
       </c>
       <c r="O88" t="n">
-        <v>0.002238878514135571</v>
+        <v>0.002594023810612239</v>
       </c>
       <c r="P88" t="n">
-        <v>0.007913876977934463</v>
+        <v>0.002937226842315908</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001210169754577415</v>
+        <v>0.001542982813600202</v>
       </c>
       <c r="R88" t="n">
-        <v>0.002454898789865113</v>
+        <v>0.00297169671989258</v>
       </c>
       <c r="S88" t="n">
-        <v>0.003161005565094947</v>
+        <v>0.002078679216776771</v>
       </c>
       <c r="T88" t="n">
-        <v>0.003329725902673043</v>
+        <v>0.003831758238383444</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01480037036079343</v>
+        <v>0.00385396002428446</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001856416415990756</v>
+        <v>0.002257348336782559</v>
       </c>
       <c r="W88" t="n">
-        <v>0.003297606894965767</v>
+        <v>0.003863956929424431</v>
       </c>
       <c r="X88" t="n">
-        <v>0.2944849453992233</v>
+        <v>0.1484832363841364</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.2744023045987236</v>
+        <v>0.2736747903302026</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5414997110839789</v>
+        <v>0.5414285896090815</v>
       </c>
       <c r="M89" t="n">
-        <v>4.565818894645068</v>
+        <v>4.565354349996714</v>
       </c>
       <c r="N89" t="n">
-        <v>4.509249927115496</v>
+        <v>4.509971428419417</v>
       </c>
       <c r="O89" t="n">
-        <v>0.002870152866398225</v>
+        <v>0.002880267046105816</v>
       </c>
       <c r="P89" t="n">
-        <v>0.002980408686188588</v>
+        <v>0.00298109841728312</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001635021145719489</v>
+        <v>0.001636950178660084</v>
       </c>
       <c r="R89" t="n">
-        <v>0.002699915099193609</v>
+        <v>0.002705031044326635</v>
       </c>
       <c r="S89" t="n">
-        <v>0.02207086978893256</v>
+        <v>0.006913556171091726</v>
       </c>
       <c r="T89" t="n">
-        <v>0.004720102390084328</v>
+        <v>0.00471077465768644</v>
       </c>
       <c r="U89" t="n">
-        <v>0.003210622145672739</v>
+        <v>0.003184566461932957</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002316230871430764</v>
+        <v>0.002309157246770159</v>
       </c>
       <c r="W89" t="n">
-        <v>0.003556408585269232</v>
+        <v>0.003518689838708392</v>
       </c>
       <c r="X89" t="n">
-        <v>8.854709178984095</v>
+        <v>0.9458894945983656</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2308034783562465</v>
+        <v>0.465001354613409</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4987691681967517</v>
+        <v>0.5376683208221573</v>
       </c>
       <c r="M90" t="n">
-        <v>4.504155908456531</v>
+        <v>4.563163426097284</v>
       </c>
       <c r="N90" t="n">
-        <v>4.286946619164399</v>
+        <v>4.297768314960274</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003712133724656009</v>
+        <v>0.003721995996715044</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003674065116094049</v>
+        <v>0.004600914156066681</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.006663209495693349</v>
+        <v>0.00707324403134388</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01028761199310081</v>
+        <v>0.01166867402569947</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002286678512656472</v>
+        <v>0.002142153199347682</v>
       </c>
       <c r="T90" t="n">
-        <v>0.006750567744379495</v>
+        <v>0.006219197860778703</v>
       </c>
       <c r="U90" t="n">
-        <v>0.006071709254221282</v>
+        <v>0.006260238092200945</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01214344360832982</v>
+        <v>0.006723042426929515</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02711329984200849</v>
+        <v>0.02702039182686322</v>
       </c>
       <c r="X90" t="n">
-        <v>0.08221776408323962</v>
+        <v>0.0604398899701111</v>
       </c>
     </row>
   </sheetData>
